--- a/research/traditional_assets/database/data/bermuda/bermuda_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_oilfield_svcs_equip.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ob_bwo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,115 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0857</v>
+        <v>0.0578</v>
       </c>
       <c r="G2">
-        <v>0.5137841658812442</v>
+        <v>0.521608565086826</v>
       </c>
       <c r="H2">
-        <v>0.5137841658812442</v>
+        <v>0.5153414283849066</v>
       </c>
       <c r="I2">
-        <v>0.1506833176248822</v>
+        <v>0.1556338947643296</v>
       </c>
       <c r="J2">
-        <v>0.1506833176248822</v>
+        <v>0.09025050922284125</v>
       </c>
       <c r="K2">
-        <v>71.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="L2">
-        <v>0.08435438265786993</v>
+        <v>0.05627366496931715</v>
       </c>
       <c r="M2">
         <v>25.4</v>
       </c>
       <c r="N2">
-        <v>0.04358270418668497</v>
+        <v>0.05566513258820951</v>
       </c>
       <c r="O2">
-        <v>0.3547486033519553</v>
+        <v>0.5893271461716937</v>
       </c>
       <c r="P2">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q2">
-        <v>0.0434111187371311</v>
+        <v>0.05566513258820951</v>
       </c>
       <c r="R2">
-        <v>0.3533519553072626</v>
+        <v>0.5893271461716937</v>
       </c>
       <c r="S2">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003937007874015803</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>243.4</v>
+        <v>277.7</v>
       </c>
       <c r="V2">
-        <v>0.4176389842141387</v>
+        <v>0.6085908393600701</v>
       </c>
       <c r="W2">
-        <v>0.08981435022579025</v>
+        <v>0.05180911167207598</v>
       </c>
       <c r="X2">
-        <v>0.1602177018238726</v>
+        <v>0.2934919223506617</v>
       </c>
       <c r="Y2">
-        <v>-0.07040335159808232</v>
+        <v>-0.2416828106785858</v>
       </c>
       <c r="Z2">
-        <v>0.4741899441340782</v>
+        <v>0.4629193109700816</v>
       </c>
       <c r="AA2">
-        <v>0.07145251396648045</v>
+        <v>0.04177870354413667</v>
       </c>
       <c r="AB2">
-        <v>0.07937665418431475</v>
+        <v>0.1263307424054955</v>
       </c>
       <c r="AC2">
-        <v>-0.007924140217834302</v>
+        <v>-0.08455203886135888</v>
       </c>
       <c r="AD2">
-        <v>1066</v>
+        <v>1250.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1066</v>
+        <v>1250.9</v>
       </c>
       <c r="AG2">
-        <v>822.6</v>
+        <v>973.2</v>
       </c>
       <c r="AH2">
-        <v>0.6465308102862688</v>
+        <v>0.7327202436738519</v>
       </c>
       <c r="AI2">
-        <v>0.4945488285780562</v>
+        <v>0.5330918389090135</v>
       </c>
       <c r="AJ2">
-        <v>0.5853137896684217</v>
+        <v>0.680797481636936</v>
       </c>
       <c r="AK2">
-        <v>0.430207625124209</v>
+        <v>0.4704176334106728</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="AM2">
-        <v>-21.2</v>
+        <v>18.6</v>
       </c>
       <c r="AN2">
-        <v>2.717308182513383</v>
+        <v>3.730688935281837</v>
+      </c>
+      <c r="AO2">
+        <v>3.820512820512821</v>
       </c>
       <c r="AP2">
-        <v>2.096864644404792</v>
+        <v>2.902475395168506</v>
       </c>
       <c r="AQ2">
-        <v>-6.033018867924529</v>
+        <v>6.408602150537634</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +721,8830 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0857</v>
+        <v>0.0578</v>
       </c>
       <c r="G3">
-        <v>0.5137841658812442</v>
+        <v>0.521608565086826</v>
       </c>
       <c r="H3">
-        <v>0.5137841658812442</v>
+        <v>0.5153414283849066</v>
       </c>
       <c r="I3">
-        <v>0.1506833176248822</v>
+        <v>0.1556338947643296</v>
       </c>
       <c r="J3">
-        <v>0.1506833176248822</v>
+        <v>0.09025050922284125</v>
       </c>
       <c r="K3">
-        <v>71.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="L3">
-        <v>0.08435438265786993</v>
+        <v>0.05627366496931715</v>
       </c>
       <c r="M3">
         <v>25.4</v>
       </c>
       <c r="N3">
-        <v>0.04358270418668497</v>
+        <v>0.05566513258820951</v>
       </c>
       <c r="O3">
-        <v>0.3547486033519553</v>
+        <v>0.5893271461716937</v>
       </c>
       <c r="P3">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q3">
-        <v>0.0434111187371311</v>
+        <v>0.05566513258820951</v>
       </c>
       <c r="R3">
-        <v>0.3533519553072626</v>
+        <v>0.5893271461716937</v>
       </c>
       <c r="S3">
-        <v>0.1000000000000014</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.003937007874015803</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>243.4</v>
+        <v>277.7</v>
       </c>
       <c r="V3">
-        <v>0.4176389842141387</v>
+        <v>0.6085908393600701</v>
       </c>
       <c r="W3">
-        <v>0.08981435022579025</v>
+        <v>0.05180911167207598</v>
       </c>
       <c r="X3">
-        <v>0.1602177018238726</v>
+        <v>0.2934919223506617</v>
       </c>
       <c r="Y3">
-        <v>-0.07040335159808232</v>
+        <v>-0.2416828106785858</v>
       </c>
       <c r="Z3">
-        <v>0.4741899441340782</v>
+        <v>0.4629193109700816</v>
       </c>
       <c r="AA3">
-        <v>0.07145251396648045</v>
+        <v>0.04177870354413667</v>
       </c>
       <c r="AB3">
-        <v>0.07937665418431475</v>
+        <v>0.1263307424054955</v>
       </c>
       <c r="AC3">
-        <v>-0.007924140217834302</v>
+        <v>-0.08455203886135888</v>
       </c>
       <c r="AD3">
-        <v>1066</v>
+        <v>1250.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1066</v>
+        <v>1250.9</v>
       </c>
       <c r="AG3">
-        <v>822.6</v>
+        <v>973.2</v>
       </c>
       <c r="AH3">
-        <v>0.6465308102862688</v>
+        <v>0.7327202436738519</v>
       </c>
       <c r="AI3">
-        <v>0.4945488285780562</v>
+        <v>0.5330918389090135</v>
       </c>
       <c r="AJ3">
-        <v>0.5853137896684217</v>
+        <v>0.680797481636936</v>
       </c>
       <c r="AK3">
-        <v>0.430207625124209</v>
+        <v>0.4704176334106728</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="AM3">
-        <v>-21.2</v>
+        <v>18.6</v>
       </c>
       <c r="AN3">
-        <v>2.717308182513383</v>
+        <v>3.730688935281837</v>
+      </c>
+      <c r="AO3">
+        <v>3.820512820512821</v>
       </c>
       <c r="AP3">
-        <v>2.096864644404792</v>
+        <v>2.902475395168506</v>
       </c>
       <c r="AQ3">
-        <v>-6.033018867924529</v>
+        <v>6.408602150537634</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BW Offshore Limited (OB:BWO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OB:BWO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oilfield Svcs/Equip.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.732720243673852</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>456.3</v>
+      </c>
+      <c r="H2">
+        <v>2115.77629288338</v>
+      </c>
+      <c r="I2">
+        <v>1429.5</v>
+      </c>
+      <c r="J2">
+        <v>1838.07629288338</v>
+      </c>
+      <c r="K2">
+        <v>1250.9</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.126330742405496</v>
+      </c>
+      <c r="N2">
+        <v>0.106873994944123</v>
+      </c>
+      <c r="O2">
+        <v>0.065354128440367</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.293491922350662</v>
+      </c>
+      <c r="T2">
+        <v>0.106873994944123</v>
+      </c>
+      <c r="U2">
+        <v>3.45353448740696</v>
+      </c>
+      <c r="V2">
+        <v>0.92305985625808</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>456.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.06535412844036698</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>335.3</v>
+      </c>
+      <c r="AH2">
+        <v>225.5</v>
+      </c>
+      <c r="AI2">
+        <v>729.9000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>1250.9</v>
+      </c>
+      <c r="AK2">
+        <v>1250.9</v>
+      </c>
+      <c r="AL2">
+        <v>31.2</v>
+      </c>
+      <c r="AM2">
+        <v>1250.9</v>
+      </c>
+      <c r="AN2">
+        <v>277.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1068739949441231</v>
+      </c>
+      <c r="C2">
+        <v>2115.776292883383</v>
+      </c>
+      <c r="D2">
+        <v>1838.076292883383</v>
+      </c>
+      <c r="E2">
+        <v>-1250.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>277.7</v>
+      </c>
+      <c r="H2">
+        <v>456.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>335.3</v>
+      </c>
+      <c r="K2">
+        <v>225.5</v>
+      </c>
+      <c r="L2">
+        <v>109.8</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>109.8</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>109.8</v>
+      </c>
+      <c r="Q2">
+        <v>335.3</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1068739949441231</v>
+      </c>
+      <c r="T2">
+        <v>0.9230598562580796</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1069429949441231</v>
+      </c>
+      <c r="C3">
+        <v>2096.843099897765</v>
+      </c>
+      <c r="D3">
+        <v>1836.215099897765</v>
+      </c>
+      <c r="E3">
+        <v>-1233.828</v>
+      </c>
+      <c r="F3">
+        <v>17.072</v>
+      </c>
+      <c r="G3">
+        <v>277.7</v>
+      </c>
+      <c r="H3">
+        <v>456.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>335.3</v>
+      </c>
+      <c r="K3">
+        <v>225.5</v>
+      </c>
+      <c r="L3">
+        <v>109.8</v>
+      </c>
+      <c r="M3">
+        <v>0.7801904000000001</v>
+      </c>
+      <c r="N3">
+        <v>109.0198096</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>109.0198096</v>
+      </c>
+      <c r="Q3">
+        <v>334.5198096</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1075616110546698</v>
+      </c>
+      <c r="T3">
+        <v>0.9323836931899795</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>140.7348770248904</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1070119949441231</v>
+      </c>
+      <c r="C4">
+        <v>2077.913672300218</v>
+      </c>
+      <c r="D4">
+        <v>1834.357672300218</v>
+      </c>
+      <c r="E4">
+        <v>-1216.756</v>
+      </c>
+      <c r="F4">
+        <v>34.144</v>
+      </c>
+      <c r="G4">
+        <v>277.7</v>
+      </c>
+      <c r="H4">
+        <v>456.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>335.3</v>
+      </c>
+      <c r="K4">
+        <v>225.5</v>
+      </c>
+      <c r="L4">
+        <v>109.8</v>
+      </c>
+      <c r="M4">
+        <v>1.5603808</v>
+      </c>
+      <c r="N4">
+        <v>108.2396192</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>108.2396192</v>
+      </c>
+      <c r="Q4">
+        <v>333.7396192</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1082632601470644</v>
+      </c>
+      <c r="T4">
+        <v>0.9418978125082446</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0457</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>70.36743851244516</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1070809949441231</v>
+      </c>
+      <c r="C5">
+        <v>2058.987998675629</v>
+      </c>
+      <c r="D5">
+        <v>1832.503998675629</v>
+      </c>
+      <c r="E5">
+        <v>-1199.684</v>
+      </c>
+      <c r="F5">
+        <v>51.216</v>
+      </c>
+      <c r="G5">
+        <v>277.7</v>
+      </c>
+      <c r="H5">
+        <v>456.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>335.3</v>
+      </c>
+      <c r="K5">
+        <v>225.5</v>
+      </c>
+      <c r="L5">
+        <v>109.8</v>
+      </c>
+      <c r="M5">
+        <v>2.3405712</v>
+      </c>
+      <c r="N5">
+        <v>107.4594288</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>107.4594288</v>
+      </c>
+      <c r="Q5">
+        <v>332.9594288</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1089793762310547</v>
+      </c>
+      <c r="T5">
+        <v>0.9516080992351336</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0457</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>46.91162567496345</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1071499949441231</v>
+      </c>
+      <c r="C6">
+        <v>2040.066067654975</v>
+      </c>
+      <c r="D6">
+        <v>1830.654067654975</v>
+      </c>
+      <c r="E6">
+        <v>-1182.612</v>
+      </c>
+      <c r="F6">
+        <v>68.288</v>
+      </c>
+      <c r="G6">
+        <v>277.7</v>
+      </c>
+      <c r="H6">
+        <v>456.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>335.3</v>
+      </c>
+      <c r="K6">
+        <v>225.5</v>
+      </c>
+      <c r="L6">
+        <v>109.8</v>
+      </c>
+      <c r="M6">
+        <v>3.1207616</v>
+      </c>
+      <c r="N6">
+        <v>106.6792384</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>106.6792384</v>
+      </c>
+      <c r="Q6">
+        <v>332.1792384</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1097104114001282</v>
+      </c>
+      <c r="T6">
+        <v>0.9615206836021664</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0457</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>35.18371925622259</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1072189949441231</v>
+      </c>
+      <c r="C7">
+        <v>2021.147867915102</v>
+      </c>
+      <c r="D7">
+        <v>1828.807867915102</v>
+      </c>
+      <c r="E7">
+        <v>-1165.54</v>
+      </c>
+      <c r="F7">
+        <v>85.36000000000001</v>
+      </c>
+      <c r="G7">
+        <v>277.7</v>
+      </c>
+      <c r="H7">
+        <v>456.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>335.3</v>
+      </c>
+      <c r="K7">
+        <v>225.5</v>
+      </c>
+      <c r="L7">
+        <v>109.8</v>
+      </c>
+      <c r="M7">
+        <v>3.900952000000001</v>
+      </c>
+      <c r="N7">
+        <v>105.899048</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>105.899048</v>
+      </c>
+      <c r="Q7">
+        <v>331.399048</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1104568367832875</v>
+      </c>
+      <c r="T7">
+        <v>0.9716419539558733</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0457</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>28.14697540497806</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1072879949441231</v>
+      </c>
+      <c r="C8">
+        <v>2002.233388178484</v>
+      </c>
+      <c r="D8">
+        <v>1826.965388178484</v>
+      </c>
+      <c r="E8">
+        <v>-1148.468</v>
+      </c>
+      <c r="F8">
+        <v>102.432</v>
+      </c>
+      <c r="G8">
+        <v>277.7</v>
+      </c>
+      <c r="H8">
+        <v>456.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>335.3</v>
+      </c>
+      <c r="K8">
+        <v>225.5</v>
+      </c>
+      <c r="L8">
+        <v>109.8</v>
+      </c>
+      <c r="M8">
+        <v>4.681142400000001</v>
+      </c>
+      <c r="N8">
+        <v>105.1188576</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>105.1188576</v>
+      </c>
+      <c r="Q8">
+        <v>330.6188576</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1112191435575778</v>
+      </c>
+      <c r="T8">
+        <v>0.9819785704873187</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.0457</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.45581283748172</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1073569949441231</v>
+      </c>
+      <c r="C9">
+        <v>1983.322617212997</v>
+      </c>
+      <c r="D9">
+        <v>1825.126617212997</v>
+      </c>
+      <c r="E9">
+        <v>-1131.396</v>
+      </c>
+      <c r="F9">
+        <v>119.504</v>
+      </c>
+      <c r="G9">
+        <v>277.7</v>
+      </c>
+      <c r="H9">
+        <v>456.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>335.3</v>
+      </c>
+      <c r="K9">
+        <v>225.5</v>
+      </c>
+      <c r="L9">
+        <v>109.8</v>
+      </c>
+      <c r="M9">
+        <v>5.461332800000001</v>
+      </c>
+      <c r="N9">
+        <v>104.3386672</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>104.3386672</v>
+      </c>
+      <c r="Q9">
+        <v>329.8386672</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1119978440259388</v>
+      </c>
+      <c r="T9">
+        <v>0.9925374798473974</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.0457</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>20.10498243212719</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1074259949441231</v>
+      </c>
+      <c r="C10">
+        <v>1964.415543831689</v>
+      </c>
+      <c r="D10">
+        <v>1823.291543831689</v>
+      </c>
+      <c r="E10">
+        <v>-1114.324</v>
+      </c>
+      <c r="F10">
+        <v>136.576</v>
+      </c>
+      <c r="G10">
+        <v>277.7</v>
+      </c>
+      <c r="H10">
+        <v>456.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>335.3</v>
+      </c>
+      <c r="K10">
+        <v>225.5</v>
+      </c>
+      <c r="L10">
+        <v>109.8</v>
+      </c>
+      <c r="M10">
+        <v>6.2415232</v>
+      </c>
+      <c r="N10">
+        <v>103.5584768</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>103.5584768</v>
+      </c>
+      <c r="Q10">
+        <v>329.0584768</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1127934727653512</v>
+      </c>
+      <c r="T10">
+        <v>1.003325930715304</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.0457</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.59185962811129</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1074949949441231</v>
+      </c>
+      <c r="C11">
+        <v>1945.512156892557</v>
+      </c>
+      <c r="D11">
+        <v>1821.460156892557</v>
+      </c>
+      <c r="E11">
+        <v>-1097.252</v>
+      </c>
+      <c r="F11">
+        <v>153.648</v>
+      </c>
+      <c r="G11">
+        <v>277.7</v>
+      </c>
+      <c r="H11">
+        <v>456.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>335.3</v>
+      </c>
+      <c r="K11">
+        <v>225.5</v>
+      </c>
+      <c r="L11">
+        <v>109.8</v>
+      </c>
+      <c r="M11">
+        <v>7.021713600000001</v>
+      </c>
+      <c r="N11">
+        <v>102.7782864</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>102.7782864</v>
+      </c>
+      <c r="Q11">
+        <v>328.2782864</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1136065878506847</v>
+      </c>
+      <c r="T11">
+        <v>1.014351490393494</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.0457</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.63720855832115</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1075639949441231</v>
+      </c>
+      <c r="C12">
+        <v>1926.612445298318</v>
+      </c>
+      <c r="D12">
+        <v>1819.632445298318</v>
+      </c>
+      <c r="E12">
+        <v>-1080.18</v>
+      </c>
+      <c r="F12">
+        <v>170.72</v>
+      </c>
+      <c r="G12">
+        <v>277.7</v>
+      </c>
+      <c r="H12">
+        <v>456.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>335.3</v>
+      </c>
+      <c r="K12">
+        <v>225.5</v>
+      </c>
+      <c r="L12">
+        <v>109.8</v>
+      </c>
+      <c r="M12">
+        <v>7.801904000000002</v>
+      </c>
+      <c r="N12">
+        <v>101.998096</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>101.998096</v>
+      </c>
+      <c r="Q12">
+        <v>327.498096</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1144377721601368</v>
+      </c>
+      <c r="T12">
+        <v>1.025622062508977</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.0457</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.07348770248903</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1078089949441231</v>
+      </c>
+      <c r="C13">
+        <v>1903.080273700992</v>
+      </c>
+      <c r="D13">
+        <v>1813.172273700992</v>
+      </c>
+      <c r="E13">
+        <v>-1063.108</v>
+      </c>
+      <c r="F13">
+        <v>187.792</v>
+      </c>
+      <c r="G13">
+        <v>277.7</v>
+      </c>
+      <c r="H13">
+        <v>456.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>335.3</v>
+      </c>
+      <c r="K13">
+        <v>225.5</v>
+      </c>
+      <c r="L13">
+        <v>109.8</v>
+      </c>
+      <c r="M13">
+        <v>8.882561600000001</v>
+      </c>
+      <c r="N13">
+        <v>100.9174384</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>100.9174384</v>
+      </c>
+      <c r="Q13">
+        <v>326.4174384</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1152876347686776</v>
+      </c>
+      <c r="T13">
+        <v>1.037145905907955</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.0473</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>12.36129901986832</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1078939949441231</v>
+      </c>
+      <c r="C14">
+        <v>1883.777694279593</v>
+      </c>
+      <c r="D14">
+        <v>1810.941694279593</v>
+      </c>
+      <c r="E14">
+        <v>-1046.036</v>
+      </c>
+      <c r="F14">
+        <v>204.864</v>
+      </c>
+      <c r="G14">
+        <v>277.7</v>
+      </c>
+      <c r="H14">
+        <v>456.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>335.3</v>
+      </c>
+      <c r="K14">
+        <v>225.5</v>
+      </c>
+      <c r="L14">
+        <v>109.8</v>
+      </c>
+      <c r="M14">
+        <v>9.690067200000001</v>
+      </c>
+      <c r="N14">
+        <v>100.1099328</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>100.1099328</v>
+      </c>
+      <c r="Q14">
+        <v>325.6099328</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1161568124365035</v>
+      </c>
+      <c r="T14">
+        <v>1.048931654838727</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.0473</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.33119076821263</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1079789949441231</v>
+      </c>
+      <c r="C15">
+        <v>1864.480596269162</v>
+      </c>
+      <c r="D15">
+        <v>1808.716596269162</v>
+      </c>
+      <c r="E15">
+        <v>-1028.964</v>
+      </c>
+      <c r="F15">
+        <v>221.936</v>
+      </c>
+      <c r="G15">
+        <v>277.7</v>
+      </c>
+      <c r="H15">
+        <v>456.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>335.3</v>
+      </c>
+      <c r="K15">
+        <v>225.5</v>
+      </c>
+      <c r="L15">
+        <v>109.8</v>
+      </c>
+      <c r="M15">
+        <v>10.4975728</v>
+      </c>
+      <c r="N15">
+        <v>99.30242720000001</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>99.30242720000001</v>
+      </c>
+      <c r="Q15">
+        <v>324.8024272</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1170459712001415</v>
+      </c>
+      <c r="T15">
+        <v>1.060988340526528</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.0473</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.45956070911935</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1085959949441231</v>
+      </c>
+      <c r="C16">
+        <v>1831.419453327773</v>
+      </c>
+      <c r="D16">
+        <v>1792.727453327773</v>
+      </c>
+      <c r="E16">
+        <v>-1011.892</v>
+      </c>
+      <c r="F16">
+        <v>239.008</v>
+      </c>
+      <c r="G16">
+        <v>277.7</v>
+      </c>
+      <c r="H16">
+        <v>456.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>335.3</v>
+      </c>
+      <c r="K16">
+        <v>225.5</v>
+      </c>
+      <c r="L16">
+        <v>109.8</v>
+      </c>
+      <c r="M16">
+        <v>12.2133088</v>
+      </c>
+      <c r="N16">
+        <v>97.5866912</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>97.5866912</v>
+      </c>
+      <c r="Q16">
+        <v>323.0866912</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1179558080745617</v>
+      </c>
+      <c r="T16">
+        <v>1.073325414253581</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.0511</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.990192731391513</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1087189949441231</v>
+      </c>
+      <c r="C17">
+        <v>1811.193725546995</v>
+      </c>
+      <c r="D17">
+        <v>1789.573725546995</v>
+      </c>
+      <c r="E17">
+        <v>-994.8200000000002</v>
+      </c>
+      <c r="F17">
+        <v>256.08</v>
+      </c>
+      <c r="G17">
+        <v>277.7</v>
+      </c>
+      <c r="H17">
+        <v>456.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>335.3</v>
+      </c>
+      <c r="K17">
+        <v>225.5</v>
+      </c>
+      <c r="L17">
+        <v>109.8</v>
+      </c>
+      <c r="M17">
+        <v>13.085688</v>
+      </c>
+      <c r="N17">
+        <v>96.71431200000001</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>96.71431200000001</v>
+      </c>
+      <c r="Q17">
+        <v>322.214312</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1188870528754389</v>
+      </c>
+      <c r="T17">
+        <v>1.085952772068329</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.0511</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.390846549298747</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1088419949441231</v>
+      </c>
+      <c r="C18">
+        <v>1790.979074221631</v>
+      </c>
+      <c r="D18">
+        <v>1786.431074221632</v>
+      </c>
+      <c r="E18">
+        <v>-977.748</v>
+      </c>
+      <c r="F18">
+        <v>273.152</v>
+      </c>
+      <c r="G18">
+        <v>277.7</v>
+      </c>
+      <c r="H18">
+        <v>456.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>335.3</v>
+      </c>
+      <c r="K18">
+        <v>225.5</v>
+      </c>
+      <c r="L18">
+        <v>109.8</v>
+      </c>
+      <c r="M18">
+        <v>13.9580672</v>
+      </c>
+      <c r="N18">
+        <v>95.84193280000001</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>95.84193280000001</v>
+      </c>
+      <c r="Q18">
+        <v>321.3419328</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1198404701715751</v>
+      </c>
+      <c r="T18">
+        <v>1.098880781259619</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.0511</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.866418639967575</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1092879949441231</v>
+      </c>
+      <c r="C19">
+        <v>1762.603755695768</v>
+      </c>
+      <c r="D19">
+        <v>1775.127755695768</v>
+      </c>
+      <c r="E19">
+        <v>-960.676</v>
+      </c>
+      <c r="F19">
+        <v>290.224</v>
+      </c>
+      <c r="G19">
+        <v>277.7</v>
+      </c>
+      <c r="H19">
+        <v>456.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>335.3</v>
+      </c>
+      <c r="K19">
+        <v>225.5</v>
+      </c>
+      <c r="L19">
+        <v>109.8</v>
+      </c>
+      <c r="M19">
+        <v>15.381872</v>
+      </c>
+      <c r="N19">
+        <v>94.41812800000001</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>94.41812800000001</v>
+      </c>
+      <c r="Q19">
+        <v>319.918128</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1208168613784616</v>
+      </c>
+      <c r="T19">
+        <v>1.112120308744674</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.138272896822961</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1094299949441231</v>
+      </c>
+      <c r="C20">
+        <v>1741.962901676902</v>
+      </c>
+      <c r="D20">
+        <v>1771.558901676903</v>
+      </c>
+      <c r="E20">
+        <v>-943.604</v>
+      </c>
+      <c r="F20">
+        <v>307.296</v>
+      </c>
+      <c r="G20">
+        <v>277.7</v>
+      </c>
+      <c r="H20">
+        <v>456.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>335.3</v>
+      </c>
+      <c r="K20">
+        <v>225.5</v>
+      </c>
+      <c r="L20">
+        <v>109.8</v>
+      </c>
+      <c r="M20">
+        <v>16.286688</v>
+      </c>
+      <c r="N20">
+        <v>93.51331200000001</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>93.51331200000001</v>
+      </c>
+      <c r="Q20">
+        <v>319.013312</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1218170670050281</v>
+      </c>
+      <c r="T20">
+        <v>1.125682751534243</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.741702180332797</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1095719949441231</v>
+      </c>
+      <c r="C21">
+        <v>1721.336369065003</v>
+      </c>
+      <c r="D21">
+        <v>1768.004369065003</v>
+      </c>
+      <c r="E21">
+        <v>-926.5320000000002</v>
+      </c>
+      <c r="F21">
+        <v>324.368</v>
+      </c>
+      <c r="G21">
+        <v>277.7</v>
+      </c>
+      <c r="H21">
+        <v>456.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>335.3</v>
+      </c>
+      <c r="K21">
+        <v>225.5</v>
+      </c>
+      <c r="L21">
+        <v>109.8</v>
+      </c>
+      <c r="M21">
+        <v>17.191504</v>
+      </c>
+      <c r="N21">
+        <v>92.608496</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>92.608496</v>
+      </c>
+      <c r="Q21">
+        <v>318.108496</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1228419690668186</v>
+      </c>
+      <c r="T21">
+        <v>1.139580069454419</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.386875749788965</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1101139949441231</v>
+      </c>
+      <c r="C22">
+        <v>1690.827197738616</v>
+      </c>
+      <c r="D22">
+        <v>1754.567197738616</v>
+      </c>
+      <c r="E22">
+        <v>-909.46</v>
+      </c>
+      <c r="F22">
+        <v>341.4400000000001</v>
+      </c>
+      <c r="G22">
+        <v>277.7</v>
+      </c>
+      <c r="H22">
+        <v>456.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>335.3</v>
+      </c>
+      <c r="K22">
+        <v>225.5</v>
+      </c>
+      <c r="L22">
+        <v>109.8</v>
+      </c>
+      <c r="M22">
+        <v>18.7792</v>
+      </c>
+      <c r="N22">
+        <v>91.02080000000001</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>91.02080000000001</v>
+      </c>
+      <c r="Q22">
+        <v>316.5208</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1238924936801539</v>
+      </c>
+      <c r="T22">
+        <v>1.1538248203226</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.055</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.846894436397716</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1102759949441231</v>
+      </c>
+      <c r="C23">
+        <v>1669.778479593512</v>
+      </c>
+      <c r="D23">
+        <v>1750.590479593512</v>
+      </c>
+      <c r="E23">
+        <v>-892.3880000000001</v>
+      </c>
+      <c r="F23">
+        <v>358.512</v>
+      </c>
+      <c r="G23">
+        <v>277.7</v>
+      </c>
+      <c r="H23">
+        <v>456.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>335.3</v>
+      </c>
+      <c r="K23">
+        <v>225.5</v>
+      </c>
+      <c r="L23">
+        <v>109.8</v>
+      </c>
+      <c r="M23">
+        <v>19.71816</v>
+      </c>
+      <c r="N23">
+        <v>90.08184000000001</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>90.08184000000001</v>
+      </c>
+      <c r="Q23">
+        <v>315.58184</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1249696138533204</v>
+      </c>
+      <c r="T23">
+        <v>1.168430197795038</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.055</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.568470891807349</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1104379949441231</v>
+      </c>
+      <c r="C24">
+        <v>1648.74774710923</v>
+      </c>
+      <c r="D24">
+        <v>1746.63174710923</v>
+      </c>
+      <c r="E24">
+        <v>-875.316</v>
+      </c>
+      <c r="F24">
+        <v>375.584</v>
+      </c>
+      <c r="G24">
+        <v>277.7</v>
+      </c>
+      <c r="H24">
+        <v>456.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>335.3</v>
+      </c>
+      <c r="K24">
+        <v>225.5</v>
+      </c>
+      <c r="L24">
+        <v>109.8</v>
+      </c>
+      <c r="M24">
+        <v>20.65712</v>
+      </c>
+      <c r="N24">
+        <v>89.14288000000002</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>89.14288000000002</v>
+      </c>
+      <c r="Q24">
+        <v>314.64288</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1260743524924655</v>
+      </c>
+      <c r="T24">
+        <v>1.183410072125743</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.055</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.31535857854338</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1105999949441231</v>
+      </c>
+      <c r="C25">
+        <v>1627.73487854438</v>
+      </c>
+      <c r="D25">
+        <v>1742.69087854438</v>
+      </c>
+      <c r="E25">
+        <v>-858.2440000000001</v>
+      </c>
+      <c r="F25">
+        <v>392.656</v>
+      </c>
+      <c r="G25">
+        <v>277.7</v>
+      </c>
+      <c r="H25">
+        <v>456.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>335.3</v>
+      </c>
+      <c r="K25">
+        <v>225.5</v>
+      </c>
+      <c r="L25">
+        <v>109.8</v>
+      </c>
+      <c r="M25">
+        <v>21.59608</v>
+      </c>
+      <c r="N25">
+        <v>88.20392000000001</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>88.20392000000001</v>
+      </c>
+      <c r="Q25">
+        <v>313.70392</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1272077856417183</v>
+      </c>
+      <c r="T25">
+        <v>1.198779034101402</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.055</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.084256031650189</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1107619949441231</v>
+      </c>
+      <c r="C26">
+        <v>1606.739753253823</v>
+      </c>
+      <c r="D26">
+        <v>1738.767753253823</v>
+      </c>
+      <c r="E26">
+        <v>-841.172</v>
+      </c>
+      <c r="F26">
+        <v>409.728</v>
+      </c>
+      <c r="G26">
+        <v>277.7</v>
+      </c>
+      <c r="H26">
+        <v>456.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>335.3</v>
+      </c>
+      <c r="K26">
+        <v>225.5</v>
+      </c>
+      <c r="L26">
+        <v>109.8</v>
+      </c>
+      <c r="M26">
+        <v>22.53504</v>
+      </c>
+      <c r="N26">
+        <v>87.26496</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>87.26496</v>
+      </c>
+      <c r="Q26">
+        <v>312.76496</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1283710459791093</v>
+      </c>
+      <c r="T26">
+        <v>1.214552442444842</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.055</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.87241203033143</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1109239949441231</v>
+      </c>
+      <c r="C27">
+        <v>1585.762251676361</v>
+      </c>
+      <c r="D27">
+        <v>1734.862251676361</v>
+      </c>
+      <c r="E27">
+        <v>-824.1000000000001</v>
+      </c>
+      <c r="F27">
+        <v>426.8</v>
+      </c>
+      <c r="G27">
+        <v>277.7</v>
+      </c>
+      <c r="H27">
+        <v>456.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>335.3</v>
+      </c>
+      <c r="K27">
+        <v>225.5</v>
+      </c>
+      <c r="L27">
+        <v>109.8</v>
+      </c>
+      <c r="M27">
+        <v>23.474</v>
+      </c>
+      <c r="N27">
+        <v>86.32600000000001</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>86.32600000000001</v>
+      </c>
+      <c r="Q27">
+        <v>311.826</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1295653265921641</v>
+      </c>
+      <c r="T27">
+        <v>1.230746475010773</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.055</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.677515549118174</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1120739949441231</v>
+      </c>
+      <c r="C28">
+        <v>1541.462425611341</v>
+      </c>
+      <c r="D28">
+        <v>1707.634425611341</v>
+      </c>
+      <c r="E28">
+        <v>-807.028</v>
+      </c>
+      <c r="F28">
+        <v>443.872</v>
+      </c>
+      <c r="G28">
+        <v>277.7</v>
+      </c>
+      <c r="H28">
+        <v>456.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>335.3</v>
+      </c>
+      <c r="K28">
+        <v>225.5</v>
+      </c>
+      <c r="L28">
+        <v>109.8</v>
+      </c>
+      <c r="M28">
+        <v>26.0996736</v>
+      </c>
+      <c r="N28">
+        <v>83.70032640000001</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>83.70032640000001</v>
+      </c>
+      <c r="Q28">
+        <v>309.2003264</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1307918850596258</v>
+      </c>
+      <c r="T28">
+        <v>1.24737818413254</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.206949162766541</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1122739949441231</v>
+      </c>
+      <c r="C29">
+        <v>1519.742156718625</v>
+      </c>
+      <c r="D29">
+        <v>1702.986156718625</v>
+      </c>
+      <c r="E29">
+        <v>-789.9560000000001</v>
+      </c>
+      <c r="F29">
+        <v>460.944</v>
+      </c>
+      <c r="G29">
+        <v>277.7</v>
+      </c>
+      <c r="H29">
+        <v>456.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>335.3</v>
+      </c>
+      <c r="K29">
+        <v>225.5</v>
+      </c>
+      <c r="L29">
+        <v>109.8</v>
+      </c>
+      <c r="M29">
+        <v>27.1035072</v>
+      </c>
+      <c r="N29">
+        <v>82.69649280000002</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>82.69649280000002</v>
+      </c>
+      <c r="Q29">
+        <v>308.1964928</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1320520478686618</v>
+      </c>
+      <c r="T29">
+        <v>1.264465556517917</v>
+      </c>
+      <c r="U29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.051136230812226</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1136499949441231</v>
+      </c>
+      <c r="C30">
+        <v>1471.36342178305</v>
+      </c>
+      <c r="D30">
+        <v>1671.67942178305</v>
+      </c>
+      <c r="E30">
+        <v>-772.884</v>
+      </c>
+      <c r="F30">
+        <v>478.0160000000001</v>
+      </c>
+      <c r="G30">
+        <v>277.7</v>
+      </c>
+      <c r="H30">
+        <v>456.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>335.3</v>
+      </c>
+      <c r="K30">
+        <v>225.5</v>
+      </c>
+      <c r="L30">
+        <v>109.8</v>
+      </c>
+      <c r="M30">
+        <v>30.11500800000001</v>
+      </c>
+      <c r="N30">
+        <v>79.68499200000001</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>79.68499200000001</v>
+      </c>
+      <c r="Q30">
+        <v>305.184992</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.133347215200171</v>
+      </c>
+      <c r="T30">
+        <v>1.282027578136222</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.063</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.646022607731002</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1138919949441231</v>
+      </c>
+      <c r="C31">
+        <v>1448.904077627758</v>
+      </c>
+      <c r="D31">
+        <v>1666.292077627758</v>
+      </c>
+      <c r="E31">
+        <v>-755.8120000000001</v>
+      </c>
+      <c r="F31">
+        <v>495.088</v>
+      </c>
+      <c r="G31">
+        <v>277.7</v>
+      </c>
+      <c r="H31">
+        <v>456.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>335.3</v>
+      </c>
+      <c r="K31">
+        <v>225.5</v>
+      </c>
+      <c r="L31">
+        <v>109.8</v>
+      </c>
+      <c r="M31">
+        <v>31.190544</v>
+      </c>
+      <c r="N31">
+        <v>78.60945600000001</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>78.60945600000001</v>
+      </c>
+      <c r="Q31">
+        <v>304.109456</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1346788661184832</v>
+      </c>
+      <c r="T31">
+        <v>1.300084304588844</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.063</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.520297690223037</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1162639949441231</v>
+      </c>
+      <c r="C32">
+        <v>1380.809085449468</v>
+      </c>
+      <c r="D32">
+        <v>1615.269085449468</v>
+      </c>
+      <c r="E32">
+        <v>-738.7400000000001</v>
+      </c>
+      <c r="F32">
+        <v>512.16</v>
+      </c>
+      <c r="G32">
+        <v>277.7</v>
+      </c>
+      <c r="H32">
+        <v>456.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>335.3</v>
+      </c>
+      <c r="K32">
+        <v>225.5</v>
+      </c>
+      <c r="L32">
+        <v>109.8</v>
+      </c>
+      <c r="M32">
+        <v>35.902416</v>
+      </c>
+      <c r="N32">
+        <v>73.89758400000002</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>73.89758400000002</v>
+      </c>
+      <c r="Q32">
+        <v>299.3975840000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1360485642058901</v>
+      </c>
+      <c r="T32">
+        <v>1.318656937511542</v>
+      </c>
+      <c r="U32">
+        <v>0.0701</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.0701</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.058290004772939</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1231799949441231</v>
+      </c>
+      <c r="C33">
+        <v>1231.345503743802</v>
+      </c>
+      <c r="D33">
+        <v>1482.877503743802</v>
+      </c>
+      <c r="E33">
+        <v>-721.6680000000001</v>
+      </c>
+      <c r="F33">
+        <v>529.232</v>
+      </c>
+      <c r="G33">
+        <v>277.7</v>
+      </c>
+      <c r="H33">
+        <v>456.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>335.3</v>
+      </c>
+      <c r="K33">
+        <v>225.5</v>
+      </c>
+      <c r="L33">
+        <v>109.8</v>
+      </c>
+      <c r="M33">
+        <v>48.3718048</v>
+      </c>
+      <c r="N33">
+        <v>61.42819520000001</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>61.42819520000001</v>
+      </c>
+      <c r="Q33">
+        <v>286.9281952</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1374579636871349</v>
+      </c>
+      <c r="T33">
+        <v>1.337767907620405</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.269917371369199</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1237059949441231</v>
+      </c>
+      <c r="C34">
+        <v>1205.086949043129</v>
+      </c>
+      <c r="D34">
+        <v>1473.690949043129</v>
+      </c>
+      <c r="E34">
+        <v>-704.5960000000001</v>
+      </c>
+      <c r="F34">
+        <v>546.304</v>
+      </c>
+      <c r="G34">
+        <v>277.7</v>
+      </c>
+      <c r="H34">
+        <v>456.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>335.3</v>
+      </c>
+      <c r="K34">
+        <v>225.5</v>
+      </c>
+      <c r="L34">
+        <v>109.8</v>
+      </c>
+      <c r="M34">
+        <v>49.9321856</v>
+      </c>
+      <c r="N34">
+        <v>59.86781440000001</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>59.86781440000001</v>
+      </c>
+      <c r="Q34">
+        <v>285.3678144</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1389088160942987</v>
+      </c>
+      <c r="T34">
+        <v>1.357440965085411</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.198982453513912</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1242319949441231</v>
+      </c>
+      <c r="C35">
+        <v>1178.94151654628</v>
+      </c>
+      <c r="D35">
+        <v>1464.61751654628</v>
+      </c>
+      <c r="E35">
+        <v>-687.524</v>
+      </c>
+      <c r="F35">
+        <v>563.3760000000001</v>
+      </c>
+      <c r="G35">
+        <v>277.7</v>
+      </c>
+      <c r="H35">
+        <v>456.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>335.3</v>
+      </c>
+      <c r="K35">
+        <v>225.5</v>
+      </c>
+      <c r="L35">
+        <v>109.8</v>
+      </c>
+      <c r="M35">
+        <v>51.49256640000002</v>
+      </c>
+      <c r="N35">
+        <v>58.3074336</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>58.3074336</v>
+      </c>
+      <c r="Q35">
+        <v>283.8074336</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1404029775285419</v>
+      </c>
+      <c r="T35">
+        <v>1.377701277997134</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.132346621589247</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1247579949441231</v>
+      </c>
+      <c r="C36">
+        <v>1152.907129578039</v>
+      </c>
+      <c r="D36">
+        <v>1455.655129578039</v>
+      </c>
+      <c r="E36">
+        <v>-670.452</v>
+      </c>
+      <c r="F36">
+        <v>580.4480000000001</v>
+      </c>
+      <c r="G36">
+        <v>277.7</v>
+      </c>
+      <c r="H36">
+        <v>456.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>335.3</v>
+      </c>
+      <c r="K36">
+        <v>225.5</v>
+      </c>
+      <c r="L36">
+        <v>109.8</v>
+      </c>
+      <c r="M36">
+        <v>53.05294720000001</v>
+      </c>
+      <c r="N36">
+        <v>56.7470528</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>56.7470528</v>
+      </c>
+      <c r="Q36">
+        <v>282.2470528</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1419424165820047</v>
+      </c>
+      <c r="T36">
+        <v>1.398575539784969</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.069630544483681</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1252839949441231</v>
+      </c>
+      <c r="C37">
+        <v>1126.981761984963</v>
+      </c>
+      <c r="D37">
+        <v>1446.801761984963</v>
+      </c>
+      <c r="E37">
+        <v>-653.38</v>
+      </c>
+      <c r="F37">
+        <v>597.5200000000001</v>
+      </c>
+      <c r="G37">
+        <v>277.7</v>
+      </c>
+      <c r="H37">
+        <v>456.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>335.3</v>
+      </c>
+      <c r="K37">
+        <v>225.5</v>
+      </c>
+      <c r="L37">
+        <v>109.8</v>
+      </c>
+      <c r="M37">
+        <v>54.61332800000002</v>
+      </c>
+      <c r="N37">
+        <v>55.18667199999999</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>55.18667199999999</v>
+      </c>
+      <c r="Q37">
+        <v>280.686672</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1435292229909586</v>
+      </c>
+      <c r="T37">
+        <v>1.420092086550892</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.010498243212719</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1334059949441231</v>
+      </c>
+      <c r="C38">
+        <v>985.7006786411188</v>
+      </c>
+      <c r="D38">
+        <v>1322.592678641119</v>
+      </c>
+      <c r="E38">
+        <v>-636.3080000000001</v>
+      </c>
+      <c r="F38">
+        <v>614.592</v>
+      </c>
+      <c r="G38">
+        <v>277.7</v>
+      </c>
+      <c r="H38">
+        <v>456.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>335.3</v>
+      </c>
+      <c r="K38">
+        <v>225.5</v>
+      </c>
+      <c r="L38">
+        <v>109.8</v>
+      </c>
+      <c r="M38">
+        <v>69.1416</v>
+      </c>
+      <c r="N38">
+        <v>40.65840000000001</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>40.65840000000001</v>
+      </c>
+      <c r="Q38">
+        <v>266.1584</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1451656171001923</v>
+      </c>
+      <c r="T38">
+        <v>1.442281025403249</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.1125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.588045402478393</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1341429949441231</v>
+      </c>
+      <c r="C39">
+        <v>958.4050559750824</v>
+      </c>
+      <c r="D39">
+        <v>1312.369055975082</v>
+      </c>
+      <c r="E39">
+        <v>-619.2360000000001</v>
+      </c>
+      <c r="F39">
+        <v>631.664</v>
+      </c>
+      <c r="G39">
+        <v>277.7</v>
+      </c>
+      <c r="H39">
+        <v>456.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>335.3</v>
+      </c>
+      <c r="K39">
+        <v>225.5</v>
+      </c>
+      <c r="L39">
+        <v>109.8</v>
+      </c>
+      <c r="M39">
+        <v>71.0622</v>
+      </c>
+      <c r="N39">
+        <v>38.73780000000001</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>38.73780000000001</v>
+      </c>
+      <c r="Q39">
+        <v>264.2378</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1468539602287668</v>
+      </c>
+      <c r="T39">
+        <v>1.465174375012825</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.1125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.545125256465463</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1348799949441231</v>
+      </c>
+      <c r="C40">
+        <v>931.2662778198993</v>
+      </c>
+      <c r="D40">
+        <v>1302.302277819899</v>
+      </c>
+      <c r="E40">
+        <v>-602.1640000000001</v>
+      </c>
+      <c r="F40">
+        <v>648.736</v>
+      </c>
+      <c r="G40">
+        <v>277.7</v>
+      </c>
+      <c r="H40">
+        <v>456.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>335.3</v>
+      </c>
+      <c r="K40">
+        <v>225.5</v>
+      </c>
+      <c r="L40">
+        <v>109.8</v>
+      </c>
+      <c r="M40">
+        <v>72.9828</v>
+      </c>
+      <c r="N40">
+        <v>36.81720000000001</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>36.81720000000001</v>
+      </c>
+      <c r="Q40">
+        <v>262.3172</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1485967660389082</v>
+      </c>
+      <c r="T40">
+        <v>1.488806219771096</v>
+      </c>
+      <c r="U40">
+        <v>0.1125</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.1125</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.504464065505845</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1684159949441231</v>
+      </c>
+      <c r="C41">
+        <v>577.2450517016578</v>
+      </c>
+      <c r="D41">
+        <v>965.3530517016577</v>
+      </c>
+      <c r="E41">
+        <v>-585.0920000000001</v>
+      </c>
+      <c r="F41">
+        <v>665.808</v>
+      </c>
+      <c r="G41">
+        <v>277.7</v>
+      </c>
+      <c r="H41">
+        <v>456.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>335.3</v>
+      </c>
+      <c r="K41">
+        <v>225.5</v>
+      </c>
+      <c r="L41">
+        <v>109.8</v>
+      </c>
+      <c r="M41">
+        <v>130.8978528</v>
+      </c>
+      <c r="N41">
+        <v>-21.0978528</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-21.0978528</v>
+      </c>
+      <c r="Q41">
+        <v>204.4021472</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1503967130231526</v>
+      </c>
+      <c r="T41">
+        <v>1.513212879111606</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.1966</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8388220100734914</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1699939949441231</v>
+      </c>
+      <c r="C42">
+        <v>548.5617952852797</v>
+      </c>
+      <c r="D42">
+        <v>953.7417952852799</v>
+      </c>
+      <c r="E42">
+        <v>-568.02</v>
+      </c>
+      <c r="F42">
+        <v>682.8800000000001</v>
+      </c>
+      <c r="G42">
+        <v>277.7</v>
+      </c>
+      <c r="H42">
+        <v>456.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>335.3</v>
+      </c>
+      <c r="K42">
+        <v>225.5</v>
+      </c>
+      <c r="L42">
+        <v>109.8</v>
+      </c>
+      <c r="M42">
+        <v>134.254208</v>
+      </c>
+      <c r="N42">
+        <v>-24.45420799999999</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-24.45420799999999</v>
+      </c>
+      <c r="Q42">
+        <v>201.045792</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1522566582402052</v>
+      </c>
+      <c r="T42">
+        <v>1.538433093763466</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.1966</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8178514598216542</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1786239949441231</v>
+      </c>
+      <c r="C43">
+        <v>472.6244217376196</v>
+      </c>
+      <c r="D43">
+        <v>894.8764217376198</v>
+      </c>
+      <c r="E43">
+        <v>-550.948</v>
+      </c>
+      <c r="F43">
+        <v>699.9520000000001</v>
+      </c>
+      <c r="G43">
+        <v>277.7</v>
+      </c>
+      <c r="H43">
+        <v>456.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>335.3</v>
+      </c>
+      <c r="K43">
+        <v>225.5</v>
+      </c>
+      <c r="L43">
+        <v>109.8</v>
+      </c>
+      <c r="M43">
+        <v>149.6497376</v>
+      </c>
+      <c r="N43">
+        <v>-39.8497376</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-39.8497376</v>
+      </c>
+      <c r="Q43">
+        <v>185.6502624</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1541796524476662</v>
+      </c>
+      <c r="T43">
+        <v>1.564508230945898</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2138</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7337132811651519</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1803739949441231</v>
+      </c>
+      <c r="C44">
+        <v>444.4908299625278</v>
+      </c>
+      <c r="D44">
+        <v>883.8148299625277</v>
+      </c>
+      <c r="E44">
+        <v>-533.8760000000001</v>
+      </c>
+      <c r="F44">
+        <v>717.024</v>
+      </c>
+      <c r="G44">
+        <v>277.7</v>
+      </c>
+      <c r="H44">
+        <v>456.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>335.3</v>
+      </c>
+      <c r="K44">
+        <v>225.5</v>
+      </c>
+      <c r="L44">
+        <v>109.8</v>
+      </c>
+      <c r="M44">
+        <v>153.2997312</v>
+      </c>
+      <c r="N44">
+        <v>-43.49973119999999</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-43.49973119999999</v>
+      </c>
+      <c r="Q44">
+        <v>182.0002688</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1561689568002122</v>
+      </c>
+      <c r="T44">
+        <v>1.591482510789792</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2138</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.7162439173278865</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1821239949441231</v>
+      </c>
+      <c r="C45">
+        <v>416.6273644229479</v>
+      </c>
+      <c r="D45">
+        <v>873.0233644229479</v>
+      </c>
+      <c r="E45">
+        <v>-516.8040000000001</v>
+      </c>
+      <c r="F45">
+        <v>734.096</v>
+      </c>
+      <c r="G45">
+        <v>277.7</v>
+      </c>
+      <c r="H45">
+        <v>456.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>335.3</v>
+      </c>
+      <c r="K45">
+        <v>225.5</v>
+      </c>
+      <c r="L45">
+        <v>109.8</v>
+      </c>
+      <c r="M45">
+        <v>156.9497248</v>
+      </c>
+      <c r="N45">
+        <v>-47.14972479999997</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-47.14972479999997</v>
+      </c>
+      <c r="Q45">
+        <v>178.3502752</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1582280613054791</v>
+      </c>
+      <c r="T45">
+        <v>1.619403256593122</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2138</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6995870820411915</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1838739949441231</v>
+      </c>
+      <c r="C46">
+        <v>389.0242496747213</v>
+      </c>
+      <c r="D46">
+        <v>862.4922496747214</v>
+      </c>
+      <c r="E46">
+        <v>-499.7320000000001</v>
+      </c>
+      <c r="F46">
+        <v>751.168</v>
+      </c>
+      <c r="G46">
+        <v>277.7</v>
+      </c>
+      <c r="H46">
+        <v>456.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>335.3</v>
+      </c>
+      <c r="K46">
+        <v>225.5</v>
+      </c>
+      <c r="L46">
+        <v>109.8</v>
+      </c>
+      <c r="M46">
+        <v>160.5997184</v>
+      </c>
+      <c r="N46">
+        <v>-50.79971839999999</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-50.79971839999999</v>
+      </c>
+      <c r="Q46">
+        <v>174.7002816</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1603607052573626</v>
+      </c>
+      <c r="T46">
+        <v>1.648321171889428</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2138</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6836873756311643</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1856239949441231</v>
+      </c>
+      <c r="C47">
+        <v>361.6721763290452</v>
+      </c>
+      <c r="D47">
+        <v>852.2121763290453</v>
+      </c>
+      <c r="E47">
+        <v>-482.6600000000001</v>
+      </c>
+      <c r="F47">
+        <v>768.24</v>
+      </c>
+      <c r="G47">
+        <v>277.7</v>
+      </c>
+      <c r="H47">
+        <v>456.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>335.3</v>
+      </c>
+      <c r="K47">
+        <v>225.5</v>
+      </c>
+      <c r="L47">
+        <v>109.8</v>
+      </c>
+      <c r="M47">
+        <v>164.249712</v>
+      </c>
+      <c r="N47">
+        <v>-54.44971199999998</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-54.44971199999998</v>
+      </c>
+      <c r="Q47">
+        <v>171.050288</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1625708998984056</v>
+      </c>
+      <c r="T47">
+        <v>1.678290647741963</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2138</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6684943228393607</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1873739949441231</v>
+      </c>
+      <c r="C48">
+        <v>334.5622736049735</v>
+      </c>
+      <c r="D48">
+        <v>842.1742736049736</v>
+      </c>
+      <c r="E48">
+        <v>-465.5880000000001</v>
+      </c>
+      <c r="F48">
+        <v>785.312</v>
+      </c>
+      <c r="G48">
+        <v>277.7</v>
+      </c>
+      <c r="H48">
+        <v>456.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>335.3</v>
+      </c>
+      <c r="K48">
+        <v>225.5</v>
+      </c>
+      <c r="L48">
+        <v>109.8</v>
+      </c>
+      <c r="M48">
+        <v>167.8997056</v>
+      </c>
+      <c r="N48">
+        <v>-58.09970559999999</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-58.09970559999999</v>
+      </c>
+      <c r="Q48">
+        <v>167.4002944</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1648629536002279</v>
+      </c>
+      <c r="T48">
+        <v>1.709370104181629</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2138</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6539618375602441</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1891239949441231</v>
+      </c>
+      <c r="C49">
+        <v>307.6860837991044</v>
+      </c>
+      <c r="D49">
+        <v>832.3700837991045</v>
+      </c>
+      <c r="E49">
+        <v>-448.5160000000001</v>
+      </c>
+      <c r="F49">
+        <v>802.384</v>
+      </c>
+      <c r="G49">
+        <v>277.7</v>
+      </c>
+      <c r="H49">
+        <v>456.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>335.3</v>
+      </c>
+      <c r="K49">
+        <v>225.5</v>
+      </c>
+      <c r="L49">
+        <v>109.8</v>
+      </c>
+      <c r="M49">
+        <v>171.5496992</v>
+      </c>
+      <c r="N49">
+        <v>-61.74969919999998</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-61.74969919999998</v>
+      </c>
+      <c r="Q49">
+        <v>163.7503008</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1672414998945718</v>
+      </c>
+      <c r="T49">
+        <v>1.741622370298263</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2138</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6400477559100262</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1908739949441231</v>
+      </c>
+      <c r="C50">
+        <v>281.0355385180152</v>
+      </c>
+      <c r="D50">
+        <v>822.7915385180152</v>
+      </c>
+      <c r="E50">
+        <v>-431.4440000000001</v>
+      </c>
+      <c r="F50">
+        <v>819.456</v>
+      </c>
+      <c r="G50">
+        <v>277.7</v>
+      </c>
+      <c r="H50">
+        <v>456.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>335.3</v>
+      </c>
+      <c r="K50">
+        <v>225.5</v>
+      </c>
+      <c r="L50">
+        <v>109.8</v>
+      </c>
+      <c r="M50">
+        <v>175.1996928</v>
+      </c>
+      <c r="N50">
+        <v>-65.3996928</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-65.3996928</v>
+      </c>
+      <c r="Q50">
+        <v>160.1003072</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1697115287386982</v>
+      </c>
+      <c r="T50">
+        <v>1.775115108188615</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2138</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6267134276619006</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1926239949441231</v>
+      </c>
+      <c r="C51">
+        <v>254.6029365330673</v>
+      </c>
+      <c r="D51">
+        <v>813.4309365330674</v>
+      </c>
+      <c r="E51">
+        <v>-414.3720000000001</v>
+      </c>
+      <c r="F51">
+        <v>836.528</v>
+      </c>
+      <c r="G51">
+        <v>277.7</v>
+      </c>
+      <c r="H51">
+        <v>456.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>335.3</v>
+      </c>
+      <c r="K51">
+        <v>225.5</v>
+      </c>
+      <c r="L51">
+        <v>109.8</v>
+      </c>
+      <c r="M51">
+        <v>178.8496864</v>
+      </c>
+      <c r="N51">
+        <v>-69.04968639999998</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-69.04968639999998</v>
+      </c>
+      <c r="Q51">
+        <v>156.4503136</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1722784214590649</v>
+      </c>
+      <c r="T51">
+        <v>1.809921286780548</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2138</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6139233577096169</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1943739949441231</v>
+      </c>
+      <c r="C52">
+        <v>228.3809231298368</v>
+      </c>
+      <c r="D52">
+        <v>804.2809231298369</v>
+      </c>
+      <c r="E52">
+        <v>-397.3000000000001</v>
+      </c>
+      <c r="F52">
+        <v>853.6</v>
+      </c>
+      <c r="G52">
+        <v>277.7</v>
+      </c>
+      <c r="H52">
+        <v>456.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>335.3</v>
+      </c>
+      <c r="K52">
+        <v>225.5</v>
+      </c>
+      <c r="L52">
+        <v>109.8</v>
+      </c>
+      <c r="M52">
+        <v>182.49968</v>
+      </c>
+      <c r="N52">
+        <v>-72.69967999999997</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-72.69967999999997</v>
+      </c>
+      <c r="Q52">
+        <v>152.80032</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1749479898882462</v>
+      </c>
+      <c r="T52">
+        <v>1.846119712516159</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2138</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6016448905554246</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1961239949441231</v>
+      </c>
+      <c r="C53">
+        <v>202.3624708357852</v>
+      </c>
+      <c r="D53">
+        <v>795.3344708357853</v>
+      </c>
+      <c r="E53">
+        <v>-380.2280000000001</v>
+      </c>
+      <c r="F53">
+        <v>870.672</v>
+      </c>
+      <c r="G53">
+        <v>277.7</v>
+      </c>
+      <c r="H53">
+        <v>456.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>335.3</v>
+      </c>
+      <c r="K53">
+        <v>225.5</v>
+      </c>
+      <c r="L53">
+        <v>109.8</v>
+      </c>
+      <c r="M53">
+        <v>186.1496736</v>
+      </c>
+      <c r="N53">
+        <v>-76.34967359999999</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-76.34967359999999</v>
+      </c>
+      <c r="Q53">
+        <v>149.1503264</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1777265202941287</v>
+      </c>
+      <c r="T53">
+        <v>1.883795625016489</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2138</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.589847931917083</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1978739949441231</v>
+      </c>
+      <c r="C54">
+        <v>176.5408614200443</v>
+      </c>
+      <c r="D54">
+        <v>786.5848614200443</v>
+      </c>
+      <c r="E54">
+        <v>-363.1560000000001</v>
+      </c>
+      <c r="F54">
+        <v>887.744</v>
+      </c>
+      <c r="G54">
+        <v>277.7</v>
+      </c>
+      <c r="H54">
+        <v>456.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>335.3</v>
+      </c>
+      <c r="K54">
+        <v>225.5</v>
+      </c>
+      <c r="L54">
+        <v>109.8</v>
+      </c>
+      <c r="M54">
+        <v>189.7996672</v>
+      </c>
+      <c r="N54">
+        <v>-79.99966719999998</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-79.99966719999998</v>
+      </c>
+      <c r="Q54">
+        <v>145.5003328</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1806208228002564</v>
+      </c>
+      <c r="T54">
+        <v>1.923041367204333</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2138</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.578504702457139</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1996239949441231</v>
+      </c>
+      <c r="C55">
+        <v>150.9096690684096</v>
+      </c>
+      <c r="D55">
+        <v>778.0256690684096</v>
+      </c>
+      <c r="E55">
+        <v>-346.0840000000001</v>
+      </c>
+      <c r="F55">
+        <v>904.816</v>
+      </c>
+      <c r="G55">
+        <v>277.7</v>
+      </c>
+      <c r="H55">
+        <v>456.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>335.3</v>
+      </c>
+      <c r="K55">
+        <v>225.5</v>
+      </c>
+      <c r="L55">
+        <v>109.8</v>
+      </c>
+      <c r="M55">
+        <v>193.4496608</v>
+      </c>
+      <c r="N55">
+        <v>-83.64966079999999</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-83.64966079999999</v>
+      </c>
+      <c r="Q55">
+        <v>141.8503392</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1836382871151555</v>
+      </c>
+      <c r="T55">
+        <v>1.963957140974637</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2138</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.56758951939191</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2013739949441231</v>
+      </c>
+      <c r="C56">
+        <v>125.4627446449944</v>
+      </c>
+      <c r="D56">
+        <v>769.6507446449945</v>
+      </c>
+      <c r="E56">
+        <v>-329.0120000000001</v>
+      </c>
+      <c r="F56">
+        <v>921.888</v>
+      </c>
+      <c r="G56">
+        <v>277.7</v>
+      </c>
+      <c r="H56">
+        <v>456.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>335.3</v>
+      </c>
+      <c r="K56">
+        <v>225.5</v>
+      </c>
+      <c r="L56">
+        <v>109.8</v>
+      </c>
+      <c r="M56">
+        <v>197.0996544</v>
+      </c>
+      <c r="N56">
+        <v>-87.29965439999998</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-87.29965439999998</v>
+      </c>
+      <c r="Q56">
+        <v>138.2003456</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1867869455307024</v>
+      </c>
+      <c r="T56">
+        <v>2.006651861430608</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2138</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5570786023661339</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2031239949441231</v>
+      </c>
+      <c r="C57">
+        <v>100.1942009595347</v>
+      </c>
+      <c r="D57">
+        <v>761.4542009595348</v>
+      </c>
+      <c r="E57">
+        <v>-311.9399999999999</v>
+      </c>
+      <c r="F57">
+        <v>938.9600000000002</v>
+      </c>
+      <c r="G57">
+        <v>277.7</v>
+      </c>
+      <c r="H57">
+        <v>456.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>335.3</v>
+      </c>
+      <c r="K57">
+        <v>225.5</v>
+      </c>
+      <c r="L57">
+        <v>109.8</v>
+      </c>
+      <c r="M57">
+        <v>200.749648</v>
+      </c>
+      <c r="N57">
+        <v>-90.94964800000002</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-90.94964800000002</v>
+      </c>
+      <c r="Q57">
+        <v>134.550352</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1900755443202735</v>
+      </c>
+      <c r="T57">
+        <v>2.051244125017955</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2138</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5469499005049314</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2048739949441231</v>
+      </c>
+      <c r="C58">
+        <v>75.098398966167</v>
+      </c>
+      <c r="D58">
+        <v>753.4303989661672</v>
+      </c>
+      <c r="E58">
+        <v>-294.8679999999999</v>
+      </c>
+      <c r="F58">
+        <v>956.0320000000002</v>
+      </c>
+      <c r="G58">
+        <v>277.7</v>
+      </c>
+      <c r="H58">
+        <v>456.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>335.3</v>
+      </c>
+      <c r="K58">
+        <v>225.5</v>
+      </c>
+      <c r="L58">
+        <v>109.8</v>
+      </c>
+      <c r="M58">
+        <v>204.3996416</v>
+      </c>
+      <c r="N58">
+        <v>-94.59964160000001</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-94.59964160000001</v>
+      </c>
+      <c r="Q58">
+        <v>130.9003584</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.193513624873007</v>
+      </c>
+      <c r="T58">
+        <v>2.097863309677454</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2138</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5371829379959148</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2066239949441231</v>
+      </c>
+      <c r="C59">
+        <v>50.1699348256858</v>
+      </c>
+      <c r="D59">
+        <v>745.573934825686</v>
+      </c>
+      <c r="E59">
+        <v>-277.7959999999999</v>
+      </c>
+      <c r="F59">
+        <v>973.1040000000002</v>
+      </c>
+      <c r="G59">
+        <v>277.7</v>
+      </c>
+      <c r="H59">
+        <v>456.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>335.3</v>
+      </c>
+      <c r="K59">
+        <v>225.5</v>
+      </c>
+      <c r="L59">
+        <v>109.8</v>
+      </c>
+      <c r="M59">
+        <v>208.0496352</v>
+      </c>
+      <c r="N59">
+        <v>-98.2496352</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-98.2496352</v>
+      </c>
+      <c r="Q59">
+        <v>127.2503648</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1971116161491235</v>
+      </c>
+      <c r="T59">
+        <v>2.146650828507163</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2138</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.527758675925811</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2083739949441231</v>
+      </c>
+      <c r="C60">
+        <v>25.40362776890606</v>
+      </c>
+      <c r="D60">
+        <v>737.8796277689061</v>
+      </c>
+      <c r="E60">
+        <v>-260.7240000000002</v>
+      </c>
+      <c r="F60">
+        <v>990.1759999999999</v>
+      </c>
+      <c r="G60">
+        <v>277.7</v>
+      </c>
+      <c r="H60">
+        <v>456.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>335.3</v>
+      </c>
+      <c r="K60">
+        <v>225.5</v>
+      </c>
+      <c r="L60">
+        <v>109.8</v>
+      </c>
+      <c r="M60">
+        <v>211.6996288</v>
+      </c>
+      <c r="N60">
+        <v>-101.8996288</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-101.8996288</v>
+      </c>
+      <c r="Q60">
+        <v>123.6003712</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2008809403431502</v>
+      </c>
+      <c r="T60">
+        <v>2.197761562519237</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2138</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5186593884098489</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.210123994944123</v>
+      </c>
+      <c r="C61">
+        <v>0.7945087038461907</v>
+      </c>
+      <c r="D61">
+        <v>730.3425087038462</v>
+      </c>
+      <c r="E61">
+        <v>-243.6520000000002</v>
+      </c>
+      <c r="F61">
+        <v>1007.248</v>
+      </c>
+      <c r="G61">
+        <v>277.7</v>
+      </c>
+      <c r="H61">
+        <v>456.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>335.3</v>
+      </c>
+      <c r="K61">
+        <v>225.5</v>
+      </c>
+      <c r="L61">
+        <v>109.8</v>
+      </c>
+      <c r="M61">
+        <v>215.3496224</v>
+      </c>
+      <c r="N61">
+        <v>-105.5496224</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-105.5496224</v>
+      </c>
+      <c r="Q61">
+        <v>119.9503776</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2048341340100563</v>
+      </c>
+      <c r="T61">
+        <v>2.251365503068486</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2138</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5098685513181564</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2118739949441231</v>
+      </c>
+      <c r="C62">
+        <v>-23.66219048591006</v>
+      </c>
+      <c r="D62">
+        <v>722.9578095140899</v>
+      </c>
+      <c r="E62">
+        <v>-226.5800000000002</v>
+      </c>
+      <c r="F62">
+        <v>1024.32</v>
+      </c>
+      <c r="G62">
+        <v>277.7</v>
+      </c>
+      <c r="H62">
+        <v>456.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>335.3</v>
+      </c>
+      <c r="K62">
+        <v>225.5</v>
+      </c>
+      <c r="L62">
+        <v>109.8</v>
+      </c>
+      <c r="M62">
+        <v>218.999616</v>
+      </c>
+      <c r="N62">
+        <v>-109.199616</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-109.199616</v>
+      </c>
+      <c r="Q62">
+        <v>116.300384</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2089849873603077</v>
+      </c>
+      <c r="T62">
+        <v>2.307649640645199</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2138</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5013707421295206</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2288739949441231</v>
+      </c>
+      <c r="C63">
+        <v>-105.3947073827776</v>
+      </c>
+      <c r="D63">
+        <v>658.2972926172225</v>
+      </c>
+      <c r="E63">
+        <v>-209.508</v>
+      </c>
+      <c r="F63">
+        <v>1041.392</v>
+      </c>
+      <c r="G63">
+        <v>277.7</v>
+      </c>
+      <c r="H63">
+        <v>456.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>335.3</v>
+      </c>
+      <c r="K63">
+        <v>225.5</v>
+      </c>
+      <c r="L63">
+        <v>109.8</v>
+      </c>
+      <c r="M63">
+        <v>248.6844096</v>
+      </c>
+      <c r="N63">
+        <v>-138.8844096</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-138.8844096</v>
+      </c>
+      <c r="Q63">
+        <v>86.61559039999997</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.213348704984931</v>
+      </c>
+      <c r="T63">
+        <v>2.366820144251486</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4415234560807788</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2308739949441231</v>
+      </c>
+      <c r="C64">
+        <v>-129.3213291425709</v>
+      </c>
+      <c r="D64">
+        <v>651.4426708574291</v>
+      </c>
+      <c r="E64">
+        <v>-192.4360000000001</v>
+      </c>
+      <c r="F64">
+        <v>1058.464</v>
+      </c>
+      <c r="G64">
+        <v>277.7</v>
+      </c>
+      <c r="H64">
+        <v>456.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>335.3</v>
+      </c>
+      <c r="K64">
+        <v>225.5</v>
+      </c>
+      <c r="L64">
+        <v>109.8</v>
+      </c>
+      <c r="M64">
+        <v>252.7612032</v>
+      </c>
+      <c r="N64">
+        <v>-142.9612032</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-142.9612032</v>
+      </c>
+      <c r="Q64">
+        <v>82.5387968</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2179420919582187</v>
+      </c>
+      <c r="T64">
+        <v>2.429104884889683</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4344021100149598</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2328739949441231</v>
+      </c>
+      <c r="C65">
+        <v>-153.1066723810093</v>
+      </c>
+      <c r="D65">
+        <v>644.7293276189907</v>
+      </c>
+      <c r="E65">
+        <v>-175.364</v>
+      </c>
+      <c r="F65">
+        <v>1075.536</v>
+      </c>
+      <c r="G65">
+        <v>277.7</v>
+      </c>
+      <c r="H65">
+        <v>456.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>335.3</v>
+      </c>
+      <c r="K65">
+        <v>225.5</v>
+      </c>
+      <c r="L65">
+        <v>109.8</v>
+      </c>
+      <c r="M65">
+        <v>256.8379968</v>
+      </c>
+      <c r="N65">
+        <v>-147.0379968</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-147.0379968</v>
+      </c>
+      <c r="Q65">
+        <v>78.46200319999997</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2227837701192516</v>
+      </c>
+      <c r="T65">
+        <v>2.49475636826508</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4275068384274207</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2348739949441231</v>
+      </c>
+      <c r="C66">
+        <v>-176.7550603186623</v>
+      </c>
+      <c r="D66">
+        <v>638.1529396813377</v>
+      </c>
+      <c r="E66">
+        <v>-158.2920000000001</v>
+      </c>
+      <c r="F66">
+        <v>1092.608</v>
+      </c>
+      <c r="G66">
+        <v>277.7</v>
+      </c>
+      <c r="H66">
+        <v>456.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>335.3</v>
+      </c>
+      <c r="K66">
+        <v>225.5</v>
+      </c>
+      <c r="L66">
+        <v>109.8</v>
+      </c>
+      <c r="M66">
+        <v>260.9147904</v>
+      </c>
+      <c r="N66">
+        <v>-151.1147904</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-151.1147904</v>
+      </c>
+      <c r="Q66">
+        <v>74.3852096</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2278944304003419</v>
+      </c>
+      <c r="T66">
+        <v>2.564055156272443</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4208270440769923</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2368739949441231</v>
+      </c>
+      <c r="C67">
+        <v>-200.2706415657753</v>
+      </c>
+      <c r="D67">
+        <v>631.7093584342248</v>
+      </c>
+      <c r="E67">
+        <v>-141.22</v>
+      </c>
+      <c r="F67">
+        <v>1109.68</v>
+      </c>
+      <c r="G67">
+        <v>277.7</v>
+      </c>
+      <c r="H67">
+        <v>456.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>335.3</v>
+      </c>
+      <c r="K67">
+        <v>225.5</v>
+      </c>
+      <c r="L67">
+        <v>109.8</v>
+      </c>
+      <c r="M67">
+        <v>264.991584</v>
+      </c>
+      <c r="N67">
+        <v>-155.191584</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-155.191584</v>
+      </c>
+      <c r="Q67">
+        <v>70.30841599999997</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2332971284117803</v>
+      </c>
+      <c r="T67">
+        <v>2.637313875023085</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4143527818604231</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2388739949441231</v>
+      </c>
+      <c r="C68">
+        <v>-223.6573988495559</v>
+      </c>
+      <c r="D68">
+        <v>625.3946011504443</v>
+      </c>
+      <c r="E68">
+        <v>-124.1479999999999</v>
+      </c>
+      <c r="F68">
+        <v>1126.752</v>
+      </c>
+      <c r="G68">
+        <v>277.7</v>
+      </c>
+      <c r="H68">
+        <v>456.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>335.3</v>
+      </c>
+      <c r="K68">
+        <v>225.5</v>
+      </c>
+      <c r="L68">
+        <v>109.8</v>
+      </c>
+      <c r="M68">
+        <v>269.0683776000001</v>
+      </c>
+      <c r="N68">
+        <v>-159.2683776000001</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-159.2683776000001</v>
+      </c>
+      <c r="Q68">
+        <v>66.23162239999994</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2390176321885973</v>
+      </c>
+      <c r="T68">
+        <v>2.714881930170823</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4080747094079924</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2408739949441231</v>
+      </c>
+      <c r="C69">
+        <v>-246.9191572231987</v>
+      </c>
+      <c r="D69">
+        <v>619.2048427768013</v>
+      </c>
+      <c r="E69">
+        <v>-107.076</v>
+      </c>
+      <c r="F69">
+        <v>1143.824</v>
+      </c>
+      <c r="G69">
+        <v>277.7</v>
+      </c>
+      <c r="H69">
+        <v>456.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>335.3</v>
+      </c>
+      <c r="K69">
+        <v>225.5</v>
+      </c>
+      <c r="L69">
+        <v>109.8</v>
+      </c>
+      <c r="M69">
+        <v>273.1451712</v>
+      </c>
+      <c r="N69">
+        <v>-163.3451712</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-163.3451712</v>
+      </c>
+      <c r="Q69">
+        <v>62.15482879999996</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2450848331640094</v>
+      </c>
+      <c r="T69">
+        <v>2.797151079569939</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4019840421033956</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2428739949441231</v>
+      </c>
+      <c r="C70">
+        <v>-270.0595917922026</v>
+      </c>
+      <c r="D70">
+        <v>613.1364082077976</v>
+      </c>
+      <c r="E70">
+        <v>-90.00399999999991</v>
+      </c>
+      <c r="F70">
+        <v>1160.896</v>
+      </c>
+      <c r="G70">
+        <v>277.7</v>
+      </c>
+      <c r="H70">
+        <v>456.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>335.3</v>
+      </c>
+      <c r="K70">
+        <v>225.5</v>
+      </c>
+      <c r="L70">
+        <v>109.8</v>
+      </c>
+      <c r="M70">
+        <v>277.2219648000001</v>
+      </c>
+      <c r="N70">
+        <v>-167.4219648000001</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-167.4219648000001</v>
+      </c>
+      <c r="Q70">
+        <v>58.07803519999993</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2515312342003847</v>
+      </c>
+      <c r="T70">
+        <v>2.884562050806499</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3960725120724632</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2448739949441231</v>
+      </c>
+      <c r="C71">
+        <v>-293.0822349907685</v>
+      </c>
+      <c r="D71">
+        <v>607.1857650092315</v>
+      </c>
+      <c r="E71">
+        <v>-72.93200000000002</v>
+      </c>
+      <c r="F71">
+        <v>1177.968</v>
+      </c>
+      <c r="G71">
+        <v>277.7</v>
+      </c>
+      <c r="H71">
+        <v>456.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>335.3</v>
+      </c>
+      <c r="K71">
+        <v>225.5</v>
+      </c>
+      <c r="L71">
+        <v>109.8</v>
+      </c>
+      <c r="M71">
+        <v>281.2987584000001</v>
+      </c>
+      <c r="N71">
+        <v>-171.4987584</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-171.4987584</v>
+      </c>
+      <c r="Q71">
+        <v>54.00124159999996</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2583935320778165</v>
+      </c>
+      <c r="T71">
+        <v>2.977612439542193</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3903323307380797</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2468739949441231</v>
+      </c>
+      <c r="C72">
+        <v>-315.9904834385604</v>
+      </c>
+      <c r="D72">
+        <v>601.3495165614398</v>
+      </c>
+      <c r="E72">
+        <v>-55.8599999999999</v>
+      </c>
+      <c r="F72">
+        <v>1195.04</v>
+      </c>
+      <c r="G72">
+        <v>277.7</v>
+      </c>
+      <c r="H72">
+        <v>456.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>335.3</v>
+      </c>
+      <c r="K72">
+        <v>225.5</v>
+      </c>
+      <c r="L72">
+        <v>109.8</v>
+      </c>
+      <c r="M72">
+        <v>285.3755520000001</v>
+      </c>
+      <c r="N72">
+        <v>-175.5755520000001</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-175.5755520000001</v>
+      </c>
+      <c r="Q72">
+        <v>49.92444799999993</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2657133164804103</v>
+      </c>
+      <c r="T72">
+        <v>3.076866187526933</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3847561545846786</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2488739949441231</v>
+      </c>
+      <c r="C73">
+        <v>-338.7876044057832</v>
+      </c>
+      <c r="D73">
+        <v>595.6243955942168</v>
+      </c>
+      <c r="E73">
+        <v>-38.78800000000001</v>
+      </c>
+      <c r="F73">
+        <v>1212.112</v>
+      </c>
+      <c r="G73">
+        <v>277.7</v>
+      </c>
+      <c r="H73">
+        <v>456.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>335.3</v>
+      </c>
+      <c r="K73">
+        <v>225.5</v>
+      </c>
+      <c r="L73">
+        <v>109.8</v>
+      </c>
+      <c r="M73">
+        <v>289.4523456000001</v>
+      </c>
+      <c r="N73">
+        <v>-179.6523456</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-179.6523456</v>
+      </c>
+      <c r="Q73">
+        <v>45.84765439999995</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2735379136004245</v>
+      </c>
+      <c r="T73">
+        <v>3.182965021579585</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3793370538158803</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2508739949441231</v>
+      </c>
+      <c r="C74">
+        <v>-361.4767419124457</v>
+      </c>
+      <c r="D74">
+        <v>590.0072580875542</v>
+      </c>
+      <c r="E74">
+        <v>-21.71600000000012</v>
+      </c>
+      <c r="F74">
+        <v>1229.184</v>
+      </c>
+      <c r="G74">
+        <v>277.7</v>
+      </c>
+      <c r="H74">
+        <v>456.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>335.3</v>
+      </c>
+      <c r="K74">
+        <v>225.5</v>
+      </c>
+      <c r="L74">
+        <v>109.8</v>
+      </c>
+      <c r="M74">
+        <v>293.5291392</v>
+      </c>
+      <c r="N74">
+        <v>-183.7291392</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-183.7291392</v>
+      </c>
+      <c r="Q74">
+        <v>41.77086079999998</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2819214105147253</v>
+      </c>
+      <c r="T74">
+        <v>3.296642343778855</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3740684836239931</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2528739949441231</v>
+      </c>
+      <c r="C75">
+        <v>-384.0609224857244</v>
+      </c>
+      <c r="D75">
+        <v>584.4950775142756</v>
+      </c>
+      <c r="E75">
+        <v>-4.644000000000005</v>
+      </c>
+      <c r="F75">
+        <v>1246.256</v>
+      </c>
+      <c r="G75">
+        <v>277.7</v>
+      </c>
+      <c r="H75">
+        <v>456.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>335.3</v>
+      </c>
+      <c r="K75">
+        <v>225.5</v>
+      </c>
+      <c r="L75">
+        <v>109.8</v>
+      </c>
+      <c r="M75">
+        <v>297.6059328000001</v>
+      </c>
+      <c r="N75">
+        <v>-187.8059328000001</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-187.8059328000001</v>
+      </c>
+      <c r="Q75">
+        <v>37.69406719999995</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2909259072004559</v>
+      </c>
+      <c r="T75">
+        <v>3.418740208363257</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3689442578209247</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2548739949441231</v>
+      </c>
+      <c r="C76">
+        <v>-406.5430605975821</v>
+      </c>
+      <c r="D76">
+        <v>579.0849394024179</v>
+      </c>
+      <c r="E76">
+        <v>12.42799999999988</v>
+      </c>
+      <c r="F76">
+        <v>1263.328</v>
+      </c>
+      <c r="G76">
+        <v>277.7</v>
+      </c>
+      <c r="H76">
+        <v>456.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>335.3</v>
+      </c>
+      <c r="K76">
+        <v>225.5</v>
+      </c>
+      <c r="L76">
+        <v>109.8</v>
+      </c>
+      <c r="M76">
+        <v>301.6827264</v>
+      </c>
+      <c r="N76">
+        <v>-191.8827264</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-191.8827264</v>
+      </c>
+      <c r="Q76">
+        <v>33.61727359999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3006230574773965</v>
+      </c>
+      <c r="T76">
+        <v>3.550230216377229</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3639585246071284</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2568739949441231</v>
+      </c>
+      <c r="C77">
+        <v>-428.9259638031733</v>
+      </c>
+      <c r="D77">
+        <v>573.7740361968267</v>
+      </c>
+      <c r="E77">
+        <v>29.5</v>
+      </c>
+      <c r="F77">
+        <v>1280.4</v>
+      </c>
+      <c r="G77">
+        <v>277.7</v>
+      </c>
+      <c r="H77">
+        <v>456.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>335.3</v>
+      </c>
+      <c r="K77">
+        <v>225.5</v>
+      </c>
+      <c r="L77">
+        <v>109.8</v>
+      </c>
+      <c r="M77">
+        <v>305.75952</v>
+      </c>
+      <c r="N77">
+        <v>-195.95952</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-195.95952</v>
+      </c>
+      <c r="Q77">
+        <v>29.54048</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3110959797764923</v>
+      </c>
+      <c r="T77">
+        <v>3.692239425032319</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3591057442790334</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2588739949441231</v>
+      </c>
+      <c r="C78">
+        <v>-451.2123375990643</v>
+      </c>
+      <c r="D78">
+        <v>568.5596624009357</v>
+      </c>
+      <c r="E78">
+        <v>46.57199999999989</v>
+      </c>
+      <c r="F78">
+        <v>1297.472</v>
+      </c>
+      <c r="G78">
+        <v>277.7</v>
+      </c>
+      <c r="H78">
+        <v>456.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>335.3</v>
+      </c>
+      <c r="K78">
+        <v>225.5</v>
+      </c>
+      <c r="L78">
+        <v>109.8</v>
+      </c>
+      <c r="M78">
+        <v>309.8363136</v>
+      </c>
+      <c r="N78">
+        <v>-200.0363136</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-200.0363136</v>
+      </c>
+      <c r="Q78">
+        <v>25.46368639999997</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3224416456005129</v>
+      </c>
+      <c r="T78">
+        <v>3.846082734408665</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3543806686964145</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2608739949441231</v>
+      </c>
+      <c r="C79">
+        <v>-473.4047900189346</v>
+      </c>
+      <c r="D79">
+        <v>563.4392099810656</v>
+      </c>
+      <c r="E79">
+        <v>63.64400000000001</v>
+      </c>
+      <c r="F79">
+        <v>1314.544</v>
+      </c>
+      <c r="G79">
+        <v>277.7</v>
+      </c>
+      <c r="H79">
+        <v>456.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>335.3</v>
+      </c>
+      <c r="K79">
+        <v>225.5</v>
+      </c>
+      <c r="L79">
+        <v>109.8</v>
+      </c>
+      <c r="M79">
+        <v>313.9131072</v>
+      </c>
+      <c r="N79">
+        <v>-204.1131072</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-204.1131072</v>
+      </c>
+      <c r="Q79">
+        <v>21.3868928</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3347738910614047</v>
+      </c>
+      <c r="T79">
+        <v>4.013303722861216</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3497783223497078</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2628739949441231</v>
+      </c>
+      <c r="C80">
+        <v>-495.5058359831621</v>
+      </c>
+      <c r="D80">
+        <v>558.4101640168378</v>
+      </c>
+      <c r="E80">
+        <v>80.71599999999989</v>
+      </c>
+      <c r="F80">
+        <v>1331.616</v>
+      </c>
+      <c r="G80">
+        <v>277.7</v>
+      </c>
+      <c r="H80">
+        <v>456.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>335.3</v>
+      </c>
+      <c r="K80">
+        <v>225.5</v>
+      </c>
+      <c r="L80">
+        <v>109.8</v>
+      </c>
+      <c r="M80">
+        <v>317.9899008</v>
+      </c>
+      <c r="N80">
+        <v>-208.1899008</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-208.1899008</v>
+      </c>
+      <c r="Q80">
+        <v>17.31009920000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.348227249746014</v>
+      </c>
+      <c r="T80">
+        <v>4.195726619354907</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.345293984883686</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2648739949441231</v>
+      </c>
+      <c r="C81">
+        <v>-517.5179014175335</v>
+      </c>
+      <c r="D81">
+        <v>553.4700985824667</v>
+      </c>
+      <c r="E81">
+        <v>97.78800000000001</v>
+      </c>
+      <c r="F81">
+        <v>1348.688</v>
+      </c>
+      <c r="G81">
+        <v>277.7</v>
+      </c>
+      <c r="H81">
+        <v>456.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>335.3</v>
+      </c>
+      <c r="K81">
+        <v>225.5</v>
+      </c>
+      <c r="L81">
+        <v>109.8</v>
+      </c>
+      <c r="M81">
+        <v>322.0666944</v>
+      </c>
+      <c r="N81">
+        <v>-212.2666944</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-212.2666944</v>
+      </c>
+      <c r="Q81">
+        <v>13.23330559999999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3629618806863005</v>
+      </c>
+      <c r="T81">
+        <v>4.395523125038475</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3409231749484495</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2668739949441231</v>
+      </c>
+      <c r="C82">
+        <v>-539.4433271552471</v>
+      </c>
+      <c r="D82">
+        <v>548.6166728447532</v>
+      </c>
+      <c r="E82">
+        <v>114.8600000000001</v>
+      </c>
+      <c r="F82">
+        <v>1365.76</v>
+      </c>
+      <c r="G82">
+        <v>277.7</v>
+      </c>
+      <c r="H82">
+        <v>456.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>335.3</v>
+      </c>
+      <c r="K82">
+        <v>225.5</v>
+      </c>
+      <c r="L82">
+        <v>109.8</v>
+      </c>
+      <c r="M82">
+        <v>326.143488</v>
+      </c>
+      <c r="N82">
+        <v>-216.343488</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-216.343488</v>
+      </c>
+      <c r="Q82">
+        <v>9.156511999999964</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3791699747206155</v>
+      </c>
+      <c r="T82">
+        <v>4.615299281290399</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3366616352615938</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2688739949441231</v>
+      </c>
+      <c r="C83">
+        <v>-561.284372635402</v>
+      </c>
+      <c r="D83">
+        <v>543.8476273645981</v>
+      </c>
+      <c r="E83">
+        <v>131.932</v>
+      </c>
+      <c r="F83">
+        <v>1382.832</v>
+      </c>
+      <c r="G83">
+        <v>277.7</v>
+      </c>
+      <c r="H83">
+        <v>456.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>335.3</v>
+      </c>
+      <c r="K83">
+        <v>225.5</v>
+      </c>
+      <c r="L83">
+        <v>109.8</v>
+      </c>
+      <c r="M83">
+        <v>330.2202816</v>
+      </c>
+      <c r="N83">
+        <v>-220.4202816</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-220.4202816</v>
+      </c>
+      <c r="Q83">
+        <v>5.07971839999999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3970841839164374</v>
+      </c>
+      <c r="T83">
+        <v>4.858209769779368</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3325053187768828</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2708739949441231</v>
+      </c>
+      <c r="C84">
+        <v>-583.043219410247</v>
+      </c>
+      <c r="D84">
+        <v>539.1607805897532</v>
+      </c>
+      <c r="E84">
+        <v>149.0040000000001</v>
+      </c>
+      <c r="F84">
+        <v>1399.904</v>
+      </c>
+      <c r="G84">
+        <v>277.7</v>
+      </c>
+      <c r="H84">
+        <v>456.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>335.3</v>
+      </c>
+      <c r="K84">
+        <v>225.5</v>
+      </c>
+      <c r="L84">
+        <v>109.8</v>
+      </c>
+      <c r="M84">
+        <v>334.2970752000001</v>
+      </c>
+      <c r="N84">
+        <v>-224.4970752</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-224.4970752</v>
+      </c>
+      <c r="Q84">
+        <v>1.00292479999996</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4169888608006839</v>
+      </c>
+      <c r="T84">
+        <v>5.128110312544888</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3284503758649696</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2728739949441231</v>
+      </c>
+      <c r="C85">
+        <v>-604.7219744726233</v>
+      </c>
+      <c r="D85">
+        <v>534.5540255273769</v>
+      </c>
+      <c r="E85">
+        <v>166.076</v>
+      </c>
+      <c r="F85">
+        <v>1416.976</v>
+      </c>
+      <c r="G85">
+        <v>277.7</v>
+      </c>
+      <c r="H85">
+        <v>456.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>335.3</v>
+      </c>
+      <c r="K85">
+        <v>225.5</v>
+      </c>
+      <c r="L85">
+        <v>109.8</v>
+      </c>
+      <c r="M85">
+        <v>338.3738688</v>
+      </c>
+      <c r="N85">
+        <v>-228.5738688</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-228.5738688</v>
+      </c>
+      <c r="Q85">
+        <v>-3.073868800000014</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4392352643771948</v>
+      </c>
+      <c r="T85">
+        <v>5.429763860341647</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3244931424208133</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2748739949441231</v>
+      </c>
+      <c r="C86">
+        <v>-626.3226734142738</v>
+      </c>
+      <c r="D86">
+        <v>530.0253265857261</v>
+      </c>
+      <c r="E86">
+        <v>183.1479999999999</v>
+      </c>
+      <c r="F86">
+        <v>1434.048</v>
+      </c>
+      <c r="G86">
+        <v>277.7</v>
+      </c>
+      <c r="H86">
+        <v>456.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>335.3</v>
+      </c>
+      <c r="K86">
+        <v>225.5</v>
+      </c>
+      <c r="L86">
+        <v>109.8</v>
+      </c>
+      <c r="M86">
+        <v>342.4506624</v>
+      </c>
+      <c r="N86">
+        <v>-232.6506624</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-232.6506624</v>
+      </c>
+      <c r="Q86">
+        <v>-7.150662399999987</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4642624684007692</v>
+      </c>
+      <c r="T86">
+        <v>5.769124101612997</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3206301288205656</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2768739949441231</v>
+      </c>
+      <c r="C87">
+        <v>-647.8472834249567</v>
+      </c>
+      <c r="D87">
+        <v>525.5727165750433</v>
+      </c>
+      <c r="E87">
+        <v>200.2199999999998</v>
+      </c>
+      <c r="F87">
+        <v>1451.12</v>
+      </c>
+      <c r="G87">
+        <v>277.7</v>
+      </c>
+      <c r="H87">
+        <v>456.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>335.3</v>
+      </c>
+      <c r="K87">
+        <v>225.5</v>
+      </c>
+      <c r="L87">
+        <v>109.8</v>
+      </c>
+      <c r="M87">
+        <v>346.527456</v>
+      </c>
+      <c r="N87">
+        <v>-236.727456</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-236.727456</v>
+      </c>
+      <c r="Q87">
+        <v>-11.22745599999996</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4926266329608205</v>
+      </c>
+      <c r="T87">
+        <v>6.153732375053863</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3168580096579707</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2788739949441231</v>
+      </c>
+      <c r="C88">
+        <v>-669.2977061416477</v>
+      </c>
+      <c r="D88">
+        <v>521.1942938583524</v>
+      </c>
+      <c r="E88">
+        <v>217.2919999999999</v>
+      </c>
+      <c r="F88">
+        <v>1468.192</v>
+      </c>
+      <c r="G88">
+        <v>277.7</v>
+      </c>
+      <c r="H88">
+        <v>456.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>335.3</v>
+      </c>
+      <c r="K88">
+        <v>225.5</v>
+      </c>
+      <c r="L88">
+        <v>109.8</v>
+      </c>
+      <c r="M88">
+        <v>350.6042496</v>
+      </c>
+      <c r="N88">
+        <v>-240.8042496</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-240.8042496</v>
+      </c>
+      <c r="Q88">
+        <v>-15.30424959999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5250428210294505</v>
+      </c>
+      <c r="T88">
+        <v>6.593284687557711</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3131736141968315</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2808739949441231</v>
+      </c>
+      <c r="C89">
+        <v>-690.6757803565063</v>
+      </c>
+      <c r="D89">
+        <v>516.8882196434938</v>
+      </c>
+      <c r="E89">
+        <v>234.364</v>
+      </c>
+      <c r="F89">
+        <v>1485.264</v>
+      </c>
+      <c r="G89">
+        <v>277.7</v>
+      </c>
+      <c r="H89">
+        <v>456.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>335.3</v>
+      </c>
+      <c r="K89">
+        <v>225.5</v>
+      </c>
+      <c r="L89">
+        <v>109.8</v>
+      </c>
+      <c r="M89">
+        <v>354.6810432</v>
+      </c>
+      <c r="N89">
+        <v>-244.8810432</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-244.8810432</v>
+      </c>
+      <c r="Q89">
+        <v>-19.38104320000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.562446114954793</v>
+      </c>
+      <c r="T89">
+        <v>7.100460432754458</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3095739174819253</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2828739949441231</v>
+      </c>
+      <c r="C90">
+        <v>-711.9832845917022</v>
+      </c>
+      <c r="D90">
+        <v>512.6527154082978</v>
+      </c>
+      <c r="E90">
+        <v>251.4359999999999</v>
+      </c>
+      <c r="F90">
+        <v>1502.336</v>
+      </c>
+      <c r="G90">
+        <v>277.7</v>
+      </c>
+      <c r="H90">
+        <v>456.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>335.3</v>
+      </c>
+      <c r="K90">
+        <v>225.5</v>
+      </c>
+      <c r="L90">
+        <v>109.8</v>
+      </c>
+      <c r="M90">
+        <v>358.7578368</v>
+      </c>
+      <c r="N90">
+        <v>-248.9578368</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-248.9578368</v>
+      </c>
+      <c r="Q90">
+        <v>-23.4578368</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6060832912010257</v>
+      </c>
+      <c r="T90">
+        <v>7.692165468817331</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3060560320559944</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2848739949441231</v>
+      </c>
+      <c r="C91">
+        <v>-733.2219395486774</v>
+      </c>
+      <c r="D91">
+        <v>508.4860604513228</v>
+      </c>
+      <c r="E91">
+        <v>268.508</v>
+      </c>
+      <c r="F91">
+        <v>1519.408</v>
+      </c>
+      <c r="G91">
+        <v>277.7</v>
+      </c>
+      <c r="H91">
+        <v>456.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>335.3</v>
+      </c>
+      <c r="K91">
+        <v>225.5</v>
+      </c>
+      <c r="L91">
+        <v>109.8</v>
+      </c>
+      <c r="M91">
+        <v>362.8346304</v>
+      </c>
+      <c r="N91">
+        <v>-253.0346304</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-253.0346304</v>
+      </c>
+      <c r="Q91">
+        <v>-27.53463040000003</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6576544994920281</v>
+      </c>
+      <c r="T91">
+        <v>8.391453238709815</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3026172002351405</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2868739949441231</v>
+      </c>
+      <c r="C92">
+        <v>-754.3934104389321</v>
+      </c>
+      <c r="D92">
+        <v>504.386589561068</v>
+      </c>
+      <c r="E92">
+        <v>285.5799999999999</v>
+      </c>
+      <c r="F92">
+        <v>1536.48</v>
+      </c>
+      <c r="G92">
+        <v>277.7</v>
+      </c>
+      <c r="H92">
+        <v>456.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>335.3</v>
+      </c>
+      <c r="K92">
+        <v>225.5</v>
+      </c>
+      <c r="L92">
+        <v>109.8</v>
+      </c>
+      <c r="M92">
+        <v>366.911424</v>
+      </c>
+      <c r="N92">
+        <v>-257.111424</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-257.111424</v>
+      </c>
+      <c r="Q92">
+        <v>-31.611424</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7195399494412311</v>
+      </c>
+      <c r="T92">
+        <v>9.230598562580798</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2992547868991945</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2888739949441231</v>
+      </c>
+      <c r="C93">
+        <v>-775.4993092029662</v>
+      </c>
+      <c r="D93">
+        <v>500.352690797034</v>
+      </c>
+      <c r="E93">
+        <v>302.652</v>
+      </c>
+      <c r="F93">
+        <v>1553.552</v>
+      </c>
+      <c r="G93">
+        <v>277.7</v>
+      </c>
+      <c r="H93">
+        <v>456.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>335.3</v>
+      </c>
+      <c r="K93">
+        <v>225.5</v>
+      </c>
+      <c r="L93">
+        <v>109.8</v>
+      </c>
+      <c r="M93">
+        <v>370.9882176</v>
+      </c>
+      <c r="N93">
+        <v>-261.1882176</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-261.1882176</v>
+      </c>
+      <c r="Q93">
+        <v>-35.68821760000003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7951777216013678</v>
+      </c>
+      <c r="T93">
+        <v>10.25622062508978</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2959662727574451</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2908739949441231</v>
+      </c>
+      <c r="C94">
+        <v>-796.5411966235858</v>
+      </c>
+      <c r="D94">
+        <v>496.3828033764142</v>
+      </c>
+      <c r="E94">
+        <v>319.7239999999999</v>
+      </c>
+      <c r="F94">
+        <v>1570.624</v>
+      </c>
+      <c r="G94">
+        <v>277.7</v>
+      </c>
+      <c r="H94">
+        <v>456.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>335.3</v>
+      </c>
+      <c r="K94">
+        <v>225.5</v>
+      </c>
+      <c r="L94">
+        <v>109.8</v>
+      </c>
+      <c r="M94">
+        <v>375.0650112</v>
+      </c>
+      <c r="N94">
+        <v>-265.2650112</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-265.2650112</v>
+      </c>
+      <c r="Q94">
+        <v>-39.7650112</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8897249368015392</v>
+      </c>
+      <c r="T94">
+        <v>11.538248203226</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2927492480535598</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2928739949441231</v>
+      </c>
+      <c r="C95">
+        <v>-817.5205843394015</v>
+      </c>
+      <c r="D95">
+        <v>492.4754156605987</v>
+      </c>
+      <c r="E95">
+        <v>336.796</v>
+      </c>
+      <c r="F95">
+        <v>1587.696</v>
+      </c>
+      <c r="G95">
+        <v>277.7</v>
+      </c>
+      <c r="H95">
+        <v>456.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>335.3</v>
+      </c>
+      <c r="K95">
+        <v>225.5</v>
+      </c>
+      <c r="L95">
+        <v>109.8</v>
+      </c>
+      <c r="M95">
+        <v>379.1418048</v>
+      </c>
+      <c r="N95">
+        <v>-269.3418048</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-269.3418048</v>
+      </c>
+      <c r="Q95">
+        <v>-43.84180480000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.011285642058902</v>
+      </c>
+      <c r="T95">
+        <v>13.18656937511543</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2896014066766398</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2948739949441231</v>
+      </c>
+      <c r="C96">
+        <v>-838.4389367639658</v>
+      </c>
+      <c r="D96">
+        <v>488.6290632360343</v>
+      </c>
+      <c r="E96">
+        <v>353.8679999999999</v>
+      </c>
+      <c r="F96">
+        <v>1604.768</v>
+      </c>
+      <c r="G96">
+        <v>277.7</v>
+      </c>
+      <c r="H96">
+        <v>456.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>335.3</v>
+      </c>
+      <c r="K96">
+        <v>225.5</v>
+      </c>
+      <c r="L96">
+        <v>109.8</v>
+      </c>
+      <c r="M96">
+        <v>383.2185984</v>
+      </c>
+      <c r="N96">
+        <v>-273.4185984</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-273.4185984</v>
+      </c>
+      <c r="Q96">
+        <v>-47.91859840000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.173366582402052</v>
+      </c>
+      <c r="T96">
+        <v>15.38433093763467</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.286520540648165</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2968739949441231</v>
+      </c>
+      <c r="C97">
+        <v>-859.2976729156794</v>
+      </c>
+      <c r="D97">
+        <v>484.8423270843207</v>
+      </c>
+      <c r="E97">
+        <v>370.9400000000001</v>
+      </c>
+      <c r="F97">
+        <v>1621.84</v>
+      </c>
+      <c r="G97">
+        <v>277.7</v>
+      </c>
+      <c r="H97">
+        <v>456.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>335.3</v>
+      </c>
+      <c r="K97">
+        <v>225.5</v>
+      </c>
+      <c r="L97">
+        <v>109.8</v>
+      </c>
+      <c r="M97">
+        <v>387.295392</v>
+      </c>
+      <c r="N97">
+        <v>-277.495392</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-277.495392</v>
+      </c>
+      <c r="Q97">
+        <v>-51.99539200000004</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.400279898882464</v>
+      </c>
+      <c r="T97">
+        <v>18.46119712516162</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2835045349571317</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2988739949441231</v>
+      </c>
+      <c r="C98">
+        <v>-880.0981681632604</v>
+      </c>
+      <c r="D98">
+        <v>481.1138318367396</v>
+      </c>
+      <c r="E98">
+        <v>388.0119999999999</v>
+      </c>
+      <c r="F98">
+        <v>1638.912</v>
+      </c>
+      <c r="G98">
+        <v>277.7</v>
+      </c>
+      <c r="H98">
+        <v>456.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>335.3</v>
+      </c>
+      <c r="K98">
+        <v>225.5</v>
+      </c>
+      <c r="L98">
+        <v>109.8</v>
+      </c>
+      <c r="M98">
+        <v>391.3721856</v>
+      </c>
+      <c r="N98">
+        <v>-281.5721856</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-281.5721856</v>
+      </c>
+      <c r="Q98">
+        <v>-56.07218560000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.740649873603076</v>
+      </c>
+      <c r="T98">
+        <v>23.07649640645197</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2805513627179949</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3008739949441231</v>
+      </c>
+      <c r="C99">
+        <v>-900.8417558912936</v>
+      </c>
+      <c r="D99">
+        <v>477.4422441087063</v>
+      </c>
+      <c r="E99">
+        <v>405.0839999999998</v>
+      </c>
+      <c r="F99">
+        <v>1655.984</v>
+      </c>
+      <c r="G99">
+        <v>277.7</v>
+      </c>
+      <c r="H99">
+        <v>456.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>335.3</v>
+      </c>
+      <c r="K99">
+        <v>225.5</v>
+      </c>
+      <c r="L99">
+        <v>109.8</v>
+      </c>
+      <c r="M99">
+        <v>395.4489792</v>
+      </c>
+      <c r="N99">
+        <v>-285.6489792</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-285.6489792</v>
+      </c>
+      <c r="Q99">
+        <v>-60.14897919999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.307933164804101</v>
+      </c>
+      <c r="T99">
+        <v>30.7686618752693</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2776590806281186</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3028739949441231</v>
+      </c>
+      <c r="C100">
+        <v>-921.5297290900915</v>
+      </c>
+      <c r="D100">
+        <v>473.8262709099085</v>
+      </c>
+      <c r="E100">
+        <v>422.1559999999999</v>
+      </c>
+      <c r="F100">
+        <v>1673.056</v>
+      </c>
+      <c r="G100">
+        <v>277.7</v>
+      </c>
+      <c r="H100">
+        <v>456.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>335.3</v>
+      </c>
+      <c r="K100">
+        <v>225.5</v>
+      </c>
+      <c r="L100">
+        <v>109.8</v>
+      </c>
+      <c r="M100">
+        <v>399.5257728</v>
+      </c>
+      <c r="N100">
+        <v>-289.7257728</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-289.7257728</v>
+      </c>
+      <c r="Q100">
+        <v>-64.22577280000002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.442499747206151</v>
+      </c>
+      <c r="T100">
+        <v>46.15299281290394</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2748258247033419</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3048739949441231</v>
+      </c>
+      <c r="C101">
+        <v>-942.1633418738543</v>
+      </c>
+      <c r="D101">
+        <v>470.2646581261457</v>
+      </c>
+      <c r="E101">
+        <v>439.2279999999998</v>
+      </c>
+      <c r="F101">
+        <v>1690.128</v>
+      </c>
+      <c r="G101">
+        <v>277.7</v>
+      </c>
+      <c r="H101">
+        <v>456.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>335.3</v>
+      </c>
+      <c r="K101">
+        <v>225.5</v>
+      </c>
+      <c r="L101">
+        <v>109.8</v>
+      </c>
+      <c r="M101">
+        <v>403.6025664</v>
+      </c>
+      <c r="N101">
+        <v>-293.8025664</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-293.8025664</v>
+      </c>
+      <c r="Q101">
+        <v>-68.30256639999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.846199494412303</v>
+      </c>
+      <c r="T101">
+        <v>92.30598562580788</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.272049806271995</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_oilfield_svcs_equip.xlsx
@@ -1133,43 +1133,43 @@
         <v>3.31121281464531</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>207.53311103733</v>
       </c>
       <c r="G2">
         <v>5.16509290283278</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0661711848918672</v>
       </c>
       <c r="I2">
         <v>0.780565273430307</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>476.7</v>
       </c>
       <c r="L2">
-        <v>2724.43996906887</v>
+        <v>2700.36932996401</v>
       </c>
       <c r="M2">
         <v>1726.1</v>
       </c>
       <c r="N2">
-        <v>2278.13996906887</v>
+        <v>2275.79332996401</v>
       </c>
       <c r="O2">
         <v>1695.7</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>21.724</v>
       </c>
       <c r="Q2">
         <v>0.103398806100961</v>
       </c>
       <c r="R2">
-        <v>0.0894414358032203</v>
+        <v>0.0894864358032204</v>
       </c>
       <c r="S2">
         <v>0.06368110587651871</v>
@@ -1191,13 +1191,13 @@
         <v>0.244681172936681</v>
       </c>
       <c r="X2">
-        <v>0.0894414358032203</v>
+        <v>0.0898822583870913</v>
       </c>
       <c r="Y2">
         <v>3.64257852651833</v>
       </c>
       <c r="Z2">
-        <v>0.799308222975183</v>
+        <v>0.807382043409276</v>
       </c>
       <c r="AA2">
         <v>1695.7</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08944143580322034</v>
+        <v>0.08948643580322035</v>
       </c>
       <c r="C2">
-        <v>2724.439969068874</v>
+        <v>2700.369329964005</v>
       </c>
       <c r="D2">
-        <v>2278.139969068874</v>
+        <v>2275.793329964005</v>
       </c>
       <c r="E2">
-        <v>-1695.7</v>
+        <v>-1673.976</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21.724</v>
       </c>
       <c r="G2">
         <v>446.3</v>
@@ -1451,28 +1451,28 @@
         <v>226.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.0927172</v>
       </c>
       <c r="N2">
-        <v>226.775</v>
+        <v>225.6822828</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>226.775</v>
+        <v>225.6822828</v>
       </c>
       <c r="Q2">
-        <v>410.375</v>
+        <v>409.2822828</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08944143580322034</v>
+        <v>0.08988225838709127</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8073820434092761</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>207.5331110373297</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08948643580322035</v>
+        <v>0.08953143580322034</v>
       </c>
       <c r="C3">
-        <v>2700.369329964005</v>
+        <v>2676.303520280253</v>
       </c>
       <c r="D3">
-        <v>2275.793329964005</v>
+        <v>2273.451520280253</v>
       </c>
       <c r="E3">
-        <v>-1673.976</v>
+        <v>-1652.252</v>
       </c>
       <c r="F3">
-        <v>21.724</v>
+        <v>43.448</v>
       </c>
       <c r="G3">
         <v>446.3</v>
@@ -1533,28 +1533,28 @@
         <v>226.775</v>
       </c>
       <c r="M3">
-        <v>1.0927172</v>
+        <v>2.1854344</v>
       </c>
       <c r="N3">
-        <v>225.6822828</v>
+        <v>224.5895656</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>225.6822828</v>
+        <v>224.5895656</v>
       </c>
       <c r="Q3">
-        <v>409.2822828</v>
+        <v>408.1895656</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08988225838709127</v>
+        <v>0.09033207735022483</v>
       </c>
       <c r="T3">
-        <v>0.8073820434092761</v>
+        <v>0.8156206356889626</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>207.5331110373297</v>
+        <v>103.7665555186648</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08953143580322034</v>
+        <v>0.08957643580322033</v>
       </c>
       <c r="C4">
-        <v>2676.303520280253</v>
+        <v>2652.242525124402</v>
       </c>
       <c r="D4">
-        <v>2273.451520280253</v>
+        <v>2271.114525124402</v>
       </c>
       <c r="E4">
-        <v>-1652.252</v>
+        <v>-1630.528</v>
       </c>
       <c r="F4">
-        <v>43.448</v>
+        <v>65.172</v>
       </c>
       <c r="G4">
         <v>446.3</v>
@@ -1615,28 +1615,28 @@
         <v>226.775</v>
       </c>
       <c r="M4">
-        <v>2.1854344</v>
+        <v>3.2781516</v>
       </c>
       <c r="N4">
-        <v>224.5895656</v>
+        <v>223.4968484</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>224.5895656</v>
+        <v>223.4968484</v>
       </c>
       <c r="Q4">
-        <v>408.1895656</v>
+        <v>407.0968484</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09033207735022483</v>
+        <v>0.09079117093115499</v>
       </c>
       <c r="T4">
-        <v>0.8156206356889626</v>
+        <v>0.8240290958507044</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.7665555186648</v>
+        <v>69.17770367910991</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08957643580322033</v>
+        <v>0.08962143580322034</v>
       </c>
       <c r="C5">
-        <v>2652.242525124402</v>
+        <v>2628.18632966441</v>
       </c>
       <c r="D5">
-        <v>2271.114525124402</v>
+        <v>2268.78232966441</v>
       </c>
       <c r="E5">
-        <v>-1630.528</v>
+        <v>-1608.804</v>
       </c>
       <c r="F5">
-        <v>65.172</v>
+        <v>86.896</v>
       </c>
       <c r="G5">
         <v>446.3</v>
@@ -1697,28 +1697,28 @@
         <v>226.775</v>
       </c>
       <c r="M5">
-        <v>3.2781516</v>
+        <v>4.3708688</v>
       </c>
       <c r="N5">
-        <v>223.4968484</v>
+        <v>222.4041312</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>223.4968484</v>
+        <v>222.4041312</v>
       </c>
       <c r="Q5">
-        <v>407.0968484</v>
+        <v>406.0041312</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09079117093115499</v>
+        <v>0.09125982896168786</v>
       </c>
       <c r="T5">
-        <v>0.8240290958507044</v>
+        <v>0.832612732265816</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.17770367910991</v>
+        <v>51.88327775933242</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08962143580322034</v>
+        <v>0.08966643580322034</v>
       </c>
       <c r="C6">
-        <v>2628.18632966441</v>
+        <v>2604.1349191291</v>
       </c>
       <c r="D6">
-        <v>2268.78232966441</v>
+        <v>2266.4549191291</v>
       </c>
       <c r="E6">
-        <v>-1608.804</v>
+        <v>-1587.08</v>
       </c>
       <c r="F6">
-        <v>86.896</v>
+        <v>108.62</v>
       </c>
       <c r="G6">
         <v>446.3</v>
@@ -1779,28 +1779,28 @@
         <v>226.775</v>
       </c>
       <c r="M6">
-        <v>4.3708688</v>
+        <v>5.463586</v>
       </c>
       <c r="N6">
-        <v>222.4041312</v>
+        <v>221.311414</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>222.4041312</v>
+        <v>221.311414</v>
       </c>
       <c r="Q6">
-        <v>406.0041312</v>
+        <v>404.911414</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09125982896168786</v>
+        <v>0.09173835347707404</v>
       </c>
       <c r="T6">
-        <v>0.832612732265816</v>
+        <v>0.8413770768159824</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.88327775933242</v>
+        <v>41.50662220746594</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08966643580322034</v>
+        <v>0.08971143580322034</v>
       </c>
       <c r="C7">
-        <v>2604.1349191291</v>
+        <v>2580.088278807843</v>
       </c>
       <c r="D7">
-        <v>2266.4549191291</v>
+        <v>2264.132278807843</v>
       </c>
       <c r="E7">
-        <v>-1587.08</v>
+        <v>-1565.356</v>
       </c>
       <c r="F7">
-        <v>108.62</v>
+        <v>130.344</v>
       </c>
       <c r="G7">
         <v>446.3</v>
@@ -1861,28 +1861,28 @@
         <v>226.775</v>
       </c>
       <c r="M7">
-        <v>5.463586</v>
+        <v>6.556303200000001</v>
       </c>
       <c r="N7">
-        <v>221.311414</v>
+        <v>220.2186968</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>221.311414</v>
+        <v>220.2186968</v>
       </c>
       <c r="Q7">
-        <v>404.911414</v>
+        <v>403.8186968</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09173835347707404</v>
+        <v>0.09222705936512803</v>
       </c>
       <c r="T7">
-        <v>0.8413770768159824</v>
+        <v>0.85032789678211</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.50662220746594</v>
+        <v>34.58885183955494</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08971143580322033</v>
+        <v>0.08975643580322035</v>
       </c>
       <c r="C8">
-        <v>2580.088278807844</v>
+        <v>2556.046394050251</v>
       </c>
       <c r="D8">
-        <v>2264.132278807844</v>
+        <v>2261.814394050251</v>
       </c>
       <c r="E8">
-        <v>-1565.356</v>
+        <v>-1543.632</v>
       </c>
       <c r="F8">
-        <v>130.344</v>
+        <v>152.068</v>
       </c>
       <c r="G8">
         <v>446.3</v>
@@ -1943,28 +1943,28 @@
         <v>226.775</v>
       </c>
       <c r="M8">
-        <v>6.556303199999999</v>
+        <v>7.649020399999999</v>
       </c>
       <c r="N8">
-        <v>220.2186968</v>
+        <v>219.1259796</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>220.2186968</v>
+        <v>219.1259796</v>
       </c>
       <c r="Q8">
-        <v>403.8186968</v>
+        <v>402.7259796</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09222705936512803</v>
+        <v>0.09272627505722618</v>
       </c>
       <c r="T8">
-        <v>0.85032789678211</v>
+        <v>0.8594712075001971</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.58885183955496</v>
+        <v>29.6475872910471</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08975643580322033</v>
+        <v>0.08980143580322035</v>
       </c>
       <c r="C9">
-        <v>2556.046394050252</v>
+        <v>2532.009250265866</v>
       </c>
       <c r="D9">
-        <v>2261.814394050252</v>
+        <v>2259.501250265866</v>
       </c>
       <c r="E9">
-        <v>-1543.632</v>
+        <v>-1521.908</v>
       </c>
       <c r="F9">
-        <v>152.068</v>
+        <v>173.792</v>
       </c>
       <c r="G9">
         <v>446.3</v>
@@ -2025,28 +2025,28 @@
         <v>226.775</v>
       </c>
       <c r="M9">
-        <v>7.6490204</v>
+        <v>8.7417376</v>
       </c>
       <c r="N9">
-        <v>219.1259796</v>
+        <v>218.0332624</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>219.1259796</v>
+        <v>218.0332624</v>
       </c>
       <c r="Q9">
-        <v>402.7259796</v>
+        <v>401.6332624</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09272627505722618</v>
+        <v>0.09323634326436994</v>
       </c>
       <c r="T9">
-        <v>0.8594712075001971</v>
+        <v>0.8688132858425905</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.6475872910471</v>
+        <v>25.94163887966621</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08980143580322035</v>
+        <v>0.08984643580322035</v>
       </c>
       <c r="C10">
-        <v>2532.009250265866</v>
+        <v>2507.976832923854</v>
       </c>
       <c r="D10">
-        <v>2259.501250265866</v>
+        <v>2257.192832923854</v>
       </c>
       <c r="E10">
-        <v>-1521.908</v>
+        <v>-1500.184</v>
       </c>
       <c r="F10">
-        <v>173.792</v>
+        <v>195.516</v>
       </c>
       <c r="G10">
         <v>446.3</v>
@@ -2107,28 +2107,28 @@
         <v>226.775</v>
       </c>
       <c r="M10">
-        <v>8.7417376</v>
+        <v>9.8344548</v>
       </c>
       <c r="N10">
-        <v>218.0332624</v>
+        <v>216.9405452</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>218.0332624</v>
+        <v>216.9405452</v>
       </c>
       <c r="Q10">
-        <v>401.6332624</v>
+        <v>400.5405452</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09323634326436994</v>
+        <v>0.0937576217617806</v>
       </c>
       <c r="T10">
-        <v>0.8688132858425905</v>
+        <v>0.8783606845881137</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.94163887966621</v>
+        <v>23.0592345597033</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08984643580322035</v>
+        <v>0.08989143580322034</v>
       </c>
       <c r="C11">
-        <v>2507.976832923854</v>
+        <v>2483.949127552705</v>
       </c>
       <c r="D11">
-        <v>2257.192832923854</v>
+        <v>2254.889127552704</v>
       </c>
       <c r="E11">
-        <v>-1500.184</v>
+        <v>-1478.46</v>
       </c>
       <c r="F11">
-        <v>195.516</v>
+        <v>217.24</v>
       </c>
       <c r="G11">
         <v>446.3</v>
@@ -2189,28 +2189,28 @@
         <v>226.775</v>
       </c>
       <c r="M11">
-        <v>9.8344548</v>
+        <v>10.927172</v>
       </c>
       <c r="N11">
-        <v>216.9405452</v>
+        <v>215.847828</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>216.9405452</v>
+        <v>215.847828</v>
       </c>
       <c r="Q11">
-        <v>400.5405452</v>
+        <v>399.447828</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0937576217617806</v>
+        <v>0.09429048422580039</v>
       </c>
       <c r="T11">
-        <v>0.8783606845881137</v>
+        <v>0.8881202477502037</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.0592345597033</v>
+        <v>20.75331110373297</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08989143580322034</v>
+        <v>0.08993643580322035</v>
       </c>
       <c r="C12">
-        <v>2483.949127552704</v>
+        <v>2459.926119739925</v>
       </c>
       <c r="D12">
-        <v>2254.889127552704</v>
+        <v>2252.590119739924</v>
       </c>
       <c r="E12">
-        <v>-1478.46</v>
+        <v>-1456.736</v>
       </c>
       <c r="F12">
-        <v>217.24</v>
+        <v>238.964</v>
       </c>
       <c r="G12">
         <v>446.3</v>
@@ -2271,28 +2271,28 @@
         <v>226.775</v>
       </c>
       <c r="M12">
-        <v>10.927172</v>
+        <v>12.0198892</v>
       </c>
       <c r="N12">
-        <v>215.847828</v>
+        <v>214.7551108</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>215.847828</v>
+        <v>214.7551108</v>
       </c>
       <c r="Q12">
-        <v>399.447828</v>
+        <v>398.3551108</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09429048422580039</v>
+        <v>0.09483532112721388</v>
       </c>
       <c r="T12">
-        <v>0.8881202477502037</v>
+        <v>0.8980991269384083</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.75331110373297</v>
+        <v>18.86664645793907</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08993643580322035</v>
+        <v>0.08998143580322034</v>
       </c>
       <c r="C13">
-        <v>2459.926119739925</v>
+        <v>2435.907795131739</v>
       </c>
       <c r="D13">
-        <v>2252.590119739924</v>
+        <v>2250.295795131739</v>
       </c>
       <c r="E13">
-        <v>-1456.736</v>
+        <v>-1435.012</v>
       </c>
       <c r="F13">
-        <v>238.964</v>
+        <v>260.688</v>
       </c>
       <c r="G13">
         <v>446.3</v>
@@ -2353,28 +2353,28 @@
         <v>226.775</v>
       </c>
       <c r="M13">
-        <v>12.0198892</v>
+        <v>13.1126064</v>
       </c>
       <c r="N13">
-        <v>214.7551108</v>
+        <v>213.6623936</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>214.7551108</v>
+        <v>213.6623936</v>
       </c>
       <c r="Q13">
-        <v>398.3551108</v>
+        <v>397.2623936</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09483532112721388</v>
+        <v>0.09539254068547766</v>
       </c>
       <c r="T13">
-        <v>0.8980991269384083</v>
+        <v>0.9083047988354355</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.86664645793907</v>
+        <v>17.29442591977748</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08998143580322034</v>
+        <v>0.09002643580322034</v>
       </c>
       <c r="C14">
-        <v>2435.907795131739</v>
+        <v>2411.894139432793</v>
       </c>
       <c r="D14">
-        <v>2250.295795131739</v>
+        <v>2248.006139432793</v>
       </c>
       <c r="E14">
-        <v>-1435.012</v>
+        <v>-1413.288</v>
       </c>
       <c r="F14">
-        <v>260.688</v>
+        <v>282.412</v>
       </c>
       <c r="G14">
         <v>446.3</v>
@@ -2435,28 +2435,28 @@
         <v>226.775</v>
       </c>
       <c r="M14">
-        <v>13.1126064</v>
+        <v>14.2053236</v>
       </c>
       <c r="N14">
-        <v>213.6623936</v>
+        <v>212.5696764</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>213.6623936</v>
+        <v>212.5696764</v>
       </c>
       <c r="Q14">
-        <v>397.2623936</v>
+        <v>396.1696764</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09539254068547766</v>
+        <v>0.09596256988875901</v>
       </c>
       <c r="T14">
-        <v>0.9083047988354355</v>
+        <v>0.918745083879521</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.29442591977748</v>
+        <v>15.96408546440997</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09002643580322034</v>
+        <v>0.09007143580322036</v>
       </c>
       <c r="C15">
-        <v>2411.894139432793</v>
+        <v>2387.885138405852</v>
       </c>
       <c r="D15">
-        <v>2248.006139432793</v>
+        <v>2245.721138405852</v>
       </c>
       <c r="E15">
-        <v>-1413.288</v>
+        <v>-1391.564</v>
       </c>
       <c r="F15">
-        <v>282.412</v>
+        <v>304.136</v>
       </c>
       <c r="G15">
         <v>446.3</v>
@@ -2517,28 +2517,28 @@
         <v>226.775</v>
       </c>
       <c r="M15">
-        <v>14.2053236</v>
+        <v>15.2980408</v>
       </c>
       <c r="N15">
-        <v>212.5696764</v>
+        <v>211.4769592</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>212.5696764</v>
+        <v>211.4769592</v>
       </c>
       <c r="Q15">
-        <v>396.1696764</v>
+        <v>395.0769592</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09596256988875901</v>
+        <v>0.09654585558513994</v>
       </c>
       <c r="T15">
-        <v>0.918745083879521</v>
+        <v>0.9294281662502132</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.96408546440997</v>
+        <v>14.82379364552355</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09007143580322036</v>
+        <v>0.09011643580322035</v>
       </c>
       <c r="C16">
-        <v>2387.885138405852</v>
+        <v>2363.880777871512</v>
       </c>
       <c r="D16">
-        <v>2245.721138405852</v>
+        <v>2243.440777871512</v>
       </c>
       <c r="E16">
-        <v>-1391.564</v>
+        <v>-1369.84</v>
       </c>
       <c r="F16">
-        <v>304.136</v>
+        <v>325.8600000000001</v>
       </c>
       <c r="G16">
         <v>446.3</v>
@@ -2599,28 +2599,28 @@
         <v>226.775</v>
       </c>
       <c r="M16">
-        <v>15.2980408</v>
+        <v>16.390758</v>
       </c>
       <c r="N16">
-        <v>211.4769592</v>
+        <v>210.384242</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>211.4769592</v>
+        <v>210.384242</v>
       </c>
       <c r="Q16">
-        <v>395.0769592</v>
+        <v>393.984242</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09654585558513994</v>
+        <v>0.09714286565084747</v>
       </c>
       <c r="T16">
-        <v>0.9294281662502132</v>
+        <v>0.9403626152649216</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.82379364552355</v>
+        <v>13.83554073582198</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09011643580322035</v>
+        <v>0.09016143580322034</v>
       </c>
       <c r="C17">
-        <v>2363.880777871512</v>
+        <v>2339.881043707902</v>
       </c>
       <c r="D17">
-        <v>2243.440777871512</v>
+        <v>2241.165043707902</v>
       </c>
       <c r="E17">
-        <v>-1369.84</v>
+        <v>-1348.116</v>
       </c>
       <c r="F17">
-        <v>325.86</v>
+        <v>347.584</v>
       </c>
       <c r="G17">
         <v>446.3</v>
@@ -2681,28 +2681,28 @@
         <v>226.775</v>
       </c>
       <c r="M17">
-        <v>16.390758</v>
+        <v>17.4834752</v>
       </c>
       <c r="N17">
-        <v>210.384242</v>
+        <v>209.2915248</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>210.384242</v>
+        <v>209.2915248</v>
       </c>
       <c r="Q17">
-        <v>393.984242</v>
+        <v>392.8915248</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09714286565084747</v>
+        <v>0.09775409024192898</v>
       </c>
       <c r="T17">
-        <v>0.9403626152649216</v>
+        <v>0.9515574083037897</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.83554073582198</v>
+        <v>12.97081943983311</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09016143580322034</v>
+        <v>0.09046143580322033</v>
       </c>
       <c r="C18">
-        <v>2339.881043707902</v>
+        <v>2303.102679668315</v>
       </c>
       <c r="D18">
-        <v>2241.165043707902</v>
+        <v>2226.110679668314</v>
       </c>
       <c r="E18">
-        <v>-1348.116</v>
+        <v>-1326.392</v>
       </c>
       <c r="F18">
-        <v>347.584</v>
+        <v>369.308</v>
       </c>
       <c r="G18">
         <v>446.3</v>
@@ -2763,45 +2763,45 @@
         <v>226.775</v>
       </c>
       <c r="M18">
-        <v>17.4834752</v>
+        <v>19.1301544</v>
       </c>
       <c r="N18">
-        <v>209.2915248</v>
+        <v>207.6448456</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>209.2915248</v>
+        <v>207.6448456</v>
       </c>
       <c r="Q18">
-        <v>392.8915248</v>
+        <v>391.2448456</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09775409024192898</v>
+        <v>0.09838004313641005</v>
       </c>
       <c r="T18">
-        <v>0.9515574083037897</v>
+        <v>0.9630219553917873</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.97081943983311</v>
+        <v>11.85432146851883</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09046143580322033</v>
+        <v>0.09052143580322033</v>
       </c>
       <c r="C19">
-        <v>2303.102679668315</v>
+        <v>2278.392043877643</v>
       </c>
       <c r="D19">
-        <v>2226.110679668314</v>
+        <v>2223.124043877643</v>
       </c>
       <c r="E19">
-        <v>-1326.392</v>
+        <v>-1304.668</v>
       </c>
       <c r="F19">
-        <v>369.308</v>
+        <v>391.032</v>
       </c>
       <c r="G19">
         <v>446.3</v>
@@ -2845,28 +2845,28 @@
         <v>226.775</v>
       </c>
       <c r="M19">
-        <v>19.1301544</v>
+        <v>20.2554576</v>
       </c>
       <c r="N19">
-        <v>207.6448456</v>
+        <v>206.5195424</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>207.6448456</v>
+        <v>206.5195424</v>
       </c>
       <c r="Q19">
-        <v>391.2448456</v>
+        <v>390.1195424</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09838004313641005</v>
+        <v>0.09902126317465895</v>
       </c>
       <c r="T19">
-        <v>0.9630219553917873</v>
+        <v>0.9747661255794918</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.85432146851883</v>
+        <v>11.19574805360112</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09052143580322035</v>
+        <v>0.09058143580322035</v>
       </c>
       <c r="C20">
-        <v>2278.392043877642</v>
+        <v>2253.689411320643</v>
       </c>
       <c r="D20">
-        <v>2223.124043877642</v>
+        <v>2220.145411320642</v>
       </c>
       <c r="E20">
-        <v>-1304.668</v>
+        <v>-1282.944</v>
       </c>
       <c r="F20">
-        <v>391.032</v>
+        <v>412.756</v>
       </c>
       <c r="G20">
         <v>446.3</v>
@@ -2927,28 +2927,28 @@
         <v>226.775</v>
       </c>
       <c r="M20">
-        <v>20.2554576</v>
+        <v>21.3807608</v>
       </c>
       <c r="N20">
-        <v>206.5195424</v>
+        <v>205.3942392</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>206.5195424</v>
+        <v>205.3942392</v>
       </c>
       <c r="Q20">
-        <v>390.1195424</v>
+        <v>388.9942392</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09902126317465895</v>
+        <v>0.09967831580644487</v>
       </c>
       <c r="T20">
-        <v>0.9747661255794918</v>
+        <v>0.9868002752780041</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.19574805360112</v>
+        <v>10.60649815604317</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09058143580322035</v>
+        <v>0.09064143580322034</v>
       </c>
       <c r="C21">
-        <v>2253.689411320643</v>
+        <v>2228.994749871179</v>
       </c>
       <c r="D21">
-        <v>2220.145411320642</v>
+        <v>2217.174749871179</v>
       </c>
       <c r="E21">
-        <v>-1282.944</v>
+        <v>-1261.22</v>
       </c>
       <c r="F21">
-        <v>412.756</v>
+        <v>434.48</v>
       </c>
       <c r="G21">
         <v>446.3</v>
@@ -3009,28 +3009,28 @@
         <v>226.775</v>
       </c>
       <c r="M21">
-        <v>21.3807608</v>
+        <v>22.506064</v>
       </c>
       <c r="N21">
-        <v>205.3942392</v>
+        <v>204.268936</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>205.3942392</v>
+        <v>204.268936</v>
       </c>
       <c r="Q21">
-        <v>388.9942392</v>
+        <v>387.868936</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09967831580644487</v>
+        <v>0.1003517947540254</v>
       </c>
       <c r="T21">
-        <v>0.9868002752780041</v>
+        <v>0.9991352787189791</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.60649815604317</v>
+        <v>10.07617324824101</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09064143580322034</v>
+        <v>0.09105843580322034</v>
       </c>
       <c r="C22">
-        <v>2228.994749871179</v>
+        <v>2186.842251751708</v>
       </c>
       <c r="D22">
-        <v>2217.174749871179</v>
+        <v>2196.746251751708</v>
       </c>
       <c r="E22">
-        <v>-1261.22</v>
+        <v>-1239.496</v>
       </c>
       <c r="F22">
-        <v>434.48</v>
+        <v>456.2040000000001</v>
       </c>
       <c r="G22">
         <v>446.3</v>
@@ -3091,45 +3091,45 @@
         <v>226.775</v>
       </c>
       <c r="M22">
-        <v>22.506064</v>
+        <v>24.406914</v>
       </c>
       <c r="N22">
-        <v>204.268936</v>
+        <v>202.368086</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>204.268936</v>
+        <v>202.368086</v>
       </c>
       <c r="Q22">
-        <v>387.868936</v>
+        <v>385.968086</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1003517947540254</v>
+        <v>0.1010423238015447</v>
       </c>
       <c r="T22">
-        <v>0.9991352787189791</v>
+        <v>1.01178256072808</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.07617324824101</v>
+        <v>9.291424552895133</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09105843580322034</v>
+        <v>0.09113543580322035</v>
       </c>
       <c r="C23">
-        <v>2186.842251751708</v>
+        <v>2161.387186672306</v>
       </c>
       <c r="D23">
-        <v>2196.746251751708</v>
+        <v>2193.015186672305</v>
       </c>
       <c r="E23">
-        <v>-1239.496</v>
+        <v>-1217.772</v>
       </c>
       <c r="F23">
-        <v>456.204</v>
+        <v>477.928</v>
       </c>
       <c r="G23">
         <v>446.3</v>
@@ -3173,28 +3173,28 @@
         <v>226.775</v>
       </c>
       <c r="M23">
-        <v>24.406914</v>
+        <v>25.569148</v>
       </c>
       <c r="N23">
-        <v>202.368086</v>
+        <v>201.205852</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>202.368086</v>
+        <v>201.205852</v>
       </c>
       <c r="Q23">
-        <v>385.968086</v>
+        <v>384.805852</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1010423238015447</v>
+        <v>0.1017505587220774</v>
       </c>
       <c r="T23">
-        <v>1.01178256072808</v>
+        <v>1.024754132019466</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.291424552895135</v>
+        <v>8.869087073218083</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09113543580322035</v>
+        <v>0.09121243580322033</v>
       </c>
       <c r="C24">
-        <v>2161.387186672306</v>
+        <v>2135.94477416289</v>
       </c>
       <c r="D24">
-        <v>2193.015186672305</v>
+        <v>2189.29677416289</v>
       </c>
       <c r="E24">
-        <v>-1217.772</v>
+        <v>-1196.048</v>
       </c>
       <c r="F24">
-        <v>477.928</v>
+        <v>499.652</v>
       </c>
       <c r="G24">
         <v>446.3</v>
@@ -3255,28 +3255,28 @@
         <v>226.775</v>
       </c>
       <c r="M24">
-        <v>25.569148</v>
+        <v>26.731382</v>
       </c>
       <c r="N24">
-        <v>201.205852</v>
+        <v>200.043618</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>201.205852</v>
+        <v>200.043618</v>
       </c>
       <c r="Q24">
-        <v>384.805852</v>
+        <v>383.643618</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1017505587220774</v>
+        <v>0.1024771893548316</v>
       </c>
       <c r="T24">
-        <v>1.024754132019466</v>
+        <v>1.038062627240498</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.869087073218083</v>
+        <v>8.483474591773817</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09121243580322033</v>
+        <v>0.09128943580322035</v>
       </c>
       <c r="C25">
-        <v>2135.94477416289</v>
+        <v>2110.514949972416</v>
       </c>
       <c r="D25">
-        <v>2189.29677416289</v>
+        <v>2185.590949972416</v>
       </c>
       <c r="E25">
-        <v>-1196.048</v>
+        <v>-1174.324</v>
       </c>
       <c r="F25">
-        <v>499.652</v>
+        <v>521.3760000000001</v>
       </c>
       <c r="G25">
         <v>446.3</v>
@@ -3337,28 +3337,28 @@
         <v>226.775</v>
       </c>
       <c r="M25">
-        <v>26.731382</v>
+        <v>27.89361600000001</v>
       </c>
       <c r="N25">
-        <v>200.043618</v>
+        <v>198.881384</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>200.043618</v>
+        <v>198.881384</v>
       </c>
       <c r="Q25">
-        <v>383.643618</v>
+        <v>382.481384</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1024771893548316</v>
+        <v>0.1032229418463426</v>
       </c>
       <c r="T25">
-        <v>1.038062627240498</v>
+        <v>1.051721346019978</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.483474591773817</v>
+        <v>8.129996483783241</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09128943580322035</v>
+        <v>0.09136643580322035</v>
       </c>
       <c r="C26">
-        <v>2110.514949972416</v>
+        <v>2085.09765028414</v>
       </c>
       <c r="D26">
-        <v>2185.590949972416</v>
+        <v>2181.89765028414</v>
       </c>
       <c r="E26">
-        <v>-1174.324</v>
+        <v>-1152.6</v>
       </c>
       <c r="F26">
-        <v>521.376</v>
+        <v>543.1</v>
       </c>
       <c r="G26">
         <v>446.3</v>
@@ -3419,28 +3419,28 @@
         <v>226.775</v>
       </c>
       <c r="M26">
-        <v>27.893616</v>
+        <v>29.05585</v>
       </c>
       <c r="N26">
-        <v>198.881384</v>
+        <v>197.71915</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>198.881384</v>
+        <v>197.71915</v>
       </c>
       <c r="Q26">
-        <v>382.481384</v>
+        <v>381.31915</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1032229418463426</v>
+        <v>0.1039885810709605</v>
       </c>
       <c r="T26">
-        <v>1.051721346019978</v>
+        <v>1.065744297300244</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.129996483783243</v>
+        <v>7.804796624431914</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09136643580322035</v>
+        <v>0.09165143580322034</v>
       </c>
       <c r="C27">
-        <v>2085.09765028414</v>
+        <v>2049.811570505446</v>
       </c>
       <c r="D27">
-        <v>2181.89765028414</v>
+        <v>2168.335570505446</v>
       </c>
       <c r="E27">
-        <v>-1152.6</v>
+        <v>-1130.876</v>
       </c>
       <c r="F27">
-        <v>543.1</v>
+        <v>564.8240000000001</v>
       </c>
       <c r="G27">
         <v>446.3</v>
@@ -3501,45 +3501,45 @@
         <v>226.775</v>
       </c>
       <c r="M27">
-        <v>29.05585</v>
+        <v>30.66994320000001</v>
       </c>
       <c r="N27">
-        <v>197.71915</v>
+        <v>196.1050568</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>197.71915</v>
+        <v>196.1050568</v>
       </c>
       <c r="Q27">
-        <v>381.31915</v>
+        <v>379.7050568</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1039885810709605</v>
+        <v>0.1047749132475951</v>
       </c>
       <c r="T27">
-        <v>1.065744297300244</v>
+        <v>1.080146247263761</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.804796624431914</v>
+        <v>7.394046950827088</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09165143580322034</v>
+        <v>0.09173643580322036</v>
       </c>
       <c r="C28">
-        <v>2049.811570505446</v>
+        <v>2024.075319222335</v>
       </c>
       <c r="D28">
-        <v>2168.335570505446</v>
+        <v>2164.323319222335</v>
       </c>
       <c r="E28">
-        <v>-1130.876</v>
+        <v>-1109.152</v>
       </c>
       <c r="F28">
-        <v>564.8240000000001</v>
+        <v>586.5480000000001</v>
       </c>
       <c r="G28">
         <v>446.3</v>
@@ -3583,28 +3583,28 @@
         <v>226.775</v>
       </c>
       <c r="M28">
-        <v>30.66994320000001</v>
+        <v>31.84955640000001</v>
       </c>
       <c r="N28">
-        <v>196.1050568</v>
+        <v>194.9254436</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>196.1050568</v>
+        <v>194.9254436</v>
       </c>
       <c r="Q28">
-        <v>379.7050568</v>
+        <v>378.5254436</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1047749132475951</v>
+        <v>0.1055827887715347</v>
       </c>
       <c r="T28">
-        <v>1.080146247263761</v>
+        <v>1.094942771198882</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.394046950827088</v>
+        <v>7.120193360055713</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09173643580322036</v>
+        <v>0.09182143580322036</v>
       </c>
       <c r="C29">
-        <v>2024.075319222335</v>
+        <v>1998.35388891789</v>
       </c>
       <c r="D29">
-        <v>2164.323319222335</v>
+        <v>2160.32588891789</v>
       </c>
       <c r="E29">
-        <v>-1109.152</v>
+        <v>-1087.428</v>
       </c>
       <c r="F29">
-        <v>586.5480000000001</v>
+        <v>608.272</v>
       </c>
       <c r="G29">
         <v>446.3</v>
@@ -3665,28 +3665,28 @@
         <v>226.775</v>
       </c>
       <c r="M29">
-        <v>31.84955640000001</v>
+        <v>33.0291696</v>
       </c>
       <c r="N29">
-        <v>194.9254436</v>
+        <v>193.7458304</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>194.9254436</v>
+        <v>193.7458304</v>
       </c>
       <c r="Q29">
-        <v>378.5254436</v>
+        <v>377.3458304</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1055827887715347</v>
+        <v>0.1064131052822505</v>
       </c>
       <c r="T29">
-        <v>1.094942771198882</v>
+        <v>1.110150309687755</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.120193360055713</v>
+        <v>6.865900740053724</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09182143580322036</v>
+        <v>0.09190643580322035</v>
       </c>
       <c r="C30">
-        <v>1998.35388891789</v>
+        <v>1972.647197622</v>
       </c>
       <c r="D30">
-        <v>2160.32588891789</v>
+        <v>2156.343197621999</v>
       </c>
       <c r="E30">
-        <v>-1087.428</v>
+        <v>-1065.704</v>
       </c>
       <c r="F30">
-        <v>608.272</v>
+        <v>629.9960000000001</v>
       </c>
       <c r="G30">
         <v>446.3</v>
@@ -3747,28 +3747,28 @@
         <v>226.775</v>
       </c>
       <c r="M30">
-        <v>33.0291696</v>
+        <v>34.20878280000001</v>
       </c>
       <c r="N30">
-        <v>193.7458304</v>
+        <v>192.5662172</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>193.7458304</v>
+        <v>192.5662172</v>
       </c>
       <c r="Q30">
-        <v>377.3458304</v>
+        <v>376.1662172</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1064131052822505</v>
+        <v>0.1072668109904512</v>
       </c>
       <c r="T30">
-        <v>1.110150309687755</v>
+        <v>1.125786229542512</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.865900740053724</v>
+        <v>6.629145542120837</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09190643580322033</v>
+        <v>0.09199143580322035</v>
       </c>
       <c r="C31">
-        <v>1972.647197622</v>
+        <v>1946.95516396791</v>
       </c>
       <c r="D31">
-        <v>2156.343197622</v>
+        <v>2152.37516396791</v>
       </c>
       <c r="E31">
-        <v>-1065.704</v>
+        <v>-1043.98</v>
       </c>
       <c r="F31">
-        <v>629.996</v>
+        <v>651.72</v>
       </c>
       <c r="G31">
         <v>446.3</v>
@@ -3829,28 +3829,28 @@
         <v>226.775</v>
       </c>
       <c r="M31">
-        <v>34.2087828</v>
+        <v>35.388396</v>
       </c>
       <c r="N31">
-        <v>192.5662172</v>
+        <v>191.386604</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>192.5662172</v>
+        <v>191.386604</v>
       </c>
       <c r="Q31">
-        <v>376.1662172</v>
+        <v>374.986604</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1072668109904512</v>
+        <v>0.1081449082903148</v>
       </c>
       <c r="T31">
-        <v>1.125786229542512</v>
+        <v>1.141868889964548</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.629145542120838</v>
+        <v>6.408174024050144</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09199143580322035</v>
+        <v>0.09207643580322035</v>
       </c>
       <c r="C32">
-        <v>1946.95516396791</v>
+        <v>1921.277707186683</v>
       </c>
       <c r="D32">
-        <v>2152.37516396791</v>
+        <v>2148.421707186683</v>
       </c>
       <c r="E32">
-        <v>-1043.98</v>
+        <v>-1022.256</v>
       </c>
       <c r="F32">
-        <v>651.72</v>
+        <v>673.4440000000001</v>
       </c>
       <c r="G32">
         <v>446.3</v>
@@ -3911,28 +3911,28 @@
         <v>226.775</v>
       </c>
       <c r="M32">
-        <v>35.388396</v>
+        <v>36.56800920000001</v>
       </c>
       <c r="N32">
-        <v>191.386604</v>
+        <v>190.2069908</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>191.386604</v>
+        <v>190.2069908</v>
       </c>
       <c r="Q32">
-        <v>374.986604</v>
+        <v>373.8069908</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1081449082903148</v>
+        <v>0.1090484576858266</v>
       </c>
       <c r="T32">
-        <v>1.141868889964548</v>
+        <v>1.158417714456788</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.408174024050144</v>
+        <v>6.201458732951751</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09207643580322035</v>
+        <v>0.09248143580322035</v>
       </c>
       <c r="C33">
-        <v>1921.277707186683</v>
+        <v>1880.914374945951</v>
       </c>
       <c r="D33">
-        <v>2148.421707186683</v>
+        <v>2129.782374945951</v>
       </c>
       <c r="E33">
-        <v>-1022.256</v>
+        <v>-1000.532</v>
       </c>
       <c r="F33">
-        <v>673.4440000000001</v>
+        <v>695.168</v>
       </c>
       <c r="G33">
         <v>446.3</v>
@@ -3993,45 +3993,45 @@
         <v>226.775</v>
       </c>
       <c r="M33">
-        <v>36.56800920000001</v>
+        <v>38.4427904</v>
       </c>
       <c r="N33">
-        <v>190.2069908</v>
+        <v>188.3322096</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>190.2069908</v>
+        <v>188.3322096</v>
       </c>
       <c r="Q33">
-        <v>373.8069908</v>
+        <v>371.9322096</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1090484576858266</v>
+        <v>0.1099785820635593</v>
       </c>
       <c r="T33">
-        <v>1.158417714456788</v>
+        <v>1.175453269081152</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.201458732951751</v>
+        <v>5.899025477609451</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09248143580322035</v>
+        <v>0.09257643580322034</v>
       </c>
       <c r="C34">
-        <v>1880.914374945951</v>
+        <v>1854.864920854686</v>
       </c>
       <c r="D34">
-        <v>2129.782374945951</v>
+        <v>2125.456920854686</v>
       </c>
       <c r="E34">
-        <v>-1000.532</v>
+        <v>-978.808</v>
       </c>
       <c r="F34">
-        <v>695.168</v>
+        <v>716.8920000000001</v>
       </c>
       <c r="G34">
         <v>446.3</v>
@@ -4075,28 +4075,28 @@
         <v>226.775</v>
       </c>
       <c r="M34">
-        <v>38.4427904</v>
+        <v>39.6441276</v>
       </c>
       <c r="N34">
-        <v>188.3322096</v>
+        <v>187.1308724</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>188.3322096</v>
+        <v>187.1308724</v>
       </c>
       <c r="Q34">
-        <v>371.9322096</v>
+        <v>370.7308724</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1099785820635593</v>
+        <v>0.1109364713480901</v>
       </c>
       <c r="T34">
-        <v>1.175453269081152</v>
+        <v>1.192997347724154</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.899025477609451</v>
+        <v>5.720267129803102</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09257643580322034</v>
+        <v>0.09267143580322033</v>
       </c>
       <c r="C35">
-        <v>1854.864920854686</v>
+        <v>1828.833000603877</v>
       </c>
       <c r="D35">
-        <v>2125.456920854686</v>
+        <v>2121.149000603877</v>
       </c>
       <c r="E35">
-        <v>-978.808</v>
+        <v>-957.0839999999999</v>
       </c>
       <c r="F35">
-        <v>716.8920000000001</v>
+        <v>738.6160000000001</v>
       </c>
       <c r="G35">
         <v>446.3</v>
@@ -4157,28 +4157,28 @@
         <v>226.775</v>
       </c>
       <c r="M35">
-        <v>39.6441276</v>
+        <v>40.84546480000001</v>
       </c>
       <c r="N35">
-        <v>187.1308724</v>
+        <v>185.9295352</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>187.1308724</v>
+        <v>185.9295352</v>
       </c>
       <c r="Q35">
-        <v>370.7308724</v>
+        <v>369.5295352</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1109364713480901</v>
+        <v>0.1119233875806369</v>
       </c>
       <c r="T35">
-        <v>1.192997347724154</v>
+        <v>1.211073065113914</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.720267129803102</v>
+        <v>5.552023978926541</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09267143580322033</v>
+        <v>0.09276643580322033</v>
       </c>
       <c r="C36">
-        <v>1828.833000603877</v>
+        <v>1802.818507795318</v>
       </c>
       <c r="D36">
-        <v>2121.149000603877</v>
+        <v>2116.858507795318</v>
       </c>
       <c r="E36">
-        <v>-957.0839999999999</v>
+        <v>-935.3599999999999</v>
       </c>
       <c r="F36">
-        <v>738.6160000000001</v>
+        <v>760.3400000000001</v>
       </c>
       <c r="G36">
         <v>446.3</v>
@@ -4239,28 +4239,28 @@
         <v>226.775</v>
       </c>
       <c r="M36">
-        <v>40.84546480000001</v>
+        <v>42.04680200000001</v>
       </c>
       <c r="N36">
-        <v>185.9295352</v>
+        <v>184.728198</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>185.9295352</v>
+        <v>184.728198</v>
       </c>
       <c r="Q36">
-        <v>369.5295352</v>
+        <v>368.328198</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1119233875806369</v>
+        <v>0.1129406704664928</v>
       </c>
       <c r="T36">
-        <v>1.211073065113914</v>
+        <v>1.229704958423359</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.552023978926541</v>
+        <v>5.393394722385782</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09276643580322033</v>
+        <v>0.09286143580322034</v>
       </c>
       <c r="C37">
-        <v>1802.818507795318</v>
+        <v>1776.82133688992</v>
       </c>
       <c r="D37">
-        <v>2116.858507795318</v>
+        <v>2112.58533688992</v>
       </c>
       <c r="E37">
-        <v>-935.3599999999999</v>
+        <v>-913.636</v>
       </c>
       <c r="F37">
-        <v>760.3400000000001</v>
+        <v>782.0640000000001</v>
       </c>
       <c r="G37">
         <v>446.3</v>
@@ -4321,28 +4321,28 @@
         <v>226.775</v>
       </c>
       <c r="M37">
-        <v>42.04680200000001</v>
+        <v>43.2481392</v>
       </c>
       <c r="N37">
-        <v>184.728198</v>
+        <v>183.5268608</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>184.728198</v>
+        <v>183.5268608</v>
       </c>
       <c r="Q37">
-        <v>368.328198</v>
+        <v>367.1268608</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1129406704664928</v>
+        <v>0.1139897434425318</v>
       </c>
       <c r="T37">
-        <v>1.229704958423359</v>
+        <v>1.248919098398724</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.393394722385782</v>
+        <v>5.243578202319512</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09286143580322034</v>
+        <v>0.09295643580322033</v>
       </c>
       <c r="C38">
-        <v>1776.821336889921</v>
+        <v>1750.841383199061</v>
       </c>
       <c r="D38">
-        <v>2112.58533688992</v>
+        <v>2108.32938319906</v>
       </c>
       <c r="E38">
-        <v>-913.6360000000001</v>
+        <v>-891.912</v>
       </c>
       <c r="F38">
-        <v>782.064</v>
+        <v>803.788</v>
       </c>
       <c r="G38">
         <v>446.3</v>
@@ -4403,28 +4403,28 @@
         <v>226.775</v>
       </c>
       <c r="M38">
-        <v>43.2481392</v>
+        <v>44.4494764</v>
       </c>
       <c r="N38">
-        <v>183.5268608</v>
+        <v>182.3255236</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>183.5268608</v>
+        <v>182.3255236</v>
       </c>
       <c r="Q38">
-        <v>367.1268608</v>
+        <v>365.9255236</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1139897434425318</v>
+        <v>0.115072120322572</v>
       </c>
       <c r="T38">
-        <v>1.248919098398724</v>
+        <v>1.26874321107172</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.243578202319512</v>
+        <v>5.101859872527092</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09295643580322033</v>
+        <v>0.09305143580322034</v>
       </c>
       <c r="C39">
-        <v>1750.841383199061</v>
+        <v>1724.878542876027</v>
       </c>
       <c r="D39">
-        <v>2108.32938319906</v>
+        <v>2104.090542876027</v>
       </c>
       <c r="E39">
-        <v>-891.912</v>
+        <v>-870.188</v>
       </c>
       <c r="F39">
-        <v>803.788</v>
+        <v>825.5120000000001</v>
       </c>
       <c r="G39">
         <v>446.3</v>
@@ -4485,28 +4485,28 @@
         <v>226.775</v>
       </c>
       <c r="M39">
-        <v>44.4494764</v>
+        <v>45.65081360000001</v>
       </c>
       <c r="N39">
-        <v>182.3255236</v>
+        <v>181.1241864</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>182.3255236</v>
+        <v>181.1241864</v>
       </c>
       <c r="Q39">
-        <v>365.9255236</v>
+        <v>364.7241864</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.115072120322572</v>
+        <v>0.1161894125858393</v>
       </c>
       <c r="T39">
-        <v>1.26874321107172</v>
+        <v>1.289206811250296</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.101859872527092</v>
+        <v>4.967600402197431</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09305143580322034</v>
+        <v>0.09314643580322035</v>
       </c>
       <c r="C40">
-        <v>1724.878542876027</v>
+        <v>1698.932712907578</v>
       </c>
       <c r="D40">
-        <v>2104.090542876027</v>
+        <v>2099.868712907578</v>
       </c>
       <c r="E40">
-        <v>-870.188</v>
+        <v>-848.4639999999999</v>
       </c>
       <c r="F40">
-        <v>825.5120000000001</v>
+        <v>847.2360000000001</v>
       </c>
       <c r="G40">
         <v>446.3</v>
@@ -4567,28 +4567,28 @@
         <v>226.775</v>
       </c>
       <c r="M40">
-        <v>45.65081360000001</v>
+        <v>46.8521508</v>
       </c>
       <c r="N40">
-        <v>181.1241864</v>
+        <v>179.9228492</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>181.1241864</v>
+        <v>179.9228492</v>
       </c>
       <c r="Q40">
-        <v>364.7241864</v>
+        <v>363.5228492</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1161894125858393</v>
+        <v>0.1173433373823284</v>
       </c>
       <c r="T40">
-        <v>1.289206811250296</v>
+        <v>1.310341349139645</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.967600402197431</v>
+        <v>4.840226032910317</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09314643580322035</v>
+        <v>0.09324143580322035</v>
       </c>
       <c r="C41">
-        <v>1698.932712907578</v>
+        <v>1673.003791105598</v>
       </c>
       <c r="D41">
-        <v>2099.868712907578</v>
+        <v>2095.663791105598</v>
       </c>
       <c r="E41">
-        <v>-848.4639999999999</v>
+        <v>-826.74</v>
       </c>
       <c r="F41">
-        <v>847.2360000000001</v>
+        <v>868.96</v>
       </c>
       <c r="G41">
         <v>446.3</v>
@@ -4649,28 +4649,28 @@
         <v>226.775</v>
       </c>
       <c r="M41">
-        <v>46.8521508</v>
+        <v>48.053488</v>
       </c>
       <c r="N41">
-        <v>179.9228492</v>
+        <v>178.721512</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>179.9228492</v>
+        <v>178.721512</v>
       </c>
       <c r="Q41">
-        <v>363.5228492</v>
+        <v>362.321512</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1173433373823284</v>
+        <v>0.1185357263387006</v>
       </c>
       <c r="T41">
-        <v>1.310341349139645</v>
+        <v>1.332180371625306</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.840226032910317</v>
+        <v>4.719220382087561</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09324143580322035</v>
+        <v>0.09333643580322033</v>
       </c>
       <c r="C42">
-        <v>1673.003791105598</v>
+        <v>1647.091676098845</v>
       </c>
       <c r="D42">
-        <v>2095.663791105598</v>
+        <v>2091.475676098845</v>
       </c>
       <c r="E42">
-        <v>-826.74</v>
+        <v>-805.016</v>
       </c>
       <c r="F42">
-        <v>868.96</v>
+        <v>890.6840000000001</v>
       </c>
       <c r="G42">
         <v>446.3</v>
@@ -4731,28 +4731,28 @@
         <v>226.775</v>
       </c>
       <c r="M42">
-        <v>48.053488</v>
+        <v>49.25482520000001</v>
       </c>
       <c r="N42">
-        <v>178.721512</v>
+        <v>177.5201748</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>178.721512</v>
+        <v>177.5201748</v>
       </c>
       <c r="Q42">
-        <v>362.321512</v>
+        <v>361.1201748</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1185357263387006</v>
+        <v>0.1197685352596955</v>
       </c>
       <c r="T42">
-        <v>1.332180371625306</v>
+        <v>1.354759699957938</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.719220382087561</v>
+        <v>4.604117445939083</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09333643580322033</v>
+        <v>0.09448143580322035</v>
       </c>
       <c r="C43">
-        <v>1647.091676098845</v>
+        <v>1576.175625584698</v>
       </c>
       <c r="D43">
-        <v>2091.475676098845</v>
+        <v>2042.283625584698</v>
       </c>
       <c r="E43">
-        <v>-805.016</v>
+        <v>-783.2919999999999</v>
       </c>
       <c r="F43">
-        <v>890.6840000000001</v>
+        <v>912.4080000000001</v>
       </c>
       <c r="G43">
         <v>446.3</v>
@@ -4813,45 +4813,45 @@
         <v>226.775</v>
       </c>
       <c r="M43">
-        <v>49.25482520000001</v>
+        <v>52.73718240000001</v>
       </c>
       <c r="N43">
-        <v>177.5201748</v>
+        <v>174.0378176</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>177.5201748</v>
+        <v>174.0378176</v>
       </c>
       <c r="Q43">
-        <v>361.1201748</v>
+        <v>357.6378175999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1197685352596955</v>
+        <v>0.1210438548331385</v>
       </c>
       <c r="T43">
-        <v>1.354759699957938</v>
+        <v>1.378117625819282</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.604117445939083</v>
+        <v>4.300097003286242</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09448143580322035</v>
+        <v>0.09460143580322035</v>
       </c>
       <c r="C44">
-        <v>1576.175625584699</v>
+        <v>1549.429764423515</v>
       </c>
       <c r="D44">
-        <v>2042.283625584698</v>
+        <v>2037.261764423515</v>
       </c>
       <c r="E44">
-        <v>-783.292</v>
+        <v>-761.568</v>
       </c>
       <c r="F44">
-        <v>912.408</v>
+        <v>934.1320000000001</v>
       </c>
       <c r="G44">
         <v>446.3</v>
@@ -4895,28 +4895,28 @@
         <v>226.775</v>
       </c>
       <c r="M44">
-        <v>52.7371824</v>
+        <v>53.99282960000001</v>
       </c>
       <c r="N44">
-        <v>174.0378176</v>
+        <v>172.7821704</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>174.0378176</v>
+        <v>172.7821704</v>
       </c>
       <c r="Q44">
-        <v>357.6378176</v>
+        <v>356.3821703999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1210438548331385</v>
+        <v>0.1223639224617901</v>
       </c>
       <c r="T44">
-        <v>1.378117625819282</v>
+        <v>1.402295128026637</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.300097003286243</v>
+        <v>4.200094747395864</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09460143580322035</v>
+        <v>0.09472143580322034</v>
       </c>
       <c r="C45">
-        <v>1549.429764423515</v>
+        <v>1522.708539634076</v>
       </c>
       <c r="D45">
-        <v>2037.261764423515</v>
+        <v>2032.264539634076</v>
       </c>
       <c r="E45">
-        <v>-761.568</v>
+        <v>-739.8440000000001</v>
       </c>
       <c r="F45">
-        <v>934.1320000000001</v>
+        <v>955.856</v>
       </c>
       <c r="G45">
         <v>446.3</v>
@@ -4977,28 +4977,28 @@
         <v>226.775</v>
       </c>
       <c r="M45">
-        <v>53.99282960000001</v>
+        <v>55.24847680000001</v>
       </c>
       <c r="N45">
-        <v>172.7821704</v>
+        <v>171.5265232</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>172.7821704</v>
+        <v>171.5265232</v>
       </c>
       <c r="Q45">
-        <v>356.3821703999999</v>
+        <v>355.1265232</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1223639224617901</v>
+        <v>0.1237311353628935</v>
       </c>
       <c r="T45">
-        <v>1.402295128026637</v>
+        <v>1.427336112455684</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.200094747395864</v>
+        <v>4.104638048591413</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09472143580322034</v>
+        <v>0.09484143580322035</v>
       </c>
       <c r="C46">
-        <v>1522.708539634076</v>
+        <v>1496.011770367396</v>
       </c>
       <c r="D46">
-        <v>2032.264539634076</v>
+        <v>2027.291770367396</v>
       </c>
       <c r="E46">
-        <v>-739.8440000000001</v>
+        <v>-718.12</v>
       </c>
       <c r="F46">
-        <v>955.856</v>
+        <v>977.58</v>
       </c>
       <c r="G46">
         <v>446.3</v>
@@ -5059,28 +5059,28 @@
         <v>226.775</v>
       </c>
       <c r="M46">
-        <v>55.24847680000001</v>
+        <v>56.504124</v>
       </c>
       <c r="N46">
-        <v>171.5265232</v>
+        <v>170.270876</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>171.5265232</v>
+        <v>170.270876</v>
       </c>
       <c r="Q46">
-        <v>355.1265232</v>
+        <v>353.870876</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1237311353628935</v>
+        <v>0.1251480650967643</v>
       </c>
       <c r="T46">
-        <v>1.427336112455684</v>
+        <v>1.453287678136697</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.104638048591413</v>
+        <v>4.013423869733826</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09484143580322035</v>
+        <v>0.09657143580322035</v>
       </c>
       <c r="C47">
-        <v>1496.011770367396</v>
+        <v>1405.209267716244</v>
       </c>
       <c r="D47">
-        <v>2027.291770367396</v>
+        <v>1958.213267716244</v>
       </c>
       <c r="E47">
-        <v>-718.12</v>
+        <v>-696.396</v>
       </c>
       <c r="F47">
-        <v>977.58</v>
+        <v>999.3040000000001</v>
       </c>
       <c r="G47">
         <v>446.3</v>
@@ -5141,45 +5141,45 @@
         <v>226.775</v>
       </c>
       <c r="M47">
-        <v>56.504124</v>
+        <v>61.25733520000001</v>
       </c>
       <c r="N47">
-        <v>170.270876</v>
+        <v>165.5176648</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>170.270876</v>
+        <v>165.5176648</v>
       </c>
       <c r="Q47">
-        <v>353.870876</v>
+        <v>349.1176648</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1251480650967643</v>
+        <v>0.1266174737096673</v>
       </c>
       <c r="T47">
-        <v>1.453287678136697</v>
+        <v>1.480200412917006</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.013423869733826</v>
+        <v>3.702005633441266</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09657143580322035</v>
+        <v>0.09672643580322036</v>
       </c>
       <c r="C48">
-        <v>1405.209267716244</v>
+        <v>1377.525238279492</v>
       </c>
       <c r="D48">
-        <v>1958.213267716244</v>
+        <v>1952.253238279492</v>
       </c>
       <c r="E48">
-        <v>-696.396</v>
+        <v>-674.6719999999999</v>
       </c>
       <c r="F48">
-        <v>999.3040000000001</v>
+        <v>1021.028</v>
       </c>
       <c r="G48">
         <v>446.3</v>
@@ -5223,28 +5223,28 @@
         <v>226.775</v>
       </c>
       <c r="M48">
-        <v>61.25733520000001</v>
+        <v>62.58901640000001</v>
       </c>
       <c r="N48">
-        <v>165.5176648</v>
+        <v>164.1859836</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>165.5176648</v>
+        <v>164.1859836</v>
       </c>
       <c r="Q48">
-        <v>349.1176648</v>
+        <v>347.7859836</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1266174737096673</v>
+        <v>0.1281423317041893</v>
       </c>
       <c r="T48">
-        <v>1.480200412917006</v>
+        <v>1.508128722594686</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.702005633441266</v>
+        <v>3.623239556134005</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09672643580322036</v>
+        <v>0.09688143580322035</v>
       </c>
       <c r="C49">
-        <v>1377.525238279492</v>
+        <v>1349.877378717302</v>
       </c>
       <c r="D49">
-        <v>1952.253238279492</v>
+        <v>1946.329378717302</v>
       </c>
       <c r="E49">
-        <v>-674.6719999999999</v>
+        <v>-652.9479999999999</v>
       </c>
       <c r="F49">
-        <v>1021.028</v>
+        <v>1042.752</v>
       </c>
       <c r="G49">
         <v>446.3</v>
@@ -5305,28 +5305,28 @@
         <v>226.775</v>
       </c>
       <c r="M49">
-        <v>62.58901640000001</v>
+        <v>63.92069760000001</v>
       </c>
       <c r="N49">
-        <v>164.1859836</v>
+        <v>162.8543024</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>164.1859836</v>
+        <v>162.8543024</v>
       </c>
       <c r="Q49">
-        <v>347.7859836</v>
+        <v>346.4543024</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1281423317041893</v>
+        <v>0.1297258380831161</v>
       </c>
       <c r="T49">
-        <v>1.508128722594686</v>
+        <v>1.537131198029199</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.623239556134005</v>
+        <v>3.547755398714547</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09688143580322034</v>
+        <v>0.09840843580322034</v>
       </c>
       <c r="C50">
-        <v>1349.877378717303</v>
+        <v>1271.659683059478</v>
       </c>
       <c r="D50">
-        <v>1946.329378717302</v>
+        <v>1889.835683059478</v>
       </c>
       <c r="E50">
-        <v>-652.9480000000001</v>
+        <v>-631.2239999999999</v>
       </c>
       <c r="F50">
-        <v>1042.752</v>
+        <v>1064.476</v>
       </c>
       <c r="G50">
         <v>446.3</v>
@@ -5387,45 +5387,45 @@
         <v>226.775</v>
       </c>
       <c r="M50">
-        <v>63.9206976</v>
+        <v>68.23291160000001</v>
       </c>
       <c r="N50">
-        <v>162.8543024</v>
+        <v>158.5420884</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>162.8543024</v>
+        <v>158.5420884</v>
       </c>
       <c r="Q50">
-        <v>346.4543024</v>
+        <v>342.1420884</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1297258380831161</v>
+        <v>0.1313714427514124</v>
       </c>
       <c r="T50">
-        <v>1.537131198029199</v>
+        <v>1.567271025441536</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.547755398714547</v>
+        <v>3.323542769644905</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09840843580322034</v>
+        <v>0.09859143580322036</v>
       </c>
       <c r="C51">
-        <v>1271.659683059478</v>
+        <v>1243.384621798537</v>
       </c>
       <c r="D51">
-        <v>1889.835683059478</v>
+        <v>1883.284621798537</v>
       </c>
       <c r="E51">
-        <v>-631.2239999999999</v>
+        <v>-609.5</v>
       </c>
       <c r="F51">
-        <v>1064.476</v>
+        <v>1086.2</v>
       </c>
       <c r="G51">
         <v>446.3</v>
@@ -5469,28 +5469,28 @@
         <v>226.775</v>
       </c>
       <c r="M51">
-        <v>68.23291160000001</v>
+        <v>69.62542000000001</v>
       </c>
       <c r="N51">
-        <v>158.5420884</v>
+        <v>157.14958</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>158.5420884</v>
+        <v>157.14958</v>
       </c>
       <c r="Q51">
-        <v>342.1420884</v>
+        <v>340.74958</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1313714427514124</v>
+        <v>0.1330828716064407</v>
       </c>
       <c r="T51">
-        <v>1.567271025441536</v>
+        <v>1.598616445950367</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.323542769644905</v>
+        <v>3.257071914252007</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09859143580322036</v>
+        <v>0.09877443580322035</v>
       </c>
       <c r="C52">
-        <v>1243.384621798537</v>
+        <v>1215.154821773232</v>
       </c>
       <c r="D52">
-        <v>1883.284621798537</v>
+        <v>1876.778821773232</v>
       </c>
       <c r="E52">
-        <v>-609.5</v>
+        <v>-587.7760000000001</v>
       </c>
       <c r="F52">
-        <v>1086.2</v>
+        <v>1107.924</v>
       </c>
       <c r="G52">
         <v>446.3</v>
@@ -5551,28 +5551,28 @@
         <v>226.775</v>
       </c>
       <c r="M52">
-        <v>69.62542000000001</v>
+        <v>71.0179284</v>
       </c>
       <c r="N52">
-        <v>157.14958</v>
+        <v>155.7570716</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>157.14958</v>
+        <v>155.7570716</v>
       </c>
       <c r="Q52">
-        <v>340.74958</v>
+        <v>339.3570716</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1330828716064407</v>
+        <v>0.1348641547004497</v>
       </c>
       <c r="T52">
-        <v>1.598616445950367</v>
+        <v>1.631241271377925</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.257071914252007</v>
+        <v>3.193207759070596</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09877443580322035</v>
+        <v>0.09895743580322035</v>
       </c>
       <c r="C53">
-        <v>1215.154821773232</v>
+        <v>1186.969815534032</v>
       </c>
       <c r="D53">
-        <v>1876.778821773232</v>
+        <v>1870.317815534032</v>
       </c>
       <c r="E53">
-        <v>-587.7760000000001</v>
+        <v>-566.0519999999999</v>
       </c>
       <c r="F53">
-        <v>1107.924</v>
+        <v>1129.648</v>
       </c>
       <c r="G53">
         <v>446.3</v>
@@ -5633,28 +5633,28 @@
         <v>226.775</v>
       </c>
       <c r="M53">
-        <v>71.0179284</v>
+        <v>72.41043680000001</v>
       </c>
       <c r="N53">
-        <v>155.7570716</v>
+        <v>154.3645632</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>155.7570716</v>
+        <v>154.3645632</v>
       </c>
       <c r="Q53">
-        <v>339.3570716</v>
+        <v>337.9645632</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1348641547004497</v>
+        <v>0.1367196579233757</v>
       </c>
       <c r="T53">
-        <v>1.631241271377925</v>
+        <v>1.665225464531632</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.193207759070596</v>
+        <v>3.131799917550007</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09895743580322035</v>
+        <v>0.09914043580322034</v>
       </c>
       <c r="C54">
-        <v>1186.969815534032</v>
+        <v>1158.829142046298</v>
       </c>
       <c r="D54">
-        <v>1870.317815534032</v>
+        <v>1863.901142046298</v>
       </c>
       <c r="E54">
-        <v>-566.0519999999999</v>
+        <v>-544.328</v>
       </c>
       <c r="F54">
-        <v>1129.648</v>
+        <v>1151.372</v>
       </c>
       <c r="G54">
         <v>446.3</v>
@@ -5715,28 +5715,28 @@
         <v>226.775</v>
       </c>
       <c r="M54">
-        <v>72.41043680000001</v>
+        <v>73.80294520000001</v>
       </c>
       <c r="N54">
-        <v>154.3645632</v>
+        <v>152.9720548</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>154.3645632</v>
+        <v>152.9720548</v>
       </c>
       <c r="Q54">
-        <v>337.9645632</v>
+        <v>336.5720548</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1367196579233757</v>
+        <v>0.138654118730256</v>
       </c>
       <c r="T54">
-        <v>1.665225464531632</v>
+        <v>1.70065579356422</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.131799917550007</v>
+        <v>3.072709353067931</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09914043580322034</v>
+        <v>0.09932343580322034</v>
       </c>
       <c r="C55">
-        <v>1158.829142046298</v>
+        <v>1130.732346580616</v>
       </c>
       <c r="D55">
-        <v>1863.901142046298</v>
+        <v>1857.528346580616</v>
       </c>
       <c r="E55">
-        <v>-544.328</v>
+        <v>-522.6039999999998</v>
       </c>
       <c r="F55">
-        <v>1151.372</v>
+        <v>1173.096</v>
       </c>
       <c r="G55">
         <v>446.3</v>
@@ -5797,28 +5797,28 @@
         <v>226.775</v>
       </c>
       <c r="M55">
-        <v>73.80294520000001</v>
+        <v>75.19545360000002</v>
       </c>
       <c r="N55">
-        <v>152.9720548</v>
+        <v>151.5795464</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>152.9720548</v>
+        <v>151.5795464</v>
       </c>
       <c r="Q55">
-        <v>336.5720548</v>
+        <v>335.1795463999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.138654118730256</v>
+        <v>0.1406726865287399</v>
       </c>
       <c r="T55">
-        <v>1.70065579356422</v>
+        <v>1.737626571685181</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.072709353067931</v>
+        <v>3.015807328011117</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09932343580322034</v>
+        <v>0.1037964358032203</v>
       </c>
       <c r="C56">
-        <v>1130.732346580616</v>
+        <v>965.7456757081109</v>
       </c>
       <c r="D56">
-        <v>1857.528346580616</v>
+        <v>1714.265675708111</v>
       </c>
       <c r="E56">
-        <v>-522.6039999999998</v>
+        <v>-500.8799999999999</v>
       </c>
       <c r="F56">
-        <v>1173.096</v>
+        <v>1194.82</v>
       </c>
       <c r="G56">
         <v>446.3</v>
@@ -5879,45 +5879,45 @@
         <v>226.775</v>
       </c>
       <c r="M56">
-        <v>75.19545360000002</v>
+        <v>85.90755800000002</v>
       </c>
       <c r="N56">
-        <v>151.5795464</v>
+        <v>140.867442</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>151.5795464</v>
+        <v>140.867442</v>
       </c>
       <c r="Q56">
-        <v>335.1795463999999</v>
+        <v>324.467442</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1406726865287399</v>
+        <v>0.1427809684516008</v>
       </c>
       <c r="T56">
-        <v>1.737626571685181</v>
+        <v>1.776240495500407</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.015807328011117</v>
+        <v>2.639756096896619</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1037964358032203</v>
+        <v>0.1040574358032204</v>
       </c>
       <c r="C57">
-        <v>965.7456757081109</v>
+        <v>936.3415686935984</v>
       </c>
       <c r="D57">
-        <v>1714.265675708111</v>
+        <v>1706.585568693598</v>
       </c>
       <c r="E57">
-        <v>-500.8799999999999</v>
+        <v>-479.1559999999999</v>
       </c>
       <c r="F57">
-        <v>1194.82</v>
+        <v>1216.544</v>
       </c>
       <c r="G57">
         <v>446.3</v>
@@ -5961,28 +5961,28 @@
         <v>226.775</v>
       </c>
       <c r="M57">
-        <v>85.90755800000002</v>
+        <v>87.46951360000001</v>
       </c>
       <c r="N57">
-        <v>140.867442</v>
+        <v>139.3054864</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>140.867442</v>
+        <v>139.3054864</v>
       </c>
       <c r="Q57">
-        <v>324.467442</v>
+        <v>322.9054864</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1427809684516008</v>
+        <v>0.1449850813709553</v>
       </c>
       <c r="T57">
-        <v>1.776240495500407</v>
+        <v>1.816609597670871</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.639756096896619</v>
+        <v>2.592617595166323</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1040574358032204</v>
+        <v>0.1043184358032204</v>
       </c>
       <c r="C58">
-        <v>936.3415686935984</v>
+        <v>907.0059702748224</v>
       </c>
       <c r="D58">
-        <v>1706.585568693598</v>
+        <v>1698.973970274822</v>
       </c>
       <c r="E58">
-        <v>-479.1559999999999</v>
+        <v>-457.4319999999998</v>
       </c>
       <c r="F58">
-        <v>1216.544</v>
+        <v>1238.268</v>
       </c>
       <c r="G58">
         <v>446.3</v>
@@ -6043,28 +6043,28 @@
         <v>226.775</v>
       </c>
       <c r="M58">
-        <v>87.46951360000001</v>
+        <v>89.03146920000003</v>
       </c>
       <c r="N58">
-        <v>139.3054864</v>
+        <v>137.7435308</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>139.3054864</v>
+        <v>137.7435308</v>
       </c>
       <c r="Q58">
-        <v>322.9054864</v>
+        <v>321.3435307999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1449850813709553</v>
+        <v>0.1472917111702799</v>
       </c>
       <c r="T58">
-        <v>1.816609597670871</v>
+        <v>1.858856332500427</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.592617595166323</v>
+        <v>2.547133075952878</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1043184358032204</v>
+        <v>0.1045794358032203</v>
       </c>
       <c r="C59">
-        <v>907.0059702748224</v>
+        <v>877.7379678497869</v>
       </c>
       <c r="D59">
-        <v>1698.973970274822</v>
+        <v>1691.429967849787</v>
       </c>
       <c r="E59">
-        <v>-457.4319999999998</v>
+        <v>-435.7079999999999</v>
       </c>
       <c r="F59">
-        <v>1238.268</v>
+        <v>1259.992</v>
       </c>
       <c r="G59">
         <v>446.3</v>
@@ -6125,28 +6125,28 @@
         <v>226.775</v>
       </c>
       <c r="M59">
-        <v>89.03146920000003</v>
+        <v>90.59342480000002</v>
       </c>
       <c r="N59">
-        <v>137.7435308</v>
+        <v>136.1815752</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>137.7435308</v>
+        <v>136.1815752</v>
       </c>
       <c r="Q59">
-        <v>321.3435307999999</v>
+        <v>319.7815752</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1472917111702799</v>
+        <v>0.149708180483858</v>
       </c>
       <c r="T59">
-        <v>1.858856332500427</v>
+        <v>1.90311481660758</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.547133075952878</v>
+        <v>2.503216988436449</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1045794358032203</v>
+        <v>0.1071414358032203</v>
       </c>
       <c r="C60">
-        <v>877.7379678497871</v>
+        <v>785.369329019803</v>
       </c>
       <c r="D60">
-        <v>1691.429967849787</v>
+        <v>1620.785329019803</v>
       </c>
       <c r="E60">
-        <v>-435.7080000000001</v>
+        <v>-413.9840000000002</v>
       </c>
       <c r="F60">
-        <v>1259.992</v>
+        <v>1281.716</v>
       </c>
       <c r="G60">
         <v>446.3</v>
@@ -6207,45 +6207,45 @@
         <v>226.775</v>
       </c>
       <c r="M60">
-        <v>90.59342480000001</v>
+        <v>97.15407279999999</v>
       </c>
       <c r="N60">
-        <v>136.1815752</v>
+        <v>129.6209272</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>136.1815752</v>
+        <v>129.6209272</v>
       </c>
       <c r="Q60">
-        <v>319.7815752</v>
+        <v>313.2209272</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1497081804838579</v>
+        <v>0.1522425263493179</v>
       </c>
       <c r="T60">
-        <v>1.903114816607579</v>
+        <v>1.949532251158983</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.50321698843645</v>
+        <v>2.33417903608463</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1071414358032203</v>
+        <v>0.1074414358032204</v>
       </c>
       <c r="C61">
-        <v>785.369329019803</v>
+        <v>755.7571999979841</v>
       </c>
       <c r="D61">
-        <v>1620.785329019803</v>
+        <v>1612.897199997984</v>
       </c>
       <c r="E61">
-        <v>-413.9840000000002</v>
+        <v>-392.26</v>
       </c>
       <c r="F61">
-        <v>1281.716</v>
+        <v>1303.44</v>
       </c>
       <c r="G61">
         <v>446.3</v>
@@ -6289,28 +6289,28 @@
         <v>226.775</v>
       </c>
       <c r="M61">
-        <v>97.15407279999999</v>
+        <v>98.80075200000002</v>
       </c>
       <c r="N61">
-        <v>129.6209272</v>
+        <v>127.974248</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>129.6209272</v>
+        <v>127.974248</v>
       </c>
       <c r="Q61">
-        <v>313.2209272</v>
+        <v>311.574248</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1522425263493179</v>
+        <v>0.1549035895080509</v>
       </c>
       <c r="T61">
-        <v>1.949532251158983</v>
+        <v>1.998270557437958</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.33417903608463</v>
+        <v>2.295276052149886</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1074414358032204</v>
+        <v>0.1077414358032203</v>
       </c>
       <c r="C62">
-        <v>755.7571999979841</v>
+        <v>726.2214798832522</v>
       </c>
       <c r="D62">
-        <v>1612.897199997984</v>
+        <v>1605.085479883252</v>
       </c>
       <c r="E62">
-        <v>-392.26</v>
+        <v>-370.5360000000001</v>
       </c>
       <c r="F62">
-        <v>1303.44</v>
+        <v>1325.164</v>
       </c>
       <c r="G62">
         <v>446.3</v>
@@ -6371,28 +6371,28 @@
         <v>226.775</v>
       </c>
       <c r="M62">
-        <v>98.80075200000002</v>
+        <v>100.4474312</v>
       </c>
       <c r="N62">
-        <v>127.974248</v>
+        <v>126.3275688</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>127.974248</v>
+        <v>126.3275688</v>
       </c>
       <c r="Q62">
-        <v>311.574248</v>
+        <v>309.9275688</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1549035895080509</v>
+        <v>0.1577011174441547</v>
       </c>
       <c r="T62">
-        <v>1.998270557437958</v>
+        <v>2.049508264038931</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.295276052149886</v>
+        <v>2.257648575885134</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1077414358032203</v>
+        <v>0.1080414358032203</v>
       </c>
       <c r="C63">
-        <v>726.2214798832522</v>
+        <v>696.7610638165129</v>
       </c>
       <c r="D63">
-        <v>1605.085479883252</v>
+        <v>1597.349063816513</v>
       </c>
       <c r="E63">
-        <v>-370.5360000000001</v>
+        <v>-348.8119999999999</v>
       </c>
       <c r="F63">
-        <v>1325.164</v>
+        <v>1346.888</v>
       </c>
       <c r="G63">
         <v>446.3</v>
@@ -6453,28 +6453,28 @@
         <v>226.775</v>
       </c>
       <c r="M63">
-        <v>100.4474312</v>
+        <v>102.0941104</v>
       </c>
       <c r="N63">
-        <v>126.3275688</v>
+        <v>124.6808896</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>126.3275688</v>
+        <v>124.6808896</v>
       </c>
       <c r="Q63">
-        <v>309.9275688</v>
+        <v>308.2808896</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1577011174441547</v>
+        <v>0.1606458836926851</v>
       </c>
       <c r="T63">
-        <v>2.049508264038931</v>
+        <v>2.103442692039956</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.257648575885134</v>
+        <v>2.221234889177309</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1080414358032203</v>
+        <v>0.1083414358032204</v>
       </c>
       <c r="C64">
-        <v>696.7610638165129</v>
+        <v>667.3748681379113</v>
       </c>
       <c r="D64">
-        <v>1597.349063816513</v>
+        <v>1589.686868137911</v>
       </c>
       <c r="E64">
-        <v>-348.8119999999999</v>
+        <v>-327.088</v>
       </c>
       <c r="F64">
-        <v>1346.888</v>
+        <v>1368.612</v>
       </c>
       <c r="G64">
         <v>446.3</v>
@@ -6535,28 +6535,28 @@
         <v>226.775</v>
       </c>
       <c r="M64">
-        <v>102.0941104</v>
+        <v>103.7407896</v>
       </c>
       <c r="N64">
-        <v>124.6808896</v>
+        <v>123.0342104</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>124.6808896</v>
+        <v>123.0342104</v>
       </c>
       <c r="Q64">
-        <v>308.2808896</v>
+        <v>306.6342104</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1606458836926851</v>
+        <v>0.1637498264951901</v>
       </c>
       <c r="T64">
-        <v>2.103442692039956</v>
+        <v>2.160292494527523</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.221234889177309</v>
+        <v>2.185977192523701</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1083414358032204</v>
+        <v>0.1086414358032203</v>
       </c>
       <c r="C65">
-        <v>667.3748681379113</v>
+        <v>638.0618298808172</v>
       </c>
       <c r="D65">
-        <v>1589.686868137911</v>
+        <v>1582.097829880817</v>
       </c>
       <c r="E65">
-        <v>-327.088</v>
+        <v>-305.364</v>
       </c>
       <c r="F65">
-        <v>1368.612</v>
+        <v>1390.336</v>
       </c>
       <c r="G65">
         <v>446.3</v>
@@ -6617,28 +6617,28 @@
         <v>226.775</v>
       </c>
       <c r="M65">
-        <v>103.7407896</v>
+        <v>105.3874688</v>
       </c>
       <c r="N65">
-        <v>123.0342104</v>
+        <v>121.3875312</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>123.0342104</v>
+        <v>121.3875312</v>
       </c>
       <c r="Q65">
-        <v>306.6342104</v>
+        <v>304.9875312</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1637498264951901</v>
+        <v>0.167026210564501</v>
       </c>
       <c r="T65">
-        <v>2.160292494527523</v>
+        <v>2.220300619375509</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.185977192523701</v>
+        <v>2.151821298890519</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1086414358032203</v>
+        <v>0.1089414358032204</v>
       </c>
       <c r="C66">
-        <v>638.0618298808172</v>
+        <v>608.8209062802287</v>
       </c>
       <c r="D66">
-        <v>1582.097829880817</v>
+        <v>1574.580906280229</v>
       </c>
       <c r="E66">
-        <v>-305.364</v>
+        <v>-283.6399999999999</v>
       </c>
       <c r="F66">
-        <v>1390.336</v>
+        <v>1412.06</v>
       </c>
       <c r="G66">
         <v>446.3</v>
@@ -6699,28 +6699,28 @@
         <v>226.775</v>
       </c>
       <c r="M66">
-        <v>105.3874688</v>
+        <v>107.034148</v>
       </c>
       <c r="N66">
-        <v>121.3875312</v>
+        <v>119.740852</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>121.3875312</v>
+        <v>119.740852</v>
       </c>
       <c r="Q66">
-        <v>304.9875312</v>
+        <v>303.340852</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.167026210564501</v>
+        <v>0.1704898165806296</v>
       </c>
       <c r="T66">
-        <v>2.220300619375509</v>
+        <v>2.283737779929095</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.151821298890519</v>
+        <v>2.118716355830664</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1089414358032204</v>
+        <v>0.1092414358032203</v>
       </c>
       <c r="C67">
-        <v>608.8209062802287</v>
+        <v>579.6510742951325</v>
       </c>
       <c r="D67">
-        <v>1574.580906280229</v>
+        <v>1567.135074295133</v>
       </c>
       <c r="E67">
-        <v>-283.6399999999999</v>
+        <v>-261.9159999999999</v>
       </c>
       <c r="F67">
-        <v>1412.06</v>
+        <v>1433.784</v>
       </c>
       <c r="G67">
         <v>446.3</v>
@@ -6781,28 +6781,28 @@
         <v>226.775</v>
       </c>
       <c r="M67">
-        <v>107.034148</v>
+        <v>108.6808272</v>
       </c>
       <c r="N67">
-        <v>119.740852</v>
+        <v>118.0941728</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>119.740852</v>
+        <v>118.0941728</v>
       </c>
       <c r="Q67">
-        <v>303.340852</v>
+        <v>301.6941728</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1704898165806296</v>
+        <v>0.1741571641271187</v>
       </c>
       <c r="T67">
-        <v>2.283737779929095</v>
+        <v>2.350906538162304</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.118716355830664</v>
+        <v>2.086614592863533</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1092414358032203</v>
+        <v>0.1095414358032203</v>
       </c>
       <c r="C68">
-        <v>579.6510742951325</v>
+        <v>550.551330144343</v>
       </c>
       <c r="D68">
-        <v>1567.135074295133</v>
+        <v>1559.759330144343</v>
       </c>
       <c r="E68">
-        <v>-261.9159999999999</v>
+        <v>-240.192</v>
       </c>
       <c r="F68">
-        <v>1433.784</v>
+        <v>1455.508</v>
       </c>
       <c r="G68">
         <v>446.3</v>
@@ -6863,28 +6863,28 @@
         <v>226.775</v>
       </c>
       <c r="M68">
-        <v>108.6808272</v>
+        <v>110.3275064</v>
       </c>
       <c r="N68">
-        <v>118.0941728</v>
+        <v>116.4474936</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>118.0941728</v>
+        <v>116.4474936</v>
       </c>
       <c r="Q68">
-        <v>301.6941728</v>
+        <v>300.0474936</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1741571641271187</v>
+        <v>0.1780467751612738</v>
       </c>
       <c r="T68">
-        <v>2.350906538162304</v>
+        <v>2.422146130227829</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.086614592863533</v>
+        <v>2.05547109147751</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1095414358032203</v>
+        <v>0.1098414358032204</v>
       </c>
       <c r="C69">
-        <v>550.551330144343</v>
+        <v>521.5206888553948</v>
       </c>
       <c r="D69">
-        <v>1559.759330144343</v>
+        <v>1552.452688855395</v>
       </c>
       <c r="E69">
-        <v>-240.192</v>
+        <v>-218.4679999999998</v>
       </c>
       <c r="F69">
-        <v>1455.508</v>
+        <v>1477.232</v>
       </c>
       <c r="G69">
         <v>446.3</v>
@@ -6945,28 +6945,28 @@
         <v>226.775</v>
       </c>
       <c r="M69">
-        <v>110.3275064</v>
+        <v>111.9741856</v>
       </c>
       <c r="N69">
-        <v>116.4474936</v>
+        <v>114.8008144</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>116.4474936</v>
+        <v>114.8008144</v>
       </c>
       <c r="Q69">
-        <v>300.0474936</v>
+        <v>298.4008143999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1780467751612738</v>
+        <v>0.1821794868850636</v>
       </c>
       <c r="T69">
-        <v>2.422146130227829</v>
+        <v>2.497838196797448</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.05547109147751</v>
+        <v>2.02524357542637</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1098414358032204</v>
+        <v>0.1199394358032203</v>
       </c>
       <c r="C70">
-        <v>521.5206888553948</v>
+        <v>288.3482595246064</v>
       </c>
       <c r="D70">
-        <v>1552.452688855395</v>
+        <v>1341.004259524607</v>
       </c>
       <c r="E70">
-        <v>-218.4679999999998</v>
+        <v>-196.7439999999999</v>
       </c>
       <c r="F70">
-        <v>1477.232</v>
+        <v>1498.956</v>
       </c>
       <c r="G70">
         <v>446.3</v>
@@ -7027,45 +7027,45 @@
         <v>226.775</v>
       </c>
       <c r="M70">
-        <v>111.9741856</v>
+        <v>134.90604</v>
       </c>
       <c r="N70">
-        <v>114.8008144</v>
+        <v>91.86895999999999</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>114.8008144</v>
+        <v>91.86895999999999</v>
       </c>
       <c r="Q70">
-        <v>298.4008143999999</v>
+        <v>275.46896</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1821794868850636</v>
+        <v>0.1865788251716786</v>
       </c>
       <c r="T70">
-        <v>2.497838196797448</v>
+        <v>2.578413622500592</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.02524357542637</v>
+        <v>1.680984780221849</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1199394358032203</v>
+        <v>0.1203814358032203</v>
       </c>
       <c r="C71">
-        <v>288.3482595246064</v>
+        <v>258.6769214728993</v>
       </c>
       <c r="D71">
-        <v>1341.004259524607</v>
+        <v>1333.0569214729</v>
       </c>
       <c r="E71">
-        <v>-196.7439999999999</v>
+        <v>-175.0199999999998</v>
       </c>
       <c r="F71">
-        <v>1498.956</v>
+        <v>1520.68</v>
       </c>
       <c r="G71">
         <v>446.3</v>
@@ -7109,28 +7109,28 @@
         <v>226.775</v>
       </c>
       <c r="M71">
-        <v>134.90604</v>
+        <v>136.8612</v>
       </c>
       <c r="N71">
-        <v>91.86895999999999</v>
+        <v>89.91379999999998</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>91.86895999999999</v>
+        <v>89.91379999999998</v>
       </c>
       <c r="Q71">
-        <v>275.46896</v>
+        <v>273.5137999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1865788251716786</v>
+        <v>0.1912714526774012</v>
       </c>
       <c r="T71">
-        <v>2.578413622500592</v>
+        <v>2.664360743250612</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.680984780221849</v>
+        <v>1.656970711932965</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1203814358032203</v>
+        <v>0.1208234358032203</v>
       </c>
       <c r="C72">
-        <v>258.6769214728993</v>
+        <v>229.0992267842628</v>
       </c>
       <c r="D72">
-        <v>1333.0569214729</v>
+        <v>1325.203226784263</v>
       </c>
       <c r="E72">
-        <v>-175.0199999999998</v>
+        <v>-153.2959999999998</v>
       </c>
       <c r="F72">
-        <v>1520.68</v>
+        <v>1542.404</v>
       </c>
       <c r="G72">
         <v>446.3</v>
@@ -7191,28 +7191,28 @@
         <v>226.775</v>
       </c>
       <c r="M72">
-        <v>136.8612</v>
+        <v>138.81636</v>
       </c>
       <c r="N72">
-        <v>89.91379999999998</v>
+        <v>87.95864</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>89.91379999999998</v>
+        <v>87.95864</v>
       </c>
       <c r="Q72">
-        <v>273.5137999999999</v>
+        <v>271.55864</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1912714526774012</v>
+        <v>0.1962877096662771</v>
       </c>
       <c r="T72">
-        <v>2.664360743250612</v>
+        <v>2.756235251638564</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.656970711932965</v>
+        <v>1.633633096271938</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1208234358032203</v>
+        <v>0.1212654358032203</v>
       </c>
       <c r="C73">
-        <v>229.099226784263</v>
+        <v>199.6135300551009</v>
       </c>
       <c r="D73">
-        <v>1325.203226784263</v>
+        <v>1317.441530055101</v>
       </c>
       <c r="E73">
-        <v>-153.296</v>
+        <v>-131.5720000000001</v>
       </c>
       <c r="F73">
-        <v>1542.404</v>
+        <v>1564.128</v>
       </c>
       <c r="G73">
         <v>446.3</v>
@@ -7273,28 +7273,28 @@
         <v>226.775</v>
       </c>
       <c r="M73">
-        <v>138.81636</v>
+        <v>140.77152</v>
       </c>
       <c r="N73">
-        <v>87.95864</v>
+        <v>86.00348000000002</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>87.95864</v>
+        <v>86.00348000000002</v>
       </c>
       <c r="Q73">
-        <v>271.55864</v>
+        <v>269.60348</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.196287709666277</v>
+        <v>0.2016622707257869</v>
       </c>
       <c r="T73">
-        <v>2.756235251638563</v>
+        <v>2.854672224911369</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.633633096271938</v>
+        <v>1.610943747712606</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1212654358032203</v>
+        <v>0.1217074358032203</v>
       </c>
       <c r="C74">
-        <v>199.6135300551009</v>
+        <v>170.2182242057779</v>
       </c>
       <c r="D74">
-        <v>1317.441530055101</v>
+        <v>1309.770224205778</v>
       </c>
       <c r="E74">
-        <v>-131.5720000000001</v>
+        <v>-109.848</v>
       </c>
       <c r="F74">
-        <v>1564.128</v>
+        <v>1585.852</v>
       </c>
       <c r="G74">
         <v>446.3</v>
@@ -7355,28 +7355,28 @@
         <v>226.775</v>
       </c>
       <c r="M74">
-        <v>140.77152</v>
+        <v>142.72668</v>
       </c>
       <c r="N74">
-        <v>86.00348000000002</v>
+        <v>84.04831999999999</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>86.00348000000002</v>
+        <v>84.04831999999999</v>
       </c>
       <c r="Q74">
-        <v>269.60348</v>
+        <v>267.64832</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2016622707257869</v>
+        <v>0.2074349474193346</v>
       </c>
       <c r="T74">
-        <v>2.854672224911369</v>
+        <v>2.960400825834012</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.610943747712606</v>
+        <v>1.5888760251412</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1217074358032203</v>
+        <v>0.1221494358032203</v>
       </c>
       <c r="C75">
-        <v>170.2182242057779</v>
+        <v>140.9117393712991</v>
       </c>
       <c r="D75">
-        <v>1309.770224205778</v>
+        <v>1302.187739371299</v>
       </c>
       <c r="E75">
-        <v>-109.848</v>
+        <v>-88.12400000000002</v>
       </c>
       <c r="F75">
-        <v>1585.852</v>
+        <v>1607.576</v>
       </c>
       <c r="G75">
         <v>446.3</v>
@@ -7437,28 +7437,28 @@
         <v>226.775</v>
       </c>
       <c r="M75">
-        <v>142.72668</v>
+        <v>144.68184</v>
       </c>
       <c r="N75">
-        <v>84.04831999999999</v>
+        <v>82.09316000000001</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>84.04831999999999</v>
+        <v>82.09316000000001</v>
       </c>
       <c r="Q75">
-        <v>267.64832</v>
+        <v>265.69316</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2074349474193346</v>
+        <v>0.2136516761662321</v>
       </c>
       <c r="T75">
-        <v>2.960400825834012</v>
+        <v>3.074262396058397</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.5888760251412</v>
+        <v>1.567404727504157</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1221494358032203</v>
+        <v>0.1225914358032203</v>
       </c>
       <c r="C76">
-        <v>140.9117393712991</v>
+        <v>111.692541830299</v>
       </c>
       <c r="D76">
-        <v>1302.187739371299</v>
+        <v>1294.692541830299</v>
       </c>
       <c r="E76">
-        <v>-88.12400000000002</v>
+        <v>-66.39999999999986</v>
       </c>
       <c r="F76">
-        <v>1607.576</v>
+        <v>1629.3</v>
       </c>
       <c r="G76">
         <v>446.3</v>
@@ -7519,28 +7519,28 @@
         <v>226.775</v>
       </c>
       <c r="M76">
-        <v>144.68184</v>
+        <v>146.637</v>
       </c>
       <c r="N76">
-        <v>82.09316000000001</v>
+        <v>80.13800000000001</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>82.09316000000001</v>
+        <v>80.13800000000001</v>
       </c>
       <c r="Q76">
-        <v>265.69316</v>
+        <v>263.738</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2136516761662321</v>
+        <v>0.2203657432128814</v>
       </c>
       <c r="T76">
-        <v>3.074262396058397</v>
+        <v>3.197232891900733</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.567404727504157</v>
+        <v>1.546505997804101</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1225914358032203</v>
+        <v>0.1230334358032203</v>
       </c>
       <c r="C77">
-        <v>111.692541830299</v>
+        <v>82.55913297081224</v>
       </c>
       <c r="D77">
-        <v>1294.692541830299</v>
+        <v>1287.283132970812</v>
       </c>
       <c r="E77">
-        <v>-66.39999999999986</v>
+        <v>-44.67599999999993</v>
       </c>
       <c r="F77">
-        <v>1629.3</v>
+        <v>1651.024</v>
       </c>
       <c r="G77">
         <v>446.3</v>
@@ -7601,28 +7601,28 @@
         <v>226.775</v>
       </c>
       <c r="M77">
-        <v>146.637</v>
+        <v>148.59216</v>
       </c>
       <c r="N77">
-        <v>80.13800000000001</v>
+        <v>78.18284</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>80.13800000000001</v>
+        <v>78.18284</v>
       </c>
       <c r="Q77">
-        <v>263.738</v>
+        <v>261.78284</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2203657432128814</v>
+        <v>0.2276393158467515</v>
       </c>
       <c r="T77">
-        <v>3.197232891900733</v>
+        <v>3.330450929063264</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.546505997804101</v>
+        <v>1.5261572346751</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1230334358032203</v>
+        <v>0.1234754358032203</v>
       </c>
       <c r="C78">
-        <v>82.55913297081224</v>
+        <v>53.51004829134513</v>
       </c>
       <c r="D78">
-        <v>1287.283132970812</v>
+        <v>1279.958048291345</v>
       </c>
       <c r="E78">
-        <v>-44.67599999999993</v>
+        <v>-22.952</v>
       </c>
       <c r="F78">
-        <v>1651.024</v>
+        <v>1672.748</v>
       </c>
       <c r="G78">
         <v>446.3</v>
@@ -7683,28 +7683,28 @@
         <v>226.775</v>
       </c>
       <c r="M78">
-        <v>148.59216</v>
+        <v>150.54732</v>
       </c>
       <c r="N78">
-        <v>78.18284</v>
+        <v>76.22768000000002</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>78.18284</v>
+        <v>76.22768000000002</v>
       </c>
       <c r="Q78">
-        <v>261.78284</v>
+        <v>259.82768</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2276393158467515</v>
+        <v>0.2355453730574797</v>
       </c>
       <c r="T78">
-        <v>3.330450929063264</v>
+        <v>3.475253143370362</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.5261572346751</v>
+        <v>1.506337010848151</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1234754358032203</v>
+        <v>0.1682214358032204</v>
       </c>
       <c r="C79">
-        <v>53.51004829134513</v>
+        <v>-436.0487100013522</v>
       </c>
       <c r="D79">
-        <v>1279.958048291345</v>
+        <v>812.123289998648</v>
       </c>
       <c r="E79">
-        <v>-22.952</v>
+        <v>-1.227999999999838</v>
       </c>
       <c r="F79">
-        <v>1672.748</v>
+        <v>1694.472</v>
       </c>
       <c r="G79">
         <v>446.3</v>
@@ -7765,45 +7765,45 @@
         <v>226.775</v>
       </c>
       <c r="M79">
-        <v>150.54732</v>
+        <v>248.7484896000001</v>
       </c>
       <c r="N79">
-        <v>76.22768000000002</v>
+        <v>-21.97348960000005</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P79">
-        <v>76.22768000000002</v>
+        <v>-21.97348960000005</v>
       </c>
       <c r="Q79">
-        <v>259.82768</v>
+        <v>161.6265103999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2355453730574797</v>
+        <v>0.2441701627419107</v>
       </c>
       <c r="T79">
-        <v>3.475253143370362</v>
+        <v>3.633219195341743</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.506337010848151</v>
+        <v>0.9116638270433942</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1682214358032204</v>
+        <v>0.1692314358032204</v>
       </c>
       <c r="C80">
-        <v>-436.0487100013522</v>
+        <v>-464.4180553913734</v>
       </c>
       <c r="D80">
-        <v>812.123289998648</v>
+        <v>805.4779446086268</v>
       </c>
       <c r="E80">
-        <v>-1.227999999999838</v>
+        <v>20.49600000000009</v>
       </c>
       <c r="F80">
-        <v>1694.472</v>
+        <v>1716.196</v>
       </c>
       <c r="G80">
         <v>446.3</v>
@@ -7847,28 +7847,28 @@
         <v>226.775</v>
       </c>
       <c r="M80">
-        <v>248.7484896000001</v>
+        <v>251.9375728000001</v>
       </c>
       <c r="N80">
-        <v>-21.97348960000005</v>
+        <v>-25.16257280000005</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-21.97348960000005</v>
+        <v>-25.16257280000005</v>
       </c>
       <c r="Q80">
-        <v>161.6265103999999</v>
+        <v>158.4374271999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2441701627419107</v>
+        <v>0.2536163609677159</v>
       </c>
       <c r="T80">
-        <v>3.633219195341743</v>
+        <v>3.80622963321516</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9116638270433942</v>
+        <v>0.900123778599807</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1692314358032204</v>
+        <v>0.1702414358032204</v>
       </c>
       <c r="C81">
-        <v>-464.4180553913734</v>
+        <v>-492.6795299777416</v>
       </c>
       <c r="D81">
-        <v>805.4779446086268</v>
+        <v>798.9404700222585</v>
       </c>
       <c r="E81">
-        <v>20.49600000000009</v>
+        <v>42.22000000000003</v>
       </c>
       <c r="F81">
-        <v>1716.196</v>
+        <v>1737.92</v>
       </c>
       <c r="G81">
         <v>446.3</v>
@@ -7929,28 +7929,28 @@
         <v>226.775</v>
       </c>
       <c r="M81">
-        <v>251.9375728000001</v>
+        <v>255.126656</v>
       </c>
       <c r="N81">
-        <v>-25.16257280000005</v>
+        <v>-28.35165600000002</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-25.16257280000005</v>
+        <v>-28.35165600000002</v>
       </c>
       <c r="Q81">
-        <v>158.4374271999999</v>
+        <v>155.248344</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2536163609677159</v>
+        <v>0.2640071790161018</v>
       </c>
       <c r="T81">
-        <v>3.80622963321516</v>
+        <v>3.996541114875917</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.900123778599807</v>
+        <v>0.8888722313673095</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1702414358032204</v>
+        <v>0.1712514358032204</v>
       </c>
       <c r="C82">
-        <v>-492.6795299777416</v>
+        <v>-520.8357391394463</v>
       </c>
       <c r="D82">
-        <v>798.9404700222585</v>
+        <v>792.5082608605539</v>
       </c>
       <c r="E82">
-        <v>42.22000000000003</v>
+        <v>63.94400000000019</v>
       </c>
       <c r="F82">
-        <v>1737.92</v>
+        <v>1759.644</v>
       </c>
       <c r="G82">
         <v>446.3</v>
@@ -8011,28 +8011,28 @@
         <v>226.775</v>
       </c>
       <c r="M82">
-        <v>255.126656</v>
+        <v>258.3157392000001</v>
       </c>
       <c r="N82">
-        <v>-28.35165600000002</v>
+        <v>-31.54073920000005</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-28.35165600000002</v>
+        <v>-31.54073920000005</v>
       </c>
       <c r="Q82">
-        <v>155.248344</v>
+        <v>152.0592607999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2640071790161018</v>
+        <v>0.2754917673853703</v>
       </c>
       <c r="T82">
-        <v>3.996541114875917</v>
+        <v>4.206885384079913</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8888722313673095</v>
+        <v>0.8778985001158611</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1712514358032204</v>
+        <v>0.1722614358032203</v>
       </c>
       <c r="C83">
-        <v>-520.8357391394463</v>
+        <v>-548.8892050227425</v>
       </c>
       <c r="D83">
-        <v>792.5082608605539</v>
+        <v>786.1787949772577</v>
       </c>
       <c r="E83">
-        <v>63.94400000000019</v>
+        <v>85.66800000000012</v>
       </c>
       <c r="F83">
-        <v>1759.644</v>
+        <v>1781.368</v>
       </c>
       <c r="G83">
         <v>446.3</v>
@@ -8093,28 +8093,28 @@
         <v>226.775</v>
       </c>
       <c r="M83">
-        <v>258.3157392000001</v>
+        <v>261.5048224</v>
       </c>
       <c r="N83">
-        <v>-31.54073920000005</v>
+        <v>-34.72982240000002</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-31.54073920000005</v>
+        <v>-34.72982240000002</v>
       </c>
       <c r="Q83">
-        <v>152.0592607999999</v>
+        <v>148.8701776</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2754917673853703</v>
+        <v>0.288252421129002</v>
       </c>
       <c r="T83">
-        <v>4.206885384079913</v>
+        <v>4.44060123875102</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8778985001158611</v>
+        <v>0.8671924208461557</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1722614358032203</v>
+        <v>0.1732714358032204</v>
       </c>
       <c r="C84">
-        <v>-548.8892050227425</v>
+        <v>-576.8423698385593</v>
       </c>
       <c r="D84">
-        <v>786.1787949772577</v>
+        <v>779.9496301614411</v>
       </c>
       <c r="E84">
-        <v>85.66800000000012</v>
+        <v>107.3920000000003</v>
       </c>
       <c r="F84">
-        <v>1781.368</v>
+        <v>1803.092</v>
       </c>
       <c r="G84">
         <v>446.3</v>
@@ -8175,28 +8175,28 @@
         <v>226.775</v>
       </c>
       <c r="M84">
-        <v>261.5048224</v>
+        <v>264.6939056000001</v>
       </c>
       <c r="N84">
-        <v>-34.72982240000002</v>
+        <v>-37.91890560000004</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-34.72982240000002</v>
+        <v>-37.91890560000004</v>
       </c>
       <c r="Q84">
-        <v>148.8701776</v>
+        <v>145.6810943999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.288252421129002</v>
+        <v>0.3025143282542374</v>
       </c>
       <c r="T84">
-        <v>4.44060123875102</v>
+        <v>4.701813076324609</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8671924208461557</v>
+        <v>0.8567443193901778</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1732714358032204</v>
+        <v>0.1742814358032204</v>
       </c>
       <c r="C85">
-        <v>-576.8423698385593</v>
+        <v>-604.6975990043786</v>
       </c>
       <c r="D85">
-        <v>779.9496301614411</v>
+        <v>773.8184009956217</v>
       </c>
       <c r="E85">
-        <v>107.3920000000003</v>
+        <v>129.1160000000002</v>
       </c>
       <c r="F85">
-        <v>1803.092</v>
+        <v>1824.816</v>
       </c>
       <c r="G85">
         <v>446.3</v>
@@ -8257,28 +8257,28 @@
         <v>226.775</v>
       </c>
       <c r="M85">
-        <v>264.6939056000001</v>
+        <v>267.8829888000001</v>
       </c>
       <c r="N85">
-        <v>-37.91890560000004</v>
+        <v>-41.10798880000007</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-37.91890560000004</v>
+        <v>-41.10798880000007</v>
       </c>
       <c r="Q85">
-        <v>145.6810943999999</v>
+        <v>142.4920111999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3025143282542374</v>
+        <v>0.3185589737701273</v>
       </c>
       <c r="T85">
-        <v>4.701813076324609</v>
+        <v>4.995676393594898</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8567443193901778</v>
+        <v>0.8465449822545803</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1742814358032204</v>
+        <v>0.1752914358032203</v>
       </c>
       <c r="C86">
-        <v>-604.6975990043784</v>
+        <v>-632.4571841390837</v>
       </c>
       <c r="D86">
-        <v>773.8184009956217</v>
+        <v>767.7828158609162</v>
       </c>
       <c r="E86">
-        <v>129.116</v>
+        <v>150.8399999999999</v>
       </c>
       <c r="F86">
-        <v>1824.816</v>
+        <v>1846.54</v>
       </c>
       <c r="G86">
         <v>446.3</v>
@@ -8339,28 +8339,28 @@
         <v>226.775</v>
       </c>
       <c r="M86">
-        <v>267.8829888</v>
+        <v>271.072072</v>
       </c>
       <c r="N86">
-        <v>-41.10798880000002</v>
+        <v>-44.29707200000004</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-41.10798880000002</v>
+        <v>-44.29707200000004</v>
       </c>
       <c r="Q86">
-        <v>142.4920112</v>
+        <v>139.302928</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3185589737701271</v>
+        <v>0.3367429053548023</v>
       </c>
       <c r="T86">
-        <v>4.995676393594895</v>
+        <v>5.328721486501221</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8465449822545805</v>
+        <v>0.8365856295221736</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1752914358032203</v>
+        <v>0.1763014358032203</v>
       </c>
       <c r="C87">
-        <v>-632.4571841390837</v>
+        <v>-660.1233459187351</v>
       </c>
       <c r="D87">
-        <v>767.7828158609162</v>
+        <v>761.840654081265</v>
       </c>
       <c r="E87">
-        <v>150.8399999999999</v>
+        <v>172.5640000000001</v>
       </c>
       <c r="F87">
-        <v>1846.54</v>
+        <v>1868.264</v>
       </c>
       <c r="G87">
         <v>446.3</v>
@@ -8421,28 +8421,28 @@
         <v>226.775</v>
       </c>
       <c r="M87">
-        <v>271.072072</v>
+        <v>274.2611552</v>
       </c>
       <c r="N87">
-        <v>-44.29707200000004</v>
+        <v>-47.48615520000001</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-44.29707200000004</v>
+        <v>-47.48615520000001</v>
       </c>
       <c r="Q87">
-        <v>139.302928</v>
+        <v>136.1138448</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3367429053548023</v>
+        <v>0.3575245414515739</v>
       </c>
       <c r="T87">
-        <v>5.328721486501221</v>
+        <v>5.709344449822738</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8365856295221736</v>
+        <v>0.8268578896440089</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1763014358032203</v>
+        <v>0.1773114358032204</v>
       </c>
       <c r="C88">
-        <v>-660.1233459187351</v>
+        <v>-687.6982368007525</v>
       </c>
       <c r="D88">
-        <v>761.840654081265</v>
+        <v>755.9897631992475</v>
       </c>
       <c r="E88">
-        <v>172.5640000000001</v>
+        <v>194.288</v>
       </c>
       <c r="F88">
-        <v>1868.264</v>
+        <v>1889.988</v>
       </c>
       <c r="G88">
         <v>446.3</v>
@@ -8503,28 +8503,28 @@
         <v>226.775</v>
       </c>
       <c r="M88">
-        <v>274.2611552</v>
+        <v>277.4502384</v>
       </c>
       <c r="N88">
-        <v>-47.48615520000001</v>
+        <v>-50.67523840000004</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-47.48615520000001</v>
+        <v>-50.67523840000004</v>
       </c>
       <c r="Q88">
-        <v>136.1138448</v>
+        <v>132.9247616</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3575245414515739</v>
+        <v>0.3815033523324642</v>
       </c>
       <c r="T88">
-        <v>5.709344449822738</v>
+        <v>6.148524792116794</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8268578896440089</v>
+        <v>0.8173537759699397</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1773114358032204</v>
+        <v>0.1783214358032204</v>
       </c>
       <c r="C89">
-        <v>-687.6982368007525</v>
+        <v>-715.1839436235266</v>
       </c>
       <c r="D89">
-        <v>755.9897631992475</v>
+        <v>750.2280563764733</v>
       </c>
       <c r="E89">
-        <v>194.288</v>
+        <v>216.0119999999999</v>
       </c>
       <c r="F89">
-        <v>1889.988</v>
+        <v>1911.712</v>
       </c>
       <c r="G89">
         <v>446.3</v>
@@ -8585,28 +8585,28 @@
         <v>226.775</v>
       </c>
       <c r="M89">
-        <v>277.4502384</v>
+        <v>280.6393216</v>
       </c>
       <c r="N89">
-        <v>-50.67523840000004</v>
+        <v>-53.86432160000001</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-50.67523840000004</v>
+        <v>-53.86432160000001</v>
       </c>
       <c r="Q89">
-        <v>132.9247616</v>
+        <v>129.7356784</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3815033523324642</v>
+        <v>0.4094786316935029</v>
       </c>
       <c r="T89">
-        <v>6.148524792116794</v>
+        <v>6.660901858126528</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8173537759699397</v>
+        <v>0.8080656648793723</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1783214358032204</v>
+        <v>0.2273914358032204</v>
       </c>
       <c r="C90">
-        <v>-715.1839436235266</v>
+        <v>-939.6360654843304</v>
       </c>
       <c r="D90">
-        <v>750.2280563764733</v>
+        <v>547.4999345156697</v>
       </c>
       <c r="E90">
-        <v>216.0119999999999</v>
+        <v>237.7360000000001</v>
       </c>
       <c r="F90">
-        <v>1911.712</v>
+        <v>1933.436</v>
       </c>
       <c r="G90">
         <v>446.3</v>
@@ -8667,45 +8667,45 @@
         <v>226.775</v>
       </c>
       <c r="M90">
-        <v>280.6393216</v>
+        <v>388.2339488000001</v>
       </c>
       <c r="N90">
-        <v>-53.86432160000001</v>
+        <v>-161.4589488000001</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-53.86432160000001</v>
+        <v>-161.4589488000001</v>
       </c>
       <c r="Q90">
-        <v>129.7356784</v>
+        <v>22.14105119999994</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4094786316935029</v>
+        <v>0.4425403254838214</v>
       </c>
       <c r="T90">
-        <v>6.660901858126528</v>
+        <v>7.266438390683486</v>
       </c>
       <c r="U90">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8080656648793723</v>
+        <v>0.5841194483402168</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2273914358032204</v>
+        <v>0.2289414358032204</v>
       </c>
       <c r="C91">
-        <v>-939.6360654843304</v>
+        <v>-965.993778738665</v>
       </c>
       <c r="D91">
-        <v>547.4999345156697</v>
+        <v>542.866221261335</v>
       </c>
       <c r="E91">
-        <v>237.7360000000001</v>
+        <v>259.46</v>
       </c>
       <c r="F91">
-        <v>1933.436</v>
+        <v>1955.16</v>
       </c>
       <c r="G91">
         <v>446.3</v>
@@ -8749,28 +8749,28 @@
         <v>226.775</v>
       </c>
       <c r="M91">
-        <v>388.2339488000001</v>
+        <v>392.596128</v>
       </c>
       <c r="N91">
-        <v>-161.4589488000001</v>
+        <v>-165.821128</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-161.4589488000001</v>
+        <v>-165.821128</v>
       </c>
       <c r="Q91">
-        <v>22.14105119999994</v>
+        <v>17.77887199999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4425403254838214</v>
+        <v>0.4822143580322035</v>
       </c>
       <c r="T91">
-        <v>7.266438390683486</v>
+        <v>7.993082229751835</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5841194483402168</v>
+        <v>0.5776292322475478</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2289414358032204</v>
+        <v>0.2304914358032203</v>
       </c>
       <c r="C92">
-        <v>-965.993778738665</v>
+        <v>-992.2737162638443</v>
       </c>
       <c r="D92">
-        <v>542.866221261335</v>
+        <v>538.310283736156</v>
       </c>
       <c r="E92">
-        <v>259.46</v>
+        <v>281.1840000000002</v>
       </c>
       <c r="F92">
-        <v>1955.16</v>
+        <v>1976.884</v>
       </c>
       <c r="G92">
         <v>446.3</v>
@@ -8831,28 +8831,28 @@
         <v>226.775</v>
       </c>
       <c r="M92">
-        <v>392.596128</v>
+        <v>396.9583072</v>
       </c>
       <c r="N92">
-        <v>-165.821128</v>
+        <v>-170.1833072</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-165.821128</v>
+        <v>-170.1833072</v>
       </c>
       <c r="Q92">
-        <v>17.77887199999998</v>
+        <v>13.41669279999996</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4822143580322035</v>
+        <v>0.530704842258004</v>
       </c>
       <c r="T92">
-        <v>7.993082229751835</v>
+        <v>8.88120247750204</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5776292322475478</v>
+        <v>0.5712816582668054</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2304914358032203</v>
+        <v>0.2320414358032203</v>
       </c>
       <c r="C93">
-        <v>-992.2737162638443</v>
+        <v>-1018.477819932464</v>
       </c>
       <c r="D93">
-        <v>538.310283736156</v>
+        <v>533.8301800675362</v>
       </c>
       <c r="E93">
-        <v>281.1840000000002</v>
+        <v>302.9080000000001</v>
       </c>
       <c r="F93">
-        <v>1976.884</v>
+        <v>1998.608</v>
       </c>
       <c r="G93">
         <v>446.3</v>
@@ -8913,28 +8913,28 @@
         <v>226.775</v>
       </c>
       <c r="M93">
-        <v>396.9583072</v>
+        <v>401.3204864</v>
       </c>
       <c r="N93">
-        <v>-170.1833072</v>
+        <v>-174.5454864</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-170.1833072</v>
+        <v>-174.5454864</v>
       </c>
       <c r="Q93">
-        <v>13.41669279999996</v>
+        <v>9.05451359999995</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.530704842258004</v>
+        <v>0.5913179475402546</v>
       </c>
       <c r="T93">
-        <v>8.88120247750204</v>
+        <v>9.991352787189797</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5712816582668054</v>
+        <v>0.565072075024775</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2320414358032203</v>
+        <v>0.2335914358032204</v>
       </c>
       <c r="C94">
-        <v>-1018.477819932464</v>
+        <v>-1044.607967505518</v>
       </c>
       <c r="D94">
-        <v>533.8301800675362</v>
+        <v>529.4240324944822</v>
       </c>
       <c r="E94">
-        <v>302.9080000000001</v>
+        <v>324.6320000000001</v>
       </c>
       <c r="F94">
-        <v>1998.608</v>
+        <v>2020.332</v>
       </c>
       <c r="G94">
         <v>446.3</v>
@@ -8995,28 +8995,28 @@
         <v>226.775</v>
       </c>
       <c r="M94">
-        <v>401.3204864</v>
+        <v>405.6826656</v>
       </c>
       <c r="N94">
-        <v>-174.5454864</v>
+        <v>-178.9076656</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-174.5454864</v>
+        <v>-178.9076656</v>
       </c>
       <c r="Q94">
-        <v>9.05451359999995</v>
+        <v>4.692334399999993</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5913179475402546</v>
+        <v>0.6692490829031482</v>
       </c>
       <c r="T94">
-        <v>9.991352787189797</v>
+        <v>11.41868889964548</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.565072075024775</v>
+        <v>0.5589960312073043</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2335914358032204</v>
+        <v>0.2351414358032204</v>
       </c>
       <c r="C95">
-        <v>-1044.607967505518</v>
+        <v>-1070.66597525657</v>
       </c>
       <c r="D95">
-        <v>529.4240324944822</v>
+        <v>525.0900247434301</v>
       </c>
       <c r="E95">
-        <v>324.6320000000001</v>
+        <v>346.3560000000002</v>
       </c>
       <c r="F95">
-        <v>2020.332</v>
+        <v>2042.056</v>
       </c>
       <c r="G95">
         <v>446.3</v>
@@ -9077,28 +9077,28 @@
         <v>226.775</v>
       </c>
       <c r="M95">
-        <v>405.6826656</v>
+        <v>410.0448448000001</v>
       </c>
       <c r="N95">
-        <v>-178.9076656</v>
+        <v>-183.2698448000001</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-178.9076656</v>
+        <v>-183.2698448000001</v>
       </c>
       <c r="Q95">
-        <v>4.692334399999993</v>
+        <v>0.3301551999999219</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6692490829031482</v>
+        <v>0.7731572633870064</v>
       </c>
       <c r="T95">
-        <v>11.41868889964548</v>
+        <v>13.32180371625307</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5589960312073043</v>
+        <v>0.5530492649178649</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2351414358032204</v>
+        <v>0.2366914358032204</v>
       </c>
       <c r="C96">
-        <v>-1070.66597525657</v>
+        <v>-1096.653600468082</v>
       </c>
       <c r="D96">
-        <v>525.0900247434301</v>
+        <v>520.8263995319184</v>
       </c>
       <c r="E96">
-        <v>346.3560000000002</v>
+        <v>368.0800000000002</v>
       </c>
       <c r="F96">
-        <v>2042.056</v>
+        <v>2063.78</v>
       </c>
       <c r="G96">
         <v>446.3</v>
@@ -9159,28 +9159,28 @@
         <v>226.775</v>
       </c>
       <c r="M96">
-        <v>410.0448448000001</v>
+        <v>414.407024</v>
       </c>
       <c r="N96">
-        <v>-183.2698448000001</v>
+        <v>-187.632024</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-183.2698448000001</v>
+        <v>-187.632024</v>
       </c>
       <c r="Q96">
-        <v>0.3301551999999219</v>
+        <v>-4.032024000000035</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7731572633870064</v>
+        <v>0.9186287160644081</v>
       </c>
       <c r="T96">
-        <v>13.32180371625307</v>
+        <v>15.98616445950369</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5530492649178649</v>
+        <v>0.5472276937082031</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2366914358032204</v>
+        <v>0.2382414358032204</v>
       </c>
       <c r="C97">
-        <v>-1096.653600468082</v>
+        <v>-1122.572543807104</v>
       </c>
       <c r="D97">
-        <v>520.8263995319184</v>
+        <v>516.6314561928967</v>
       </c>
       <c r="E97">
-        <v>368.0800000000002</v>
+        <v>389.8040000000003</v>
       </c>
       <c r="F97">
-        <v>2063.78</v>
+        <v>2085.504</v>
       </c>
       <c r="G97">
         <v>446.3</v>
@@ -9241,28 +9241,28 @@
         <v>226.775</v>
       </c>
       <c r="M97">
-        <v>414.407024</v>
+        <v>418.7692032000001</v>
       </c>
       <c r="N97">
-        <v>-187.632024</v>
+        <v>-191.9942032000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-187.632024</v>
+        <v>-191.9942032000001</v>
       </c>
       <c r="Q97">
-        <v>-4.032024000000035</v>
+        <v>-8.394203200000106</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9186287160644081</v>
+        <v>1.136835895080511</v>
       </c>
       <c r="T97">
-        <v>15.98616445950369</v>
+        <v>19.98270557437962</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5472276937082031</v>
+        <v>0.541527405232076</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2382414358032204</v>
+        <v>0.2397914358032204</v>
       </c>
       <c r="C98">
-        <v>-1122.572543807103</v>
+        <v>-1148.42445158707</v>
       </c>
       <c r="D98">
-        <v>516.6314561928967</v>
+        <v>512.5035484129302</v>
       </c>
       <c r="E98">
-        <v>389.8039999999999</v>
+        <v>411.528</v>
       </c>
       <c r="F98">
-        <v>2085.504</v>
+        <v>2107.228</v>
       </c>
       <c r="G98">
         <v>446.3</v>
@@ -9323,28 +9323,28 @@
         <v>226.775</v>
       </c>
       <c r="M98">
-        <v>418.7692032</v>
+        <v>423.1313824</v>
       </c>
       <c r="N98">
-        <v>-191.9942032</v>
+        <v>-196.3563824</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-191.9942032</v>
+        <v>-196.3563824</v>
       </c>
       <c r="Q98">
-        <v>-8.394203199999993</v>
+        <v>-12.75638240000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.136835895080508</v>
+        <v>1.500514526774011</v>
       </c>
       <c r="T98">
-        <v>19.98270557437957</v>
+        <v>26.64360743250609</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5415274052320761</v>
+        <v>0.5359446484771062</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2397914358032204</v>
+        <v>0.2413414358032204</v>
       </c>
       <c r="C99">
-        <v>-1148.42445158707</v>
+        <v>-1174.210917922029</v>
       </c>
       <c r="D99">
-        <v>512.5035484129302</v>
+        <v>508.4410820779717</v>
       </c>
       <c r="E99">
-        <v>411.528</v>
+        <v>433.2520000000002</v>
       </c>
       <c r="F99">
-        <v>2107.228</v>
+        <v>2128.952</v>
       </c>
       <c r="G99">
         <v>446.3</v>
@@ -9405,28 +9405,28 @@
         <v>226.775</v>
       </c>
       <c r="M99">
-        <v>423.1313824</v>
+        <v>427.4935616000001</v>
       </c>
       <c r="N99">
-        <v>-196.3563824</v>
+        <v>-200.7185616000001</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-196.3563824</v>
+        <v>-200.7185616000001</v>
       </c>
       <c r="Q99">
-        <v>-12.75638240000001</v>
+        <v>-17.11856160000008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.500514526774011</v>
+        <v>2.227871790161015</v>
       </c>
       <c r="T99">
-        <v>26.64360743250609</v>
+        <v>39.96541114875913</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5359446484771062</v>
+        <v>0.5304758255334622</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2413414358032204</v>
+        <v>0.2428914358032203</v>
       </c>
       <c r="C100">
-        <v>-1174.210917922029</v>
+        <v>-1199.933486779214</v>
       </c>
       <c r="D100">
-        <v>508.4410820779717</v>
+        <v>504.4425132207856</v>
       </c>
       <c r="E100">
-        <v>433.2520000000002</v>
+        <v>454.9759999999999</v>
       </c>
       <c r="F100">
-        <v>2128.952</v>
+        <v>2150.676</v>
       </c>
       <c r="G100">
         <v>446.3</v>
@@ -9487,28 +9487,28 @@
         <v>226.775</v>
       </c>
       <c r="M100">
-        <v>427.4935616000001</v>
+        <v>431.8557408</v>
       </c>
       <c r="N100">
-        <v>-200.7185616000001</v>
+        <v>-205.0807408</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-200.7185616000001</v>
+        <v>-205.0807408</v>
       </c>
       <c r="Q100">
-        <v>-17.11856160000008</v>
+        <v>-21.48074079999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.227871790161015</v>
+        <v>4.409943580322031</v>
       </c>
       <c r="T100">
-        <v>39.96541114875913</v>
+        <v>79.93082229751826</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5304758255334622</v>
+        <v>0.5251174838614071</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2428914358032203</v>
-      </c>
-      <c r="C101">
-        <v>-1199.933486779214</v>
-      </c>
-      <c r="D101">
-        <v>504.4425132207856</v>
-      </c>
-      <c r="E101">
-        <v>454.9759999999999</v>
-      </c>
-      <c r="F101">
-        <v>2150.676</v>
-      </c>
-      <c r="G101">
-        <v>446.3</v>
-      </c>
-      <c r="H101">
-        <v>476.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>410.375</v>
-      </c>
-      <c r="K101">
-        <v>183.6</v>
-      </c>
-      <c r="L101">
-        <v>226.775</v>
-      </c>
-      <c r="M101">
-        <v>431.8557408</v>
-      </c>
-      <c r="N101">
-        <v>-205.0807408</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-205.0807408</v>
-      </c>
-      <c r="Q101">
-        <v>-21.48074079999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.409943580322031</v>
-      </c>
-      <c r="T101">
-        <v>79.93082229751826</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2008</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5251174838614071</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
